--- a/src/plugins/downloads/helpers/fcerm1/fcerm1_template.xlsx
+++ b/src/plugins/downloads/helpers/fcerm1/fcerm1_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/795110/Documents/Fujale-Space/Work/Projects/EA/FCRM/PAFs/Remote/migration/pafs-backend-api/src/plugins/downloads/helpers/fcerm1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C15E8E1-D707-9141-AF11-DC8D38681C81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF37731B-D2B5-9F44-A18A-33B688FC8F50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="16380" windowHeight="8200" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-2800" yWindow="-21000" windowWidth="38400" windowHeight="21000" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Master local choices" sheetId="1" r:id="rId1"/>
@@ -1571,7 +1571,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -1629,6 +1629,72 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1642,50 +1708,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="11" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1838,6 +1862,24 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="15" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1853,22 +1895,67 @@
     <xf numFmtId="0" fontId="7" fillId="19" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="11" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2156,4209 +2243,4217 @@
     <tabColor rgb="FF92D050"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:NL7"/>
+  <dimension ref="A1:NM7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="24.140625" style="15" customWidth="1"/>
-    <col min="2" max="2" width="39" style="16" customWidth="1"/>
-    <col min="3" max="4" width="21" style="16" customWidth="1"/>
-    <col min="5" max="5" width="21" style="17" customWidth="1"/>
-    <col min="6" max="6" width="21" style="16" customWidth="1"/>
-    <col min="7" max="7" width="21" style="15" customWidth="1"/>
-    <col min="8" max="17" width="21" style="16" customWidth="1"/>
-    <col min="18" max="19" width="21" style="18" customWidth="1"/>
-    <col min="20" max="22" width="21" style="16" customWidth="1"/>
-    <col min="23" max="24" width="21" style="18" customWidth="1"/>
-    <col min="25" max="32" width="21" style="16" customWidth="1"/>
-    <col min="33" max="38" width="21" style="19" customWidth="1"/>
-    <col min="39" max="360" width="21" style="16" customWidth="1"/>
-    <col min="361" max="363" width="22.28515625" style="20" customWidth="1"/>
-    <col min="364" max="364" width="17.140625" style="20" customWidth="1"/>
-    <col min="365" max="365" width="19.7109375" style="20" customWidth="1"/>
-    <col min="366" max="366" width="21.5703125" style="20" customWidth="1"/>
-    <col min="367" max="372" width="19.7109375" style="20" customWidth="1"/>
-    <col min="373" max="373" width="21.5703125" style="20" customWidth="1"/>
-    <col min="377" max="16384" width="8.7109375" style="20"/>
+    <col min="1" max="1" width="24.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="39" style="2" customWidth="1"/>
+    <col min="3" max="4" width="21" style="2" customWidth="1"/>
+    <col min="5" max="5" width="21" style="3" customWidth="1"/>
+    <col min="6" max="6" width="21" style="2" customWidth="1"/>
+    <col min="7" max="7" width="21" style="1" customWidth="1"/>
+    <col min="8" max="17" width="21" style="2" customWidth="1"/>
+    <col min="18" max="19" width="21" style="4" customWidth="1"/>
+    <col min="20" max="22" width="21" style="2" customWidth="1"/>
+    <col min="23" max="24" width="21" style="4" customWidth="1"/>
+    <col min="25" max="32" width="21" style="2" customWidth="1"/>
+    <col min="33" max="38" width="21" style="5" customWidth="1"/>
+    <col min="39" max="360" width="21" style="2" customWidth="1"/>
+    <col min="361" max="363" width="22.28515625" style="6" customWidth="1"/>
+    <col min="364" max="364" width="17.140625" style="6" customWidth="1"/>
+    <col min="365" max="365" width="19.7109375" style="6" customWidth="1"/>
+    <col min="366" max="366" width="21.5703125" style="6" customWidth="1"/>
+    <col min="367" max="373" width="19.7109375" style="6" customWidth="1"/>
+    <col min="374" max="374" width="21.5703125" style="6" customWidth="1"/>
+    <col min="378" max="16384" width="8.7109375" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:373" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:374" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="73" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
-      <c r="K1" s="21"/>
-      <c r="L1" s="21"/>
-      <c r="M1" s="21"/>
-      <c r="N1" s="21"/>
-      <c r="O1" s="21"/>
-      <c r="P1" s="21"/>
-      <c r="Q1" s="21"/>
-      <c r="R1" s="25"/>
-      <c r="S1" s="25"/>
-      <c r="T1" s="21"/>
-      <c r="U1" s="21"/>
-      <c r="V1" s="21"/>
-      <c r="W1" s="25"/>
-      <c r="X1" s="25"/>
-      <c r="Y1" s="21"/>
-      <c r="Z1" s="21"/>
-      <c r="AA1" s="21"/>
-      <c r="AB1" s="21"/>
-      <c r="AC1" s="21"/>
-      <c r="AD1" s="21"/>
-      <c r="AE1" s="21"/>
-      <c r="AF1" s="21"/>
-      <c r="AG1" s="26"/>
-      <c r="AH1" s="26"/>
-      <c r="AI1" s="26"/>
-      <c r="AJ1" s="26"/>
-      <c r="AK1" s="26"/>
-      <c r="AL1" s="26"/>
-      <c r="AM1" s="21"/>
-      <c r="AN1" s="21"/>
-      <c r="AO1" s="21"/>
-      <c r="AP1" s="21"/>
-      <c r="AQ1" s="21"/>
-      <c r="AR1" s="21"/>
-      <c r="AS1" s="21"/>
-      <c r="AT1" s="21"/>
-      <c r="AU1" s="21"/>
-      <c r="AV1" s="21"/>
-      <c r="AW1" s="21"/>
-      <c r="AX1" s="21"/>
-      <c r="AY1" s="21"/>
-      <c r="AZ1" s="21"/>
-      <c r="BA1" s="21"/>
-      <c r="BB1" s="21"/>
-      <c r="BC1" s="21"/>
-      <c r="BD1" s="21"/>
-      <c r="BE1" s="21"/>
-      <c r="BF1" s="21"/>
-      <c r="BG1" s="21"/>
-      <c r="BH1" s="21"/>
-      <c r="BI1" s="21"/>
-      <c r="BJ1" s="21"/>
-      <c r="BK1" s="21"/>
-      <c r="BL1" s="21"/>
-      <c r="BM1" s="21"/>
-      <c r="BN1" s="21"/>
-      <c r="BO1" s="21"/>
-      <c r="BP1" s="21"/>
-      <c r="BQ1" s="21"/>
-      <c r="BR1" s="21"/>
-      <c r="BS1" s="21"/>
-      <c r="BT1" s="21"/>
-      <c r="BU1" s="21"/>
-      <c r="BV1" s="21"/>
-      <c r="BW1" s="21"/>
-      <c r="BX1" s="21"/>
-      <c r="BY1" s="21"/>
-      <c r="BZ1" s="21"/>
-      <c r="CA1" s="21"/>
-      <c r="CB1" s="27"/>
-      <c r="CC1" s="28"/>
-      <c r="CD1" s="28"/>
-      <c r="CE1" s="28"/>
-      <c r="CF1" s="21"/>
-      <c r="CG1" s="21"/>
-      <c r="CH1" s="21"/>
-      <c r="CI1" s="21"/>
-      <c r="CJ1" s="21"/>
-      <c r="CK1" s="21"/>
-      <c r="CL1" s="27"/>
-      <c r="CM1" s="28"/>
-      <c r="CN1" s="28"/>
-      <c r="CO1" s="28"/>
-      <c r="CP1" s="21"/>
-      <c r="CQ1" s="21"/>
-      <c r="CR1" s="21"/>
-      <c r="CS1" s="21"/>
-      <c r="CT1" s="21"/>
-      <c r="CU1" s="21"/>
-      <c r="CV1" s="27"/>
-      <c r="CW1" s="28"/>
-      <c r="CX1" s="28"/>
-      <c r="CY1" s="28"/>
-      <c r="CZ1" s="21"/>
-      <c r="DA1" s="21"/>
-      <c r="DB1" s="21"/>
-      <c r="DC1" s="21"/>
-      <c r="DD1" s="21"/>
-      <c r="DE1" s="21"/>
-      <c r="DF1" s="27"/>
-      <c r="DG1" s="28"/>
-      <c r="DH1" s="28"/>
-      <c r="DI1" s="28"/>
-      <c r="DJ1" s="21"/>
-      <c r="DK1" s="21"/>
-      <c r="DL1" s="21"/>
-      <c r="DM1" s="21"/>
-      <c r="DN1" s="21"/>
-      <c r="DO1" s="21"/>
-      <c r="DP1" s="27"/>
-      <c r="DQ1" s="28"/>
-      <c r="DR1" s="28"/>
-      <c r="DS1" s="28"/>
-      <c r="DT1" s="21"/>
-      <c r="DU1" s="21"/>
-      <c r="DV1" s="21"/>
-      <c r="DW1" s="21"/>
-      <c r="DX1" s="21"/>
-      <c r="DY1" s="21"/>
-      <c r="DZ1" s="27"/>
-      <c r="EA1" s="28"/>
-      <c r="EB1" s="28"/>
-      <c r="EC1" s="28"/>
-      <c r="ED1" s="21"/>
-      <c r="EE1" s="21"/>
-      <c r="EF1" s="21"/>
-      <c r="EG1" s="21"/>
-      <c r="EH1" s="21"/>
-      <c r="EI1" s="21"/>
-      <c r="EJ1" s="27"/>
-      <c r="EK1" s="28"/>
-      <c r="EL1" s="28"/>
-      <c r="EM1" s="28"/>
-      <c r="EN1" s="21"/>
-      <c r="EO1" s="21"/>
-      <c r="EP1" s="21"/>
-      <c r="EQ1" s="21"/>
-      <c r="ER1" s="21"/>
-      <c r="ES1" s="21"/>
-      <c r="ET1" s="27"/>
-      <c r="EU1" s="28"/>
-      <c r="EV1" s="28"/>
-      <c r="EW1" s="28"/>
-      <c r="EX1" s="21"/>
-      <c r="EY1" s="21"/>
-      <c r="EZ1" s="21"/>
-      <c r="FA1" s="21"/>
-      <c r="FB1" s="21"/>
-      <c r="FC1" s="21"/>
-      <c r="FD1" s="21"/>
-      <c r="FE1" s="21"/>
-      <c r="FF1" s="21"/>
-      <c r="FG1" s="21"/>
-      <c r="FH1" s="21"/>
-      <c r="FI1" s="21"/>
-      <c r="FJ1" s="21"/>
-      <c r="FK1" s="21"/>
-      <c r="FL1" s="21"/>
-      <c r="FM1" s="21"/>
-      <c r="FN1" s="21"/>
-      <c r="FO1" s="21"/>
-      <c r="FP1" s="21"/>
-      <c r="FQ1" s="21"/>
-      <c r="FR1" s="21"/>
-      <c r="FS1" s="21"/>
-      <c r="FT1" s="21"/>
-      <c r="FU1" s="21"/>
-      <c r="FV1" s="21"/>
-      <c r="FW1" s="21"/>
-      <c r="FX1" s="21"/>
-      <c r="FY1" s="21"/>
-      <c r="FZ1" s="21"/>
-      <c r="GA1" s="21"/>
-      <c r="GB1" s="21"/>
-      <c r="GC1" s="21"/>
-      <c r="GD1" s="21"/>
-      <c r="GE1" s="21"/>
-      <c r="GF1" s="21"/>
-      <c r="GG1" s="21"/>
-      <c r="GH1" s="21"/>
-      <c r="GI1" s="21"/>
-      <c r="GJ1" s="21"/>
-      <c r="GK1" s="21"/>
-      <c r="GL1" s="21"/>
-      <c r="GM1" s="21"/>
-      <c r="GN1" s="21"/>
-      <c r="GO1" s="21"/>
-      <c r="GP1" s="21"/>
-      <c r="GQ1" s="21"/>
-      <c r="GR1" s="21"/>
-      <c r="GS1" s="21"/>
-      <c r="GT1" s="21"/>
-      <c r="GU1" s="21"/>
-      <c r="GV1" s="21"/>
-      <c r="GW1" s="21"/>
-      <c r="GX1" s="21"/>
-      <c r="GY1" s="21"/>
-      <c r="GZ1" s="21"/>
-      <c r="HA1" s="21"/>
-      <c r="HB1" s="21"/>
-      <c r="HC1" s="21"/>
-      <c r="HD1" s="21"/>
-      <c r="HE1" s="21"/>
-      <c r="HF1" s="21"/>
-      <c r="HG1" s="21"/>
-      <c r="HH1" s="21"/>
-      <c r="HI1" s="21"/>
-      <c r="HJ1" s="21"/>
-      <c r="HK1" s="21"/>
-      <c r="HL1" s="21"/>
-      <c r="HM1" s="21"/>
-      <c r="HN1" s="21"/>
-      <c r="HO1" s="21"/>
-      <c r="HP1" s="21"/>
-      <c r="HQ1" s="21"/>
-      <c r="HR1" s="21"/>
-      <c r="HS1" s="21"/>
-      <c r="HT1" s="21"/>
-      <c r="HU1" s="21"/>
-      <c r="HV1" s="21"/>
-      <c r="HW1" s="21"/>
-      <c r="HX1" s="21"/>
-      <c r="HY1" s="21"/>
-      <c r="HZ1" s="21"/>
-      <c r="IA1" s="21"/>
-      <c r="IB1" s="21"/>
-      <c r="IC1" s="21"/>
-      <c r="ID1" s="21"/>
-      <c r="IE1" s="21"/>
-      <c r="IF1" s="21"/>
-      <c r="IG1" s="21"/>
-      <c r="IH1" s="21"/>
-      <c r="II1" s="21"/>
-      <c r="IJ1" s="21"/>
-      <c r="IK1" s="21"/>
-      <c r="IL1" s="21"/>
-      <c r="IM1" s="21"/>
-      <c r="IN1" s="21"/>
-      <c r="IO1" s="21"/>
-      <c r="IP1" s="21"/>
-      <c r="IQ1" s="21"/>
-      <c r="IR1" s="21"/>
-      <c r="IS1" s="21"/>
-      <c r="IT1" s="21"/>
-      <c r="IU1" s="21"/>
-      <c r="IV1" s="21"/>
-      <c r="IW1" s="21"/>
-      <c r="IX1" s="21"/>
-      <c r="IY1" s="21"/>
-      <c r="IZ1" s="21"/>
-      <c r="JA1" s="21"/>
-      <c r="JB1" s="21"/>
-      <c r="JC1" s="21"/>
-      <c r="JD1" s="21"/>
-      <c r="JE1" s="21"/>
-      <c r="JF1" s="21"/>
-      <c r="JG1" s="21"/>
-      <c r="JH1" s="21"/>
-      <c r="JI1" s="21"/>
-      <c r="JJ1" s="21"/>
-      <c r="JK1" s="21"/>
-      <c r="JL1" s="21"/>
-      <c r="JM1" s="21"/>
-      <c r="JN1" s="21"/>
-      <c r="JO1" s="21"/>
-      <c r="JP1" s="21"/>
-      <c r="JQ1" s="21"/>
-      <c r="JR1" s="21"/>
-      <c r="JS1" s="21"/>
-      <c r="JT1" s="21"/>
-      <c r="JU1" s="21"/>
-      <c r="JV1" s="21"/>
-      <c r="JW1" s="21"/>
-      <c r="JX1" s="21"/>
-      <c r="JY1" s="21"/>
-      <c r="JZ1" s="21"/>
-      <c r="KA1" s="21"/>
-      <c r="KB1" s="21"/>
-      <c r="KC1" s="21"/>
-      <c r="KD1" s="21"/>
-      <c r="KE1" s="21"/>
-      <c r="KF1" s="21"/>
-      <c r="KG1" s="21"/>
-      <c r="KH1" s="21"/>
-      <c r="KI1" s="21"/>
-      <c r="KJ1" s="21"/>
-      <c r="KK1" s="21"/>
-      <c r="KL1" s="21"/>
-      <c r="KM1" s="21"/>
-      <c r="KN1" s="21"/>
-      <c r="KO1" s="21"/>
-      <c r="KP1" s="21"/>
-      <c r="KQ1" s="21"/>
-      <c r="KR1" s="21"/>
-      <c r="KS1" s="21"/>
-      <c r="KT1" s="21"/>
-      <c r="KU1" s="21"/>
-      <c r="KV1" s="21"/>
-      <c r="KW1" s="21"/>
-      <c r="KX1" s="21"/>
-      <c r="KY1" s="21"/>
-      <c r="KZ1" s="21"/>
-      <c r="LA1" s="21"/>
-      <c r="LB1" s="21"/>
-      <c r="LC1" s="21"/>
-      <c r="LD1" s="21"/>
-      <c r="LE1" s="21"/>
-      <c r="LF1" s="21"/>
-      <c r="LG1" s="21"/>
-      <c r="LH1" s="21"/>
-      <c r="LI1" s="21"/>
-      <c r="LJ1" s="21"/>
-      <c r="LK1" s="21"/>
-      <c r="LL1" s="21"/>
-      <c r="LM1" s="21"/>
-      <c r="LN1" s="21"/>
-      <c r="LO1" s="21"/>
-      <c r="LP1" s="21"/>
-      <c r="LQ1" s="21"/>
-      <c r="LR1" s="21"/>
-      <c r="LS1" s="21"/>
-      <c r="LT1" s="21"/>
-      <c r="LU1" s="21"/>
-      <c r="LV1" s="21"/>
-      <c r="LW1" s="21"/>
-      <c r="LX1" s="21"/>
-      <c r="LY1" s="21"/>
-      <c r="LZ1" s="21"/>
-      <c r="MA1" s="21"/>
-      <c r="MB1" s="21"/>
-      <c r="MC1" s="21"/>
-      <c r="MD1" s="21"/>
-      <c r="ME1" s="21"/>
-      <c r="MF1" s="21"/>
-      <c r="MG1" s="21"/>
-      <c r="MH1" s="21"/>
-      <c r="MI1" s="21"/>
-      <c r="MJ1" s="21"/>
-      <c r="MK1" s="21"/>
-      <c r="ML1" s="21"/>
-      <c r="MM1" s="21"/>
-      <c r="MN1" s="21"/>
-      <c r="MO1" s="21"/>
-      <c r="MP1" s="21"/>
-      <c r="MQ1" s="21"/>
-      <c r="MR1" s="21"/>
-      <c r="MS1" s="21"/>
-      <c r="MT1" s="21"/>
-      <c r="MU1" s="21"/>
-      <c r="MV1" s="21"/>
-      <c r="MW1" s="29"/>
-      <c r="MX1" s="29"/>
-      <c r="MY1" s="29"/>
-      <c r="MZ1" s="29"/>
-      <c r="NA1" s="29"/>
-      <c r="NB1" s="29"/>
-      <c r="NC1" s="29"/>
-      <c r="ND1" s="29"/>
-      <c r="NE1" s="29"/>
-      <c r="NF1" s="29"/>
-      <c r="NG1" s="29"/>
-      <c r="NH1" s="29"/>
-      <c r="NI1" s="29"/>
+      <c r="B1" s="73"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
+      <c r="K1" s="7"/>
+      <c r="L1" s="7"/>
+      <c r="M1" s="7"/>
+      <c r="N1" s="7"/>
+      <c r="O1" s="7"/>
+      <c r="P1" s="7"/>
+      <c r="Q1" s="7"/>
+      <c r="R1" s="11"/>
+      <c r="S1" s="11"/>
+      <c r="T1" s="7"/>
+      <c r="U1" s="7"/>
+      <c r="V1" s="7"/>
+      <c r="W1" s="11"/>
+      <c r="X1" s="11"/>
+      <c r="Y1" s="7"/>
+      <c r="Z1" s="7"/>
+      <c r="AA1" s="7"/>
+      <c r="AB1" s="7"/>
+      <c r="AC1" s="7"/>
+      <c r="AD1" s="7"/>
+      <c r="AE1" s="7"/>
+      <c r="AF1" s="7"/>
+      <c r="AG1" s="12"/>
+      <c r="AH1" s="12"/>
+      <c r="AI1" s="12"/>
+      <c r="AJ1" s="12"/>
+      <c r="AK1" s="12"/>
+      <c r="AL1" s="12"/>
+      <c r="AM1" s="7"/>
+      <c r="AN1" s="7"/>
+      <c r="AO1" s="7"/>
+      <c r="AP1" s="7"/>
+      <c r="AQ1" s="7"/>
+      <c r="AR1" s="7"/>
+      <c r="AS1" s="7"/>
+      <c r="AT1" s="7"/>
+      <c r="AU1" s="7"/>
+      <c r="AV1" s="7"/>
+      <c r="AW1" s="7"/>
+      <c r="AX1" s="7"/>
+      <c r="AY1" s="7"/>
+      <c r="AZ1" s="7"/>
+      <c r="BA1" s="7"/>
+      <c r="BB1" s="7"/>
+      <c r="BC1" s="7"/>
+      <c r="BD1" s="7"/>
+      <c r="BE1" s="7"/>
+      <c r="BF1" s="7"/>
+      <c r="BG1" s="7"/>
+      <c r="BH1" s="7"/>
+      <c r="BI1" s="7"/>
+      <c r="BJ1" s="7"/>
+      <c r="BK1" s="7"/>
+      <c r="BL1" s="7"/>
+      <c r="BM1" s="7"/>
+      <c r="BN1" s="7"/>
+      <c r="BO1" s="7"/>
+      <c r="BP1" s="7"/>
+      <c r="BQ1" s="7"/>
+      <c r="BR1" s="7"/>
+      <c r="BS1" s="7"/>
+      <c r="BT1" s="7"/>
+      <c r="BU1" s="7"/>
+      <c r="BV1" s="7"/>
+      <c r="BW1" s="7"/>
+      <c r="BX1" s="7"/>
+      <c r="BY1" s="7"/>
+      <c r="BZ1" s="7"/>
+      <c r="CA1" s="7"/>
+      <c r="CB1" s="13"/>
+      <c r="CC1" s="14"/>
+      <c r="CD1" s="14"/>
+      <c r="CE1" s="14"/>
+      <c r="CF1" s="7"/>
+      <c r="CG1" s="7"/>
+      <c r="CH1" s="7"/>
+      <c r="CI1" s="7"/>
+      <c r="CJ1" s="7"/>
+      <c r="CK1" s="7"/>
+      <c r="CL1" s="13"/>
+      <c r="CM1" s="14"/>
+      <c r="CN1" s="14"/>
+      <c r="CO1" s="14"/>
+      <c r="CP1" s="7"/>
+      <c r="CQ1" s="7"/>
+      <c r="CR1" s="7"/>
+      <c r="CS1" s="7"/>
+      <c r="CT1" s="7"/>
+      <c r="CU1" s="7"/>
+      <c r="CV1" s="13"/>
+      <c r="CW1" s="14"/>
+      <c r="CX1" s="14"/>
+      <c r="CY1" s="14"/>
+      <c r="CZ1" s="7"/>
+      <c r="DA1" s="7"/>
+      <c r="DB1" s="7"/>
+      <c r="DC1" s="7"/>
+      <c r="DD1" s="7"/>
+      <c r="DE1" s="7"/>
+      <c r="DF1" s="13"/>
+      <c r="DG1" s="14"/>
+      <c r="DH1" s="14"/>
+      <c r="DI1" s="14"/>
+      <c r="DJ1" s="7"/>
+      <c r="DK1" s="7"/>
+      <c r="DL1" s="7"/>
+      <c r="DM1" s="7"/>
+      <c r="DN1" s="7"/>
+      <c r="DO1" s="7"/>
+      <c r="DP1" s="13"/>
+      <c r="DQ1" s="14"/>
+      <c r="DR1" s="14"/>
+      <c r="DS1" s="14"/>
+      <c r="DT1" s="7"/>
+      <c r="DU1" s="7"/>
+      <c r="DV1" s="7"/>
+      <c r="DW1" s="7"/>
+      <c r="DX1" s="7"/>
+      <c r="DY1" s="7"/>
+      <c r="DZ1" s="13"/>
+      <c r="EA1" s="14"/>
+      <c r="EB1" s="14"/>
+      <c r="EC1" s="14"/>
+      <c r="ED1" s="7"/>
+      <c r="EE1" s="7"/>
+      <c r="EF1" s="7"/>
+      <c r="EG1" s="7"/>
+      <c r="EH1" s="7"/>
+      <c r="EI1" s="7"/>
+      <c r="EJ1" s="13"/>
+      <c r="EK1" s="14"/>
+      <c r="EL1" s="14"/>
+      <c r="EM1" s="14"/>
+      <c r="EN1" s="7"/>
+      <c r="EO1" s="7"/>
+      <c r="EP1" s="7"/>
+      <c r="EQ1" s="7"/>
+      <c r="ER1" s="7"/>
+      <c r="ES1" s="7"/>
+      <c r="ET1" s="13"/>
+      <c r="EU1" s="14"/>
+      <c r="EV1" s="14"/>
+      <c r="EW1" s="14"/>
+      <c r="EX1" s="7"/>
+      <c r="EY1" s="7"/>
+      <c r="EZ1" s="7"/>
+      <c r="FA1" s="7"/>
+      <c r="FB1" s="7"/>
+      <c r="FC1" s="7"/>
+      <c r="FD1" s="7"/>
+      <c r="FE1" s="7"/>
+      <c r="FF1" s="7"/>
+      <c r="FG1" s="7"/>
+      <c r="FH1" s="7"/>
+      <c r="FI1" s="7"/>
+      <c r="FJ1" s="7"/>
+      <c r="FK1" s="7"/>
+      <c r="FL1" s="7"/>
+      <c r="FM1" s="7"/>
+      <c r="FN1" s="7"/>
+      <c r="FO1" s="7"/>
+      <c r="FP1" s="7"/>
+      <c r="FQ1" s="7"/>
+      <c r="FR1" s="7"/>
+      <c r="FS1" s="7"/>
+      <c r="FT1" s="7"/>
+      <c r="FU1" s="7"/>
+      <c r="FV1" s="7"/>
+      <c r="FW1" s="7"/>
+      <c r="FX1" s="7"/>
+      <c r="FY1" s="7"/>
+      <c r="FZ1" s="7"/>
+      <c r="GA1" s="7"/>
+      <c r="GB1" s="7"/>
+      <c r="GC1" s="7"/>
+      <c r="GD1" s="7"/>
+      <c r="GE1" s="7"/>
+      <c r="GF1" s="7"/>
+      <c r="GG1" s="7"/>
+      <c r="GH1" s="7"/>
+      <c r="GI1" s="7"/>
+      <c r="GJ1" s="7"/>
+      <c r="GK1" s="7"/>
+      <c r="GL1" s="7"/>
+      <c r="GM1" s="7"/>
+      <c r="GN1" s="7"/>
+      <c r="GO1" s="7"/>
+      <c r="GP1" s="7"/>
+      <c r="GQ1" s="7"/>
+      <c r="GR1" s="7"/>
+      <c r="GS1" s="7"/>
+      <c r="GT1" s="7"/>
+      <c r="GU1" s="7"/>
+      <c r="GV1" s="7"/>
+      <c r="GW1" s="7"/>
+      <c r="GX1" s="7"/>
+      <c r="GY1" s="7"/>
+      <c r="GZ1" s="7"/>
+      <c r="HA1" s="7"/>
+      <c r="HB1" s="7"/>
+      <c r="HC1" s="7"/>
+      <c r="HD1" s="7"/>
+      <c r="HE1" s="7"/>
+      <c r="HF1" s="7"/>
+      <c r="HG1" s="7"/>
+      <c r="HH1" s="7"/>
+      <c r="HI1" s="7"/>
+      <c r="HJ1" s="7"/>
+      <c r="HK1" s="7"/>
+      <c r="HL1" s="7"/>
+      <c r="HM1" s="7"/>
+      <c r="HN1" s="7"/>
+      <c r="HO1" s="7"/>
+      <c r="HP1" s="7"/>
+      <c r="HQ1" s="7"/>
+      <c r="HR1" s="7"/>
+      <c r="HS1" s="7"/>
+      <c r="HT1" s="7"/>
+      <c r="HU1" s="7"/>
+      <c r="HV1" s="7"/>
+      <c r="HW1" s="7"/>
+      <c r="HX1" s="7"/>
+      <c r="HY1" s="7"/>
+      <c r="HZ1" s="7"/>
+      <c r="IA1" s="7"/>
+      <c r="IB1" s="7"/>
+      <c r="IC1" s="7"/>
+      <c r="ID1" s="7"/>
+      <c r="IE1" s="7"/>
+      <c r="IF1" s="7"/>
+      <c r="IG1" s="7"/>
+      <c r="IH1" s="7"/>
+      <c r="II1" s="7"/>
+      <c r="IJ1" s="7"/>
+      <c r="IK1" s="7"/>
+      <c r="IL1" s="7"/>
+      <c r="IM1" s="7"/>
+      <c r="IN1" s="7"/>
+      <c r="IO1" s="7"/>
+      <c r="IP1" s="7"/>
+      <c r="IQ1" s="7"/>
+      <c r="IR1" s="7"/>
+      <c r="IS1" s="7"/>
+      <c r="IT1" s="7"/>
+      <c r="IU1" s="7"/>
+      <c r="IV1" s="7"/>
+      <c r="IW1" s="7"/>
+      <c r="IX1" s="7"/>
+      <c r="IY1" s="7"/>
+      <c r="IZ1" s="7"/>
+      <c r="JA1" s="7"/>
+      <c r="JB1" s="7"/>
+      <c r="JC1" s="7"/>
+      <c r="JD1" s="7"/>
+      <c r="JE1" s="7"/>
+      <c r="JF1" s="7"/>
+      <c r="JG1" s="7"/>
+      <c r="JH1" s="7"/>
+      <c r="JI1" s="7"/>
+      <c r="JJ1" s="7"/>
+      <c r="JK1" s="7"/>
+      <c r="JL1" s="7"/>
+      <c r="JM1" s="7"/>
+      <c r="JN1" s="7"/>
+      <c r="JO1" s="7"/>
+      <c r="JP1" s="7"/>
+      <c r="JQ1" s="7"/>
+      <c r="JR1" s="7"/>
+      <c r="JS1" s="7"/>
+      <c r="JT1" s="7"/>
+      <c r="JU1" s="7"/>
+      <c r="JV1" s="7"/>
+      <c r="JW1" s="7"/>
+      <c r="JX1" s="7"/>
+      <c r="JY1" s="7"/>
+      <c r="JZ1" s="7"/>
+      <c r="KA1" s="7"/>
+      <c r="KB1" s="7"/>
+      <c r="KC1" s="7"/>
+      <c r="KD1" s="7"/>
+      <c r="KE1" s="7"/>
+      <c r="KF1" s="7"/>
+      <c r="KG1" s="7"/>
+      <c r="KH1" s="7"/>
+      <c r="KI1" s="7"/>
+      <c r="KJ1" s="7"/>
+      <c r="KK1" s="7"/>
+      <c r="KL1" s="7"/>
+      <c r="KM1" s="7"/>
+      <c r="KN1" s="7"/>
+      <c r="KO1" s="7"/>
+      <c r="KP1" s="7"/>
+      <c r="KQ1" s="7"/>
+      <c r="KR1" s="7"/>
+      <c r="KS1" s="7"/>
+      <c r="KT1" s="7"/>
+      <c r="KU1" s="7"/>
+      <c r="KV1" s="7"/>
+      <c r="KW1" s="7"/>
+      <c r="KX1" s="7"/>
+      <c r="KY1" s="7"/>
+      <c r="KZ1" s="7"/>
+      <c r="LA1" s="7"/>
+      <c r="LB1" s="7"/>
+      <c r="LC1" s="7"/>
+      <c r="LD1" s="7"/>
+      <c r="LE1" s="7"/>
+      <c r="LF1" s="7"/>
+      <c r="LG1" s="7"/>
+      <c r="LH1" s="7"/>
+      <c r="LI1" s="7"/>
+      <c r="LJ1" s="7"/>
+      <c r="LK1" s="7"/>
+      <c r="LL1" s="7"/>
+      <c r="LM1" s="7"/>
+      <c r="LN1" s="7"/>
+      <c r="LO1" s="7"/>
+      <c r="LP1" s="7"/>
+      <c r="LQ1" s="7"/>
+      <c r="LR1" s="7"/>
+      <c r="LS1" s="7"/>
+      <c r="LT1" s="7"/>
+      <c r="LU1" s="7"/>
+      <c r="LV1" s="7"/>
+      <c r="LW1" s="7"/>
+      <c r="LX1" s="7"/>
+      <c r="LY1" s="7"/>
+      <c r="LZ1" s="7"/>
+      <c r="MA1" s="7"/>
+      <c r="MB1" s="7"/>
+      <c r="MC1" s="7"/>
+      <c r="MD1" s="7"/>
+      <c r="ME1" s="7"/>
+      <c r="MF1" s="7"/>
+      <c r="MG1" s="7"/>
+      <c r="MH1" s="7"/>
+      <c r="MI1" s="7"/>
+      <c r="MJ1" s="7"/>
+      <c r="MK1" s="7"/>
+      <c r="ML1" s="7"/>
+      <c r="MM1" s="7"/>
+      <c r="MN1" s="7"/>
+      <c r="MO1" s="7"/>
+      <c r="MP1" s="7"/>
+      <c r="MQ1" s="7"/>
+      <c r="MR1" s="7"/>
+      <c r="MS1" s="7"/>
+      <c r="MT1" s="7"/>
+      <c r="MU1" s="7"/>
+      <c r="MV1" s="7"/>
+      <c r="MW1" s="15"/>
+      <c r="MX1" s="15"/>
+      <c r="MY1" s="15"/>
+      <c r="MZ1" s="15"/>
+      <c r="NA1" s="15"/>
+      <c r="NB1" s="15"/>
+      <c r="NC1" s="15"/>
+      <c r="ND1" s="15"/>
+      <c r="NE1" s="15"/>
+      <c r="NF1" s="15"/>
+      <c r="NG1" s="15"/>
+      <c r="NH1" s="15"/>
+      <c r="NI1" s="15"/>
+      <c r="NJ1" s="15"/>
     </row>
-    <row r="2" spans="1:373" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="13" t="s">
+    <row r="2" spans="1:374" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="74" t="s">
         <v>421</v>
       </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="23"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="21"/>
-      <c r="I2" s="21"/>
-      <c r="J2" s="21"/>
-      <c r="K2" s="21"/>
-      <c r="L2" s="21"/>
-      <c r="M2" s="21"/>
-      <c r="N2" s="21"/>
-      <c r="O2" s="21"/>
-      <c r="P2" s="21"/>
-      <c r="Q2" s="21"/>
-      <c r="R2" s="25"/>
-      <c r="S2" s="25"/>
-      <c r="T2" s="21"/>
-      <c r="U2" s="21"/>
-      <c r="V2" s="21"/>
-      <c r="W2" s="25"/>
-      <c r="X2" s="25"/>
-      <c r="Y2" s="21"/>
-      <c r="Z2" s="21"/>
-      <c r="AA2" s="21"/>
-      <c r="AB2" s="21"/>
-      <c r="AC2" s="21"/>
-      <c r="AD2" s="21"/>
-      <c r="AE2" s="21"/>
-      <c r="AF2" s="21"/>
-      <c r="AG2" s="26"/>
-      <c r="AH2" s="26"/>
-      <c r="AI2" s="26"/>
-      <c r="AJ2" s="26"/>
-      <c r="AK2" s="26"/>
-      <c r="AL2" s="26"/>
-      <c r="AM2" s="21"/>
-      <c r="AN2" s="21"/>
-      <c r="AO2" s="21"/>
-      <c r="AP2" s="21"/>
-      <c r="AQ2" s="21"/>
-      <c r="AR2" s="21"/>
-      <c r="AS2" s="21"/>
-      <c r="AT2" s="21"/>
-      <c r="AU2" s="21"/>
-      <c r="AV2" s="21"/>
-      <c r="AW2" s="21"/>
-      <c r="AX2" s="21"/>
-      <c r="AY2" s="21"/>
-      <c r="AZ2" s="21"/>
-      <c r="BA2" s="21"/>
-      <c r="BB2" s="21"/>
-      <c r="BC2" s="21"/>
-      <c r="BD2" s="21"/>
-      <c r="BE2" s="21"/>
-      <c r="BF2" s="21"/>
-      <c r="BG2" s="21"/>
-      <c r="BH2" s="21"/>
-      <c r="BI2" s="21"/>
-      <c r="BJ2" s="21"/>
-      <c r="BK2" s="21"/>
-      <c r="BL2" s="21"/>
-      <c r="BM2" s="21"/>
-      <c r="BN2" s="21"/>
-      <c r="BO2" s="21"/>
-      <c r="BP2" s="21"/>
-      <c r="BQ2" s="21"/>
-      <c r="BR2" s="21"/>
-      <c r="BS2" s="21"/>
-      <c r="BT2" s="21"/>
-      <c r="BU2" s="21"/>
-      <c r="BV2" s="21"/>
-      <c r="BW2" s="21"/>
-      <c r="BX2" s="21"/>
-      <c r="BY2" s="21"/>
-      <c r="BZ2" s="31"/>
-      <c r="CA2" s="31"/>
-      <c r="CB2" s="28"/>
-      <c r="CC2" s="28"/>
-      <c r="CD2" s="28"/>
-      <c r="CE2" s="28"/>
-      <c r="CF2" s="21"/>
-      <c r="CG2" s="32"/>
-      <c r="CH2" s="32"/>
-      <c r="CI2" s="21"/>
-      <c r="CJ2" s="31"/>
-      <c r="CK2" s="31"/>
-      <c r="CL2" s="28"/>
-      <c r="CM2" s="28"/>
-      <c r="CN2" s="28"/>
-      <c r="CO2" s="28"/>
-      <c r="CP2" s="21"/>
-      <c r="CQ2" s="32"/>
-      <c r="CR2" s="32"/>
-      <c r="CS2" s="21"/>
-      <c r="CT2" s="31"/>
-      <c r="CU2" s="31"/>
-      <c r="CV2" s="28"/>
-      <c r="CW2" s="28"/>
-      <c r="CX2" s="28"/>
-      <c r="CY2" s="28"/>
-      <c r="CZ2" s="21"/>
-      <c r="DA2" s="32"/>
-      <c r="DB2" s="32"/>
-      <c r="DC2" s="21"/>
-      <c r="DD2" s="31"/>
-      <c r="DE2" s="31"/>
-      <c r="DF2" s="28"/>
-      <c r="DG2" s="28"/>
-      <c r="DH2" s="28"/>
-      <c r="DI2" s="28"/>
-      <c r="DJ2" s="21"/>
-      <c r="DK2" s="32"/>
-      <c r="DL2" s="32"/>
-      <c r="DM2" s="21"/>
-      <c r="DN2" s="31"/>
-      <c r="DO2" s="31"/>
-      <c r="DP2" s="28"/>
-      <c r="DQ2" s="28"/>
-      <c r="DR2" s="28"/>
-      <c r="DS2" s="28"/>
-      <c r="DT2" s="21"/>
-      <c r="DU2" s="32"/>
-      <c r="DV2" s="32"/>
-      <c r="DW2" s="21"/>
-      <c r="DX2" s="31"/>
-      <c r="DY2" s="31"/>
-      <c r="DZ2" s="28"/>
-      <c r="EA2" s="28"/>
-      <c r="EB2" s="28"/>
-      <c r="EC2" s="28"/>
-      <c r="ED2" s="21"/>
-      <c r="EE2" s="32"/>
-      <c r="EF2" s="32"/>
-      <c r="EG2" s="21"/>
-      <c r="EH2" s="31"/>
-      <c r="EI2" s="31"/>
-      <c r="EJ2" s="28"/>
-      <c r="EK2" s="28"/>
-      <c r="EL2" s="28"/>
-      <c r="EM2" s="28"/>
-      <c r="EN2" s="21"/>
-      <c r="EO2" s="32"/>
-      <c r="EP2" s="32"/>
-      <c r="EQ2" s="21"/>
-      <c r="ER2" s="31"/>
-      <c r="ES2" s="31"/>
-      <c r="ET2" s="28"/>
-      <c r="EU2" s="28"/>
-      <c r="EV2" s="28"/>
-      <c r="EW2" s="28"/>
-      <c r="EX2" s="21"/>
-      <c r="EY2" s="32"/>
-      <c r="EZ2" s="32"/>
-      <c r="FA2" s="21"/>
-      <c r="FB2" s="21"/>
-      <c r="FC2" s="21"/>
-      <c r="FD2" s="21"/>
-      <c r="FE2" s="21"/>
-      <c r="FF2" s="21"/>
-      <c r="FG2" s="21"/>
-      <c r="FH2" s="21"/>
-      <c r="FI2" s="21"/>
-      <c r="FJ2" s="21"/>
-      <c r="FK2" s="21"/>
-      <c r="FL2" s="21"/>
-      <c r="FM2" s="21"/>
-      <c r="FN2" s="21"/>
-      <c r="FO2" s="21"/>
-      <c r="FP2" s="21"/>
-      <c r="FQ2" s="21"/>
-      <c r="FR2" s="21"/>
-      <c r="FS2" s="21"/>
-      <c r="FT2" s="21"/>
-      <c r="FU2" s="21"/>
-      <c r="FV2" s="21"/>
-      <c r="FW2" s="21"/>
-      <c r="FX2" s="21"/>
-      <c r="FY2" s="21"/>
-      <c r="FZ2" s="21"/>
-      <c r="GA2" s="21"/>
-      <c r="GB2" s="21"/>
-      <c r="GC2" s="21"/>
-      <c r="GD2" s="21"/>
-      <c r="GE2" s="21"/>
-      <c r="GF2" s="21"/>
-      <c r="GG2" s="21"/>
-      <c r="GH2" s="21"/>
-      <c r="GI2" s="21"/>
-      <c r="GJ2" s="21"/>
-      <c r="GK2" s="21"/>
-      <c r="GL2" s="21"/>
-      <c r="GM2" s="21"/>
-      <c r="GN2" s="21"/>
-      <c r="GO2" s="21"/>
-      <c r="GP2" s="21"/>
-      <c r="GQ2" s="21"/>
-      <c r="GR2" s="21"/>
-      <c r="GS2" s="21"/>
-      <c r="GT2" s="21"/>
-      <c r="GU2" s="21"/>
-      <c r="GV2" s="21"/>
-      <c r="GW2" s="21"/>
-      <c r="GX2" s="21"/>
-      <c r="GY2" s="21"/>
-      <c r="GZ2" s="21"/>
-      <c r="HA2" s="21"/>
-      <c r="HB2" s="21"/>
-      <c r="HC2" s="21"/>
-      <c r="HD2" s="21"/>
-      <c r="HE2" s="21"/>
-      <c r="HF2" s="21"/>
-      <c r="HG2" s="21"/>
-      <c r="HH2" s="21"/>
-      <c r="HI2" s="21"/>
-      <c r="HJ2" s="21"/>
-      <c r="HK2" s="21"/>
-      <c r="HL2" s="21"/>
-      <c r="HM2" s="21"/>
-      <c r="HN2" s="21"/>
-      <c r="HO2" s="21"/>
-      <c r="HP2" s="21"/>
-      <c r="HQ2" s="21"/>
-      <c r="HR2" s="21"/>
-      <c r="HS2" s="21"/>
-      <c r="HT2" s="21"/>
-      <c r="HU2" s="21"/>
-      <c r="HV2" s="21"/>
-      <c r="HW2" s="21"/>
-      <c r="HX2" s="21"/>
-      <c r="HY2" s="21"/>
-      <c r="HZ2" s="21"/>
-      <c r="IA2" s="21"/>
-      <c r="IB2" s="21"/>
-      <c r="IC2" s="21"/>
-      <c r="ID2" s="21"/>
-      <c r="IE2" s="21"/>
-      <c r="IF2" s="21"/>
-      <c r="IG2" s="21"/>
-      <c r="IH2" s="21"/>
-      <c r="II2" s="21"/>
-      <c r="IJ2" s="21"/>
-      <c r="IK2" s="21"/>
-      <c r="IL2" s="21"/>
-      <c r="IM2" s="21"/>
-      <c r="IN2" s="21"/>
-      <c r="IO2" s="21"/>
-      <c r="IP2" s="21"/>
-      <c r="IQ2" s="21"/>
-      <c r="IR2" s="21"/>
-      <c r="IS2" s="21"/>
-      <c r="IT2" s="21"/>
-      <c r="IU2" s="21"/>
-      <c r="IV2" s="21"/>
-      <c r="IW2" s="21"/>
-      <c r="IX2" s="21"/>
-      <c r="IY2" s="21"/>
-      <c r="IZ2" s="21"/>
-      <c r="JA2" s="21"/>
-      <c r="JB2" s="21"/>
-      <c r="JC2" s="21"/>
-      <c r="JD2" s="21"/>
-      <c r="JE2" s="21"/>
-      <c r="JF2" s="21"/>
-      <c r="JG2" s="21"/>
-      <c r="JH2" s="21"/>
-      <c r="JI2" s="21"/>
-      <c r="JJ2" s="21"/>
-      <c r="JK2" s="21"/>
-      <c r="JL2" s="21"/>
-      <c r="JM2" s="21"/>
-      <c r="JN2" s="21"/>
-      <c r="JO2" s="21"/>
-      <c r="JP2" s="21"/>
-      <c r="JQ2" s="21"/>
-      <c r="JR2" s="21"/>
-      <c r="JS2" s="21"/>
-      <c r="JT2" s="21"/>
-      <c r="JU2" s="21"/>
-      <c r="JV2" s="21"/>
-      <c r="JW2" s="21"/>
-      <c r="JX2" s="21"/>
-      <c r="JY2" s="21"/>
-      <c r="JZ2" s="21"/>
-      <c r="KA2" s="21"/>
-      <c r="KB2" s="21"/>
-      <c r="KC2" s="21"/>
-      <c r="KD2" s="21"/>
-      <c r="KE2" s="21"/>
-      <c r="KF2" s="21"/>
-      <c r="KG2" s="21"/>
-      <c r="KH2" s="21"/>
-      <c r="KI2" s="21"/>
-      <c r="KJ2" s="21"/>
-      <c r="KK2" s="21"/>
-      <c r="KL2" s="21"/>
-      <c r="KM2" s="21"/>
-      <c r="KN2" s="21"/>
-      <c r="KO2" s="21"/>
-      <c r="KP2" s="21"/>
-      <c r="KQ2" s="21"/>
-      <c r="KR2" s="21"/>
-      <c r="KS2" s="21"/>
-      <c r="KT2" s="21"/>
-      <c r="KU2" s="21"/>
-      <c r="KV2" s="21"/>
-      <c r="KW2" s="21"/>
-      <c r="KX2" s="21"/>
-      <c r="KY2" s="21"/>
-      <c r="KZ2" s="21"/>
-      <c r="LA2" s="21"/>
-      <c r="LB2" s="21"/>
-      <c r="LC2" s="21"/>
-      <c r="LD2" s="21"/>
-      <c r="LE2" s="21"/>
-      <c r="LF2" s="21"/>
-      <c r="LG2" s="21"/>
-      <c r="LH2" s="21"/>
-      <c r="LI2" s="21"/>
-      <c r="LJ2" s="21"/>
-      <c r="LK2" s="21"/>
-      <c r="LL2" s="21"/>
-      <c r="LM2" s="21"/>
-      <c r="LN2" s="21"/>
-      <c r="LO2" s="21"/>
-      <c r="LP2" s="21"/>
-      <c r="LQ2" s="21"/>
-      <c r="LR2" s="21"/>
-      <c r="LS2" s="21"/>
-      <c r="LT2" s="21"/>
-      <c r="LU2" s="21"/>
-      <c r="LV2" s="21"/>
-      <c r="LW2" s="21"/>
-      <c r="LX2" s="21"/>
-      <c r="LY2" s="21"/>
-      <c r="LZ2" s="21"/>
-      <c r="MA2" s="21"/>
-      <c r="MB2" s="21"/>
-      <c r="MC2" s="21"/>
-      <c r="MD2" s="21"/>
-      <c r="ME2" s="21"/>
-      <c r="MF2" s="21"/>
-      <c r="MG2" s="21"/>
-      <c r="MH2" s="21"/>
-      <c r="MI2" s="21"/>
-      <c r="MJ2" s="21"/>
-      <c r="MK2" s="21"/>
-      <c r="ML2" s="21"/>
-      <c r="MM2" s="21"/>
-      <c r="MN2" s="21"/>
-      <c r="MO2" s="21"/>
-      <c r="MP2" s="21"/>
-      <c r="MQ2" s="21"/>
-      <c r="MR2" s="21"/>
-      <c r="MS2" s="21"/>
-      <c r="MT2" s="21"/>
-      <c r="MU2" s="21"/>
-      <c r="MV2" s="21"/>
-      <c r="MW2" s="29"/>
-      <c r="MX2" s="29"/>
-      <c r="MY2" s="29"/>
-      <c r="MZ2" s="29"/>
-      <c r="NA2" s="29"/>
-      <c r="NB2" s="29"/>
-      <c r="NC2" s="29"/>
-      <c r="ND2" s="29"/>
-      <c r="NE2" s="29"/>
-      <c r="NF2" s="29"/>
-      <c r="NG2" s="29"/>
-      <c r="NH2" s="29"/>
-      <c r="NI2" s="29"/>
+      <c r="B2" s="74"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="7"/>
+      <c r="M2" s="7"/>
+      <c r="N2" s="7"/>
+      <c r="O2" s="7"/>
+      <c r="P2" s="7"/>
+      <c r="Q2" s="7"/>
+      <c r="R2" s="11"/>
+      <c r="S2" s="11"/>
+      <c r="T2" s="7"/>
+      <c r="U2" s="7"/>
+      <c r="V2" s="7"/>
+      <c r="W2" s="11"/>
+      <c r="X2" s="11"/>
+      <c r="Y2" s="7"/>
+      <c r="Z2" s="7"/>
+      <c r="AA2" s="7"/>
+      <c r="AB2" s="7"/>
+      <c r="AC2" s="7"/>
+      <c r="AD2" s="7"/>
+      <c r="AE2" s="7"/>
+      <c r="AF2" s="7"/>
+      <c r="AG2" s="12"/>
+      <c r="AH2" s="12"/>
+      <c r="AI2" s="12"/>
+      <c r="AJ2" s="12"/>
+      <c r="AK2" s="12"/>
+      <c r="AL2" s="12"/>
+      <c r="AM2" s="7"/>
+      <c r="AN2" s="7"/>
+      <c r="AO2" s="7"/>
+      <c r="AP2" s="7"/>
+      <c r="AQ2" s="7"/>
+      <c r="AR2" s="7"/>
+      <c r="AS2" s="7"/>
+      <c r="AT2" s="7"/>
+      <c r="AU2" s="7"/>
+      <c r="AV2" s="7"/>
+      <c r="AW2" s="7"/>
+      <c r="AX2" s="7"/>
+      <c r="AY2" s="7"/>
+      <c r="AZ2" s="7"/>
+      <c r="BA2" s="7"/>
+      <c r="BB2" s="7"/>
+      <c r="BC2" s="7"/>
+      <c r="BD2" s="7"/>
+      <c r="BE2" s="7"/>
+      <c r="BF2" s="7"/>
+      <c r="BG2" s="7"/>
+      <c r="BH2" s="7"/>
+      <c r="BI2" s="7"/>
+      <c r="BJ2" s="7"/>
+      <c r="BK2" s="7"/>
+      <c r="BL2" s="7"/>
+      <c r="BM2" s="7"/>
+      <c r="BN2" s="7"/>
+      <c r="BO2" s="7"/>
+      <c r="BP2" s="7"/>
+      <c r="BQ2" s="7"/>
+      <c r="BR2" s="7"/>
+      <c r="BS2" s="7"/>
+      <c r="BT2" s="7"/>
+      <c r="BU2" s="7"/>
+      <c r="BV2" s="7"/>
+      <c r="BW2" s="7"/>
+      <c r="BX2" s="7"/>
+      <c r="BY2" s="7"/>
+      <c r="BZ2" s="17"/>
+      <c r="CA2" s="17"/>
+      <c r="CB2" s="14"/>
+      <c r="CC2" s="14"/>
+      <c r="CD2" s="14"/>
+      <c r="CE2" s="14"/>
+      <c r="CF2" s="7"/>
+      <c r="CG2" s="18"/>
+      <c r="CH2" s="18"/>
+      <c r="CI2" s="7"/>
+      <c r="CJ2" s="17"/>
+      <c r="CK2" s="17"/>
+      <c r="CL2" s="14"/>
+      <c r="CM2" s="14"/>
+      <c r="CN2" s="14"/>
+      <c r="CO2" s="14"/>
+      <c r="CP2" s="7"/>
+      <c r="CQ2" s="18"/>
+      <c r="CR2" s="18"/>
+      <c r="CS2" s="7"/>
+      <c r="CT2" s="17"/>
+      <c r="CU2" s="17"/>
+      <c r="CV2" s="14"/>
+      <c r="CW2" s="14"/>
+      <c r="CX2" s="14"/>
+      <c r="CY2" s="14"/>
+      <c r="CZ2" s="7"/>
+      <c r="DA2" s="18"/>
+      <c r="DB2" s="18"/>
+      <c r="DC2" s="7"/>
+      <c r="DD2" s="17"/>
+      <c r="DE2" s="17"/>
+      <c r="DF2" s="14"/>
+      <c r="DG2" s="14"/>
+      <c r="DH2" s="14"/>
+      <c r="DI2" s="14"/>
+      <c r="DJ2" s="7"/>
+      <c r="DK2" s="18"/>
+      <c r="DL2" s="18"/>
+      <c r="DM2" s="7"/>
+      <c r="DN2" s="17"/>
+      <c r="DO2" s="17"/>
+      <c r="DP2" s="14"/>
+      <c r="DQ2" s="14"/>
+      <c r="DR2" s="14"/>
+      <c r="DS2" s="14"/>
+      <c r="DT2" s="7"/>
+      <c r="DU2" s="18"/>
+      <c r="DV2" s="18"/>
+      <c r="DW2" s="7"/>
+      <c r="DX2" s="17"/>
+      <c r="DY2" s="17"/>
+      <c r="DZ2" s="14"/>
+      <c r="EA2" s="14"/>
+      <c r="EB2" s="14"/>
+      <c r="EC2" s="14"/>
+      <c r="ED2" s="7"/>
+      <c r="EE2" s="18"/>
+      <c r="EF2" s="18"/>
+      <c r="EG2" s="7"/>
+      <c r="EH2" s="17"/>
+      <c r="EI2" s="17"/>
+      <c r="EJ2" s="14"/>
+      <c r="EK2" s="14"/>
+      <c r="EL2" s="14"/>
+      <c r="EM2" s="14"/>
+      <c r="EN2" s="7"/>
+      <c r="EO2" s="18"/>
+      <c r="EP2" s="18"/>
+      <c r="EQ2" s="7"/>
+      <c r="ER2" s="17"/>
+      <c r="ES2" s="17"/>
+      <c r="ET2" s="14"/>
+      <c r="EU2" s="14"/>
+      <c r="EV2" s="14"/>
+      <c r="EW2" s="14"/>
+      <c r="EX2" s="7"/>
+      <c r="EY2" s="18"/>
+      <c r="EZ2" s="18"/>
+      <c r="FA2" s="7"/>
+      <c r="FB2" s="7"/>
+      <c r="FC2" s="7"/>
+      <c r="FD2" s="7"/>
+      <c r="FE2" s="7"/>
+      <c r="FF2" s="7"/>
+      <c r="FG2" s="7"/>
+      <c r="FH2" s="7"/>
+      <c r="FI2" s="7"/>
+      <c r="FJ2" s="7"/>
+      <c r="FK2" s="7"/>
+      <c r="FL2" s="7"/>
+      <c r="FM2" s="7"/>
+      <c r="FN2" s="7"/>
+      <c r="FO2" s="7"/>
+      <c r="FP2" s="7"/>
+      <c r="FQ2" s="7"/>
+      <c r="FR2" s="7"/>
+      <c r="FS2" s="7"/>
+      <c r="FT2" s="7"/>
+      <c r="FU2" s="7"/>
+      <c r="FV2" s="7"/>
+      <c r="FW2" s="7"/>
+      <c r="FX2" s="7"/>
+      <c r="FY2" s="7"/>
+      <c r="FZ2" s="7"/>
+      <c r="GA2" s="7"/>
+      <c r="GB2" s="7"/>
+      <c r="GC2" s="7"/>
+      <c r="GD2" s="7"/>
+      <c r="GE2" s="7"/>
+      <c r="GF2" s="7"/>
+      <c r="GG2" s="7"/>
+      <c r="GH2" s="7"/>
+      <c r="GI2" s="7"/>
+      <c r="GJ2" s="7"/>
+      <c r="GK2" s="7"/>
+      <c r="GL2" s="7"/>
+      <c r="GM2" s="7"/>
+      <c r="GN2" s="7"/>
+      <c r="GO2" s="7"/>
+      <c r="GP2" s="7"/>
+      <c r="GQ2" s="7"/>
+      <c r="GR2" s="7"/>
+      <c r="GS2" s="7"/>
+      <c r="GT2" s="7"/>
+      <c r="GU2" s="7"/>
+      <c r="GV2" s="7"/>
+      <c r="GW2" s="7"/>
+      <c r="GX2" s="7"/>
+      <c r="GY2" s="7"/>
+      <c r="GZ2" s="7"/>
+      <c r="HA2" s="7"/>
+      <c r="HB2" s="7"/>
+      <c r="HC2" s="7"/>
+      <c r="HD2" s="7"/>
+      <c r="HE2" s="7"/>
+      <c r="HF2" s="7"/>
+      <c r="HG2" s="7"/>
+      <c r="HH2" s="7"/>
+      <c r="HI2" s="7"/>
+      <c r="HJ2" s="7"/>
+      <c r="HK2" s="7"/>
+      <c r="HL2" s="7"/>
+      <c r="HM2" s="7"/>
+      <c r="HN2" s="7"/>
+      <c r="HO2" s="7"/>
+      <c r="HP2" s="7"/>
+      <c r="HQ2" s="7"/>
+      <c r="HR2" s="7"/>
+      <c r="HS2" s="7"/>
+      <c r="HT2" s="7"/>
+      <c r="HU2" s="7"/>
+      <c r="HV2" s="7"/>
+      <c r="HW2" s="7"/>
+      <c r="HX2" s="7"/>
+      <c r="HY2" s="7"/>
+      <c r="HZ2" s="7"/>
+      <c r="IA2" s="7"/>
+      <c r="IB2" s="7"/>
+      <c r="IC2" s="7"/>
+      <c r="ID2" s="7"/>
+      <c r="IE2" s="7"/>
+      <c r="IF2" s="7"/>
+      <c r="IG2" s="7"/>
+      <c r="IH2" s="7"/>
+      <c r="II2" s="7"/>
+      <c r="IJ2" s="7"/>
+      <c r="IK2" s="7"/>
+      <c r="IL2" s="7"/>
+      <c r="IM2" s="7"/>
+      <c r="IN2" s="7"/>
+      <c r="IO2" s="7"/>
+      <c r="IP2" s="7"/>
+      <c r="IQ2" s="7"/>
+      <c r="IR2" s="7"/>
+      <c r="IS2" s="7"/>
+      <c r="IT2" s="7"/>
+      <c r="IU2" s="7"/>
+      <c r="IV2" s="7"/>
+      <c r="IW2" s="7"/>
+      <c r="IX2" s="7"/>
+      <c r="IY2" s="7"/>
+      <c r="IZ2" s="7"/>
+      <c r="JA2" s="7"/>
+      <c r="JB2" s="7"/>
+      <c r="JC2" s="7"/>
+      <c r="JD2" s="7"/>
+      <c r="JE2" s="7"/>
+      <c r="JF2" s="7"/>
+      <c r="JG2" s="7"/>
+      <c r="JH2" s="7"/>
+      <c r="JI2" s="7"/>
+      <c r="JJ2" s="7"/>
+      <c r="JK2" s="7"/>
+      <c r="JL2" s="7"/>
+      <c r="JM2" s="7"/>
+      <c r="JN2" s="7"/>
+      <c r="JO2" s="7"/>
+      <c r="JP2" s="7"/>
+      <c r="JQ2" s="7"/>
+      <c r="JR2" s="7"/>
+      <c r="JS2" s="7"/>
+      <c r="JT2" s="7"/>
+      <c r="JU2" s="7"/>
+      <c r="JV2" s="7"/>
+      <c r="JW2" s="7"/>
+      <c r="JX2" s="7"/>
+      <c r="JY2" s="7"/>
+      <c r="JZ2" s="7"/>
+      <c r="KA2" s="7"/>
+      <c r="KB2" s="7"/>
+      <c r="KC2" s="7"/>
+      <c r="KD2" s="7"/>
+      <c r="KE2" s="7"/>
+      <c r="KF2" s="7"/>
+      <c r="KG2" s="7"/>
+      <c r="KH2" s="7"/>
+      <c r="KI2" s="7"/>
+      <c r="KJ2" s="7"/>
+      <c r="KK2" s="7"/>
+      <c r="KL2" s="7"/>
+      <c r="KM2" s="7"/>
+      <c r="KN2" s="7"/>
+      <c r="KO2" s="7"/>
+      <c r="KP2" s="7"/>
+      <c r="KQ2" s="7"/>
+      <c r="KR2" s="7"/>
+      <c r="KS2" s="7"/>
+      <c r="KT2" s="7"/>
+      <c r="KU2" s="7"/>
+      <c r="KV2" s="7"/>
+      <c r="KW2" s="7"/>
+      <c r="KX2" s="7"/>
+      <c r="KY2" s="7"/>
+      <c r="KZ2" s="7"/>
+      <c r="LA2" s="7"/>
+      <c r="LB2" s="7"/>
+      <c r="LC2" s="7"/>
+      <c r="LD2" s="7"/>
+      <c r="LE2" s="7"/>
+      <c r="LF2" s="7"/>
+      <c r="LG2" s="7"/>
+      <c r="LH2" s="7"/>
+      <c r="LI2" s="7"/>
+      <c r="LJ2" s="7"/>
+      <c r="LK2" s="7"/>
+      <c r="LL2" s="7"/>
+      <c r="LM2" s="7"/>
+      <c r="LN2" s="7"/>
+      <c r="LO2" s="7"/>
+      <c r="LP2" s="7"/>
+      <c r="LQ2" s="7"/>
+      <c r="LR2" s="7"/>
+      <c r="LS2" s="7"/>
+      <c r="LT2" s="7"/>
+      <c r="LU2" s="7"/>
+      <c r="LV2" s="7"/>
+      <c r="LW2" s="7"/>
+      <c r="LX2" s="7"/>
+      <c r="LY2" s="7"/>
+      <c r="LZ2" s="7"/>
+      <c r="MA2" s="7"/>
+      <c r="MB2" s="7"/>
+      <c r="MC2" s="7"/>
+      <c r="MD2" s="7"/>
+      <c r="ME2" s="7"/>
+      <c r="MF2" s="7"/>
+      <c r="MG2" s="7"/>
+      <c r="MH2" s="7"/>
+      <c r="MI2" s="7"/>
+      <c r="MJ2" s="7"/>
+      <c r="MK2" s="7"/>
+      <c r="ML2" s="7"/>
+      <c r="MM2" s="7"/>
+      <c r="MN2" s="7"/>
+      <c r="MO2" s="7"/>
+      <c r="MP2" s="7"/>
+      <c r="MQ2" s="7"/>
+      <c r="MR2" s="7"/>
+      <c r="MS2" s="7"/>
+      <c r="MT2" s="7"/>
+      <c r="MU2" s="7"/>
+      <c r="MV2" s="7"/>
+      <c r="MW2" s="15"/>
+      <c r="MX2" s="15"/>
+      <c r="MY2" s="15"/>
+      <c r="MZ2" s="15"/>
+      <c r="NA2" s="15"/>
+      <c r="NB2" s="15"/>
+      <c r="NC2" s="15"/>
+      <c r="ND2" s="15"/>
+      <c r="NE2" s="15"/>
+      <c r="NF2" s="15"/>
+      <c r="NG2" s="15"/>
+      <c r="NH2" s="15"/>
+      <c r="NI2" s="15"/>
+      <c r="NJ2" s="15"/>
     </row>
-    <row r="3" spans="1:373" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="33"/>
-      <c r="B3" s="34"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
-      <c r="H3" s="34"/>
-      <c r="I3" s="34"/>
-      <c r="J3" s="34"/>
-      <c r="K3" s="34"/>
-      <c r="L3" s="34"/>
-      <c r="M3" s="34"/>
-      <c r="N3" s="34"/>
-      <c r="O3" s="34"/>
-      <c r="P3" s="34"/>
-      <c r="Q3" s="34"/>
-      <c r="R3" s="35"/>
-      <c r="S3" s="35"/>
-      <c r="T3" s="34"/>
-      <c r="U3" s="34"/>
-      <c r="V3" s="34"/>
-      <c r="W3" s="35"/>
-      <c r="X3" s="35"/>
-      <c r="Y3" s="34"/>
-      <c r="Z3" s="34"/>
-      <c r="AA3" s="34"/>
-      <c r="AB3" s="34"/>
-      <c r="AC3" s="34"/>
-      <c r="AD3" s="34"/>
-      <c r="AE3" s="34"/>
-      <c r="AF3" s="34"/>
-      <c r="AG3" s="36"/>
-      <c r="AH3" s="37"/>
-      <c r="AI3" s="37"/>
-      <c r="AJ3" s="37"/>
-      <c r="AK3" s="37"/>
-      <c r="AL3" s="37"/>
-      <c r="AM3" s="38"/>
-      <c r="AN3" s="38"/>
-      <c r="AO3" s="38"/>
-      <c r="AP3" s="38"/>
-      <c r="AQ3" s="38"/>
-      <c r="AR3" s="38"/>
-      <c r="AS3" s="38"/>
-      <c r="AT3" s="38"/>
-      <c r="AU3" s="38"/>
-      <c r="AV3" s="38"/>
-      <c r="AW3" s="38"/>
-      <c r="AX3" s="38"/>
-      <c r="AY3" s="38"/>
-      <c r="AZ3" s="38"/>
-      <c r="BA3" s="38"/>
-      <c r="BB3" s="38"/>
-      <c r="BC3" s="38"/>
-      <c r="BD3" s="38"/>
-      <c r="BE3" s="38"/>
-      <c r="BF3" s="38"/>
-      <c r="BG3" s="38"/>
-      <c r="BH3" s="38"/>
-      <c r="BI3" s="38"/>
-      <c r="BJ3" s="38"/>
-      <c r="BK3" s="38"/>
-      <c r="BL3" s="38"/>
-      <c r="BM3" s="38"/>
-      <c r="BN3" s="38"/>
-      <c r="BO3" s="38"/>
-      <c r="BP3" s="38"/>
-      <c r="BQ3" s="38"/>
-      <c r="BR3" s="39"/>
-      <c r="BS3" s="39"/>
-      <c r="BT3" s="39"/>
-      <c r="BU3" s="39"/>
-      <c r="BV3" s="39"/>
-      <c r="BW3" s="39"/>
-      <c r="BX3" s="39"/>
-      <c r="BY3" s="39"/>
-      <c r="BZ3" s="39"/>
-      <c r="CA3" s="39"/>
-      <c r="CB3" s="39"/>
-      <c r="CC3" s="39"/>
-      <c r="CD3" s="39"/>
-      <c r="CE3" s="39"/>
-      <c r="CF3" s="39"/>
-      <c r="CG3" s="39"/>
-      <c r="CH3" s="39"/>
-      <c r="CI3" s="39"/>
-      <c r="CJ3" s="39"/>
-      <c r="CK3" s="39"/>
-      <c r="CL3" s="39"/>
-      <c r="CM3" s="39"/>
-      <c r="CN3" s="39"/>
-      <c r="CO3" s="39"/>
-      <c r="CP3" s="39"/>
-      <c r="CQ3" s="39"/>
-      <c r="CR3" s="39"/>
-      <c r="CS3" s="39"/>
-      <c r="CT3" s="39"/>
-      <c r="CU3" s="39"/>
-      <c r="CV3" s="39"/>
-      <c r="CW3" s="39"/>
-      <c r="CX3" s="39"/>
-      <c r="CY3" s="39"/>
-      <c r="CZ3" s="39"/>
-      <c r="DA3" s="39"/>
-      <c r="DB3" s="39"/>
-      <c r="DC3" s="39"/>
-      <c r="DD3" s="39"/>
-      <c r="DE3" s="39"/>
-      <c r="DF3" s="39"/>
-      <c r="DG3" s="39"/>
-      <c r="DH3" s="39"/>
-      <c r="DI3" s="39"/>
-      <c r="DJ3" s="39"/>
-      <c r="DK3" s="39"/>
-      <c r="DL3" s="39"/>
-      <c r="DM3" s="39"/>
-      <c r="DN3" s="39"/>
-      <c r="DO3" s="39"/>
-      <c r="DP3" s="39"/>
-      <c r="DQ3" s="39"/>
-      <c r="DR3" s="39"/>
-      <c r="DS3" s="39"/>
-      <c r="DT3" s="39"/>
-      <c r="DU3" s="39"/>
-      <c r="DV3" s="39"/>
-      <c r="DW3" s="39"/>
-      <c r="DX3" s="39"/>
-      <c r="DY3" s="39"/>
-      <c r="DZ3" s="39"/>
-      <c r="EA3" s="39"/>
-      <c r="EB3" s="39"/>
-      <c r="EC3" s="39"/>
-      <c r="ED3" s="39"/>
-      <c r="EE3" s="39"/>
-      <c r="EF3" s="39"/>
-      <c r="EG3" s="39"/>
-      <c r="EH3" s="39"/>
-      <c r="EI3" s="39"/>
-      <c r="EJ3" s="39"/>
-      <c r="EK3" s="39"/>
-      <c r="EL3" s="39"/>
-      <c r="EM3" s="39"/>
-      <c r="EN3" s="39"/>
-      <c r="EO3" s="39"/>
-      <c r="EP3" s="39"/>
-      <c r="EQ3" s="39"/>
-      <c r="ER3" s="39"/>
-      <c r="ES3" s="39"/>
-      <c r="ET3" s="39"/>
-      <c r="EU3" s="39"/>
-      <c r="EV3" s="39"/>
-      <c r="EW3" s="39"/>
-      <c r="EX3" s="39"/>
-      <c r="EY3" s="39"/>
-      <c r="EZ3" s="39"/>
-      <c r="FA3" s="39"/>
-      <c r="FB3" s="39"/>
-      <c r="FC3" s="39"/>
-      <c r="FD3" s="39"/>
-      <c r="FE3" s="39"/>
-      <c r="FF3" s="39"/>
-      <c r="FG3" s="39"/>
-      <c r="FH3" s="39"/>
-      <c r="FI3" s="39"/>
-      <c r="FJ3" s="39"/>
-      <c r="FK3" s="39"/>
-      <c r="FL3" s="39"/>
-      <c r="FM3" s="39"/>
-      <c r="FN3" s="39"/>
-      <c r="FO3" s="39"/>
-      <c r="FP3" s="39"/>
-      <c r="FQ3" s="39"/>
-      <c r="FR3" s="39"/>
-      <c r="FS3" s="39"/>
-      <c r="FT3" s="39"/>
-      <c r="FU3" s="39"/>
-      <c r="FV3" s="39"/>
-      <c r="FW3" s="39"/>
-      <c r="FX3" s="39"/>
-      <c r="FY3" s="39"/>
-      <c r="FZ3" s="39"/>
-      <c r="GA3" s="39"/>
-      <c r="GB3" s="39"/>
-      <c r="GC3" s="39"/>
-      <c r="GD3" s="39"/>
-      <c r="GE3" s="39"/>
-      <c r="GF3" s="39"/>
-      <c r="GG3" s="39"/>
-      <c r="GH3" s="39"/>
-      <c r="GI3" s="39"/>
-      <c r="GJ3" s="39"/>
-      <c r="GK3" s="39"/>
-      <c r="GL3" s="39"/>
-      <c r="GM3" s="39"/>
-      <c r="GN3" s="39"/>
-      <c r="GO3" s="39"/>
-      <c r="GP3" s="39"/>
-      <c r="GQ3" s="39"/>
-      <c r="GR3" s="39"/>
-      <c r="GS3" s="39"/>
-      <c r="GT3" s="39"/>
-      <c r="GU3" s="39"/>
-      <c r="GV3" s="39"/>
-      <c r="GW3" s="39"/>
-      <c r="GX3" s="39"/>
-      <c r="GY3" s="39"/>
-      <c r="GZ3" s="39"/>
-      <c r="HA3" s="39"/>
-      <c r="HB3" s="39"/>
-      <c r="HC3" s="39"/>
-      <c r="HD3" s="39"/>
-      <c r="HE3" s="39"/>
-      <c r="HF3" s="39"/>
-      <c r="HG3" s="39"/>
-      <c r="HH3" s="39"/>
-      <c r="HI3" s="39"/>
-      <c r="HJ3" s="39"/>
-      <c r="HK3" s="39"/>
-      <c r="HL3" s="39"/>
-      <c r="HM3" s="39"/>
-      <c r="HN3" s="39"/>
-      <c r="HO3" s="39"/>
-      <c r="HP3" s="39"/>
-      <c r="HQ3" s="39"/>
-      <c r="HR3" s="39"/>
-      <c r="HS3" s="39"/>
-      <c r="HT3" s="39"/>
-      <c r="HU3" s="39"/>
-      <c r="HV3" s="39"/>
-      <c r="HW3" s="39"/>
-      <c r="HX3" s="39"/>
-      <c r="HY3" s="39"/>
-      <c r="HZ3" s="39"/>
-      <c r="IA3" s="39"/>
-      <c r="IB3" s="39"/>
-      <c r="IC3" s="39"/>
-      <c r="ID3" s="39"/>
-      <c r="IE3" s="39"/>
-      <c r="IF3" s="39"/>
-      <c r="IG3" s="39"/>
-      <c r="IH3" s="39"/>
-      <c r="II3" s="39"/>
-      <c r="IJ3" s="39"/>
-      <c r="IK3" s="39"/>
-      <c r="IL3" s="39"/>
-      <c r="IM3" s="39"/>
-      <c r="IN3" s="39"/>
-      <c r="IO3" s="39"/>
-      <c r="IP3" s="39"/>
-      <c r="IQ3" s="39"/>
-      <c r="IR3" s="39"/>
-      <c r="IS3" s="39"/>
-      <c r="IT3" s="39"/>
-      <c r="IU3" s="39"/>
-      <c r="IV3" s="39"/>
-      <c r="IW3" s="39"/>
-      <c r="IX3" s="39"/>
-      <c r="IY3" s="39"/>
-      <c r="IZ3" s="39"/>
-      <c r="JA3" s="39"/>
-      <c r="JB3" s="39"/>
-      <c r="JC3" s="39"/>
-      <c r="JD3" s="39"/>
-      <c r="JE3" s="39"/>
-      <c r="JF3" s="39"/>
-      <c r="JG3" s="39"/>
-      <c r="JH3" s="39"/>
-      <c r="JI3" s="39"/>
-      <c r="JJ3" s="39"/>
-      <c r="JK3" s="39"/>
-      <c r="JL3" s="39"/>
-      <c r="JM3" s="39"/>
-      <c r="JN3" s="39"/>
-      <c r="JO3" s="39"/>
-      <c r="JP3" s="39"/>
-      <c r="JQ3" s="39"/>
-      <c r="JR3" s="39"/>
-      <c r="JS3" s="39"/>
-      <c r="JT3" s="39"/>
-      <c r="JU3" s="39"/>
-      <c r="JV3" s="39"/>
-      <c r="JW3" s="39"/>
-      <c r="JX3" s="39"/>
-      <c r="JY3" s="39"/>
-      <c r="JZ3" s="39"/>
-      <c r="KA3" s="39"/>
-      <c r="KB3" s="39"/>
-      <c r="KC3" s="39"/>
-      <c r="KD3" s="39"/>
-      <c r="KE3" s="39"/>
-      <c r="KF3" s="39"/>
-      <c r="KG3" s="39"/>
-      <c r="KH3" s="39"/>
-      <c r="KI3" s="39"/>
-      <c r="KJ3" s="39"/>
-      <c r="KK3" s="39"/>
-      <c r="KL3" s="39"/>
-      <c r="KM3" s="39"/>
-      <c r="KN3" s="39"/>
-      <c r="KO3" s="39"/>
-      <c r="KP3" s="39"/>
-      <c r="KQ3" s="39"/>
-      <c r="KR3" s="39"/>
-      <c r="KS3" s="39"/>
-      <c r="KT3" s="39"/>
-      <c r="KU3" s="39"/>
-      <c r="KV3" s="39"/>
-      <c r="KW3" s="39"/>
-      <c r="KX3" s="39"/>
-      <c r="KY3" s="39"/>
-      <c r="KZ3" s="39"/>
-      <c r="LA3" s="39"/>
-      <c r="LB3" s="39"/>
-      <c r="LC3" s="39"/>
-      <c r="LD3" s="39"/>
-      <c r="LE3" s="39"/>
-      <c r="LF3" s="39"/>
-      <c r="LG3" s="39"/>
-      <c r="LH3" s="39"/>
-      <c r="LI3" s="39"/>
-      <c r="LJ3" s="39"/>
-      <c r="LK3" s="39"/>
-      <c r="LL3" s="39"/>
-      <c r="LM3" s="39"/>
-      <c r="LN3" s="39"/>
-      <c r="LO3" s="39"/>
-      <c r="LP3" s="39"/>
-      <c r="LQ3" s="39"/>
-      <c r="LR3" s="39"/>
-      <c r="LS3" s="39"/>
-      <c r="LT3" s="39"/>
-      <c r="LU3" s="39"/>
-      <c r="LV3" s="39"/>
-      <c r="LW3" s="39"/>
-      <c r="LX3" s="39"/>
-      <c r="LY3" s="39"/>
-      <c r="LZ3" s="39"/>
-      <c r="MA3" s="39"/>
-      <c r="MB3" s="39"/>
-      <c r="MC3" s="39"/>
-      <c r="MD3" s="39"/>
-      <c r="ME3" s="39"/>
-      <c r="MF3" s="39"/>
-      <c r="MG3" s="39"/>
-      <c r="MH3" s="39"/>
-      <c r="MI3" s="39"/>
-      <c r="MJ3" s="39"/>
-      <c r="MK3" s="39"/>
-      <c r="ML3" s="39"/>
-      <c r="MM3" s="39"/>
-      <c r="MN3" s="39"/>
-      <c r="MO3" s="39"/>
-      <c r="MP3" s="39"/>
-      <c r="MQ3" s="39"/>
-      <c r="MR3" s="39"/>
-      <c r="MS3" s="39"/>
-      <c r="MT3" s="39"/>
-      <c r="MU3" s="39"/>
-      <c r="MV3" s="39"/>
-      <c r="MW3" s="29"/>
-      <c r="MX3" s="29"/>
-      <c r="MY3" s="29"/>
-      <c r="MZ3" s="29"/>
-      <c r="NA3" s="29"/>
-      <c r="NB3" s="29"/>
-      <c r="NC3" s="29"/>
-      <c r="ND3" s="29"/>
-      <c r="NE3" s="29"/>
-      <c r="NF3" s="29"/>
-      <c r="NG3" s="29"/>
-      <c r="NH3" s="29"/>
-      <c r="NI3" s="29"/>
+    <row r="3" spans="1:374" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="19"/>
+      <c r="B3" s="20"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="20"/>
+      <c r="G3" s="20"/>
+      <c r="H3" s="20"/>
+      <c r="I3" s="20"/>
+      <c r="J3" s="20"/>
+      <c r="K3" s="20"/>
+      <c r="L3" s="20"/>
+      <c r="M3" s="20"/>
+      <c r="N3" s="20"/>
+      <c r="O3" s="20"/>
+      <c r="P3" s="20"/>
+      <c r="Q3" s="20"/>
+      <c r="R3" s="21"/>
+      <c r="S3" s="21"/>
+      <c r="T3" s="20"/>
+      <c r="U3" s="20"/>
+      <c r="V3" s="20"/>
+      <c r="W3" s="21"/>
+      <c r="X3" s="21"/>
+      <c r="Y3" s="20"/>
+      <c r="Z3" s="20"/>
+      <c r="AA3" s="20"/>
+      <c r="AB3" s="20"/>
+      <c r="AC3" s="20"/>
+      <c r="AD3" s="20"/>
+      <c r="AE3" s="20"/>
+      <c r="AF3" s="20"/>
+      <c r="AG3" s="22"/>
+      <c r="AH3" s="23"/>
+      <c r="AI3" s="23"/>
+      <c r="AJ3" s="23"/>
+      <c r="AK3" s="23"/>
+      <c r="AL3" s="23"/>
+      <c r="AM3" s="24"/>
+      <c r="AN3" s="24"/>
+      <c r="AO3" s="24"/>
+      <c r="AP3" s="24"/>
+      <c r="AQ3" s="24"/>
+      <c r="AR3" s="24"/>
+      <c r="AS3" s="24"/>
+      <c r="AT3" s="24"/>
+      <c r="AU3" s="24"/>
+      <c r="AV3" s="24"/>
+      <c r="AW3" s="24"/>
+      <c r="AX3" s="24"/>
+      <c r="AY3" s="24"/>
+      <c r="AZ3" s="24"/>
+      <c r="BA3" s="24"/>
+      <c r="BB3" s="24"/>
+      <c r="BC3" s="24"/>
+      <c r="BD3" s="24"/>
+      <c r="BE3" s="24"/>
+      <c r="BF3" s="24"/>
+      <c r="BG3" s="24"/>
+      <c r="BH3" s="24"/>
+      <c r="BI3" s="24"/>
+      <c r="BJ3" s="24"/>
+      <c r="BK3" s="24"/>
+      <c r="BL3" s="24"/>
+      <c r="BM3" s="24"/>
+      <c r="BN3" s="24"/>
+      <c r="BO3" s="24"/>
+      <c r="BP3" s="24"/>
+      <c r="BQ3" s="24"/>
+      <c r="BR3" s="25"/>
+      <c r="BS3" s="25"/>
+      <c r="BT3" s="25"/>
+      <c r="BU3" s="25"/>
+      <c r="BV3" s="25"/>
+      <c r="BW3" s="25"/>
+      <c r="BX3" s="25"/>
+      <c r="BY3" s="25"/>
+      <c r="BZ3" s="25"/>
+      <c r="CA3" s="25"/>
+      <c r="CB3" s="25"/>
+      <c r="CC3" s="25"/>
+      <c r="CD3" s="25"/>
+      <c r="CE3" s="25"/>
+      <c r="CF3" s="25"/>
+      <c r="CG3" s="25"/>
+      <c r="CH3" s="25"/>
+      <c r="CI3" s="25"/>
+      <c r="CJ3" s="25"/>
+      <c r="CK3" s="25"/>
+      <c r="CL3" s="25"/>
+      <c r="CM3" s="25"/>
+      <c r="CN3" s="25"/>
+      <c r="CO3" s="25"/>
+      <c r="CP3" s="25"/>
+      <c r="CQ3" s="25"/>
+      <c r="CR3" s="25"/>
+      <c r="CS3" s="25"/>
+      <c r="CT3" s="25"/>
+      <c r="CU3" s="25"/>
+      <c r="CV3" s="25"/>
+      <c r="CW3" s="25"/>
+      <c r="CX3" s="25"/>
+      <c r="CY3" s="25"/>
+      <c r="CZ3" s="25"/>
+      <c r="DA3" s="25"/>
+      <c r="DB3" s="25"/>
+      <c r="DC3" s="25"/>
+      <c r="DD3" s="25"/>
+      <c r="DE3" s="25"/>
+      <c r="DF3" s="25"/>
+      <c r="DG3" s="25"/>
+      <c r="DH3" s="25"/>
+      <c r="DI3" s="25"/>
+      <c r="DJ3" s="25"/>
+      <c r="DK3" s="25"/>
+      <c r="DL3" s="25"/>
+      <c r="DM3" s="25"/>
+      <c r="DN3" s="25"/>
+      <c r="DO3" s="25"/>
+      <c r="DP3" s="25"/>
+      <c r="DQ3" s="25"/>
+      <c r="DR3" s="25"/>
+      <c r="DS3" s="25"/>
+      <c r="DT3" s="25"/>
+      <c r="DU3" s="25"/>
+      <c r="DV3" s="25"/>
+      <c r="DW3" s="25"/>
+      <c r="DX3" s="25"/>
+      <c r="DY3" s="25"/>
+      <c r="DZ3" s="25"/>
+      <c r="EA3" s="25"/>
+      <c r="EB3" s="25"/>
+      <c r="EC3" s="25"/>
+      <c r="ED3" s="25"/>
+      <c r="EE3" s="25"/>
+      <c r="EF3" s="25"/>
+      <c r="EG3" s="25"/>
+      <c r="EH3" s="25"/>
+      <c r="EI3" s="25"/>
+      <c r="EJ3" s="25"/>
+      <c r="EK3" s="25"/>
+      <c r="EL3" s="25"/>
+      <c r="EM3" s="25"/>
+      <c r="EN3" s="25"/>
+      <c r="EO3" s="25"/>
+      <c r="EP3" s="25"/>
+      <c r="EQ3" s="25"/>
+      <c r="ER3" s="25"/>
+      <c r="ES3" s="25"/>
+      <c r="ET3" s="25"/>
+      <c r="EU3" s="25"/>
+      <c r="EV3" s="25"/>
+      <c r="EW3" s="25"/>
+      <c r="EX3" s="25"/>
+      <c r="EY3" s="25"/>
+      <c r="EZ3" s="25"/>
+      <c r="FA3" s="25"/>
+      <c r="FB3" s="25"/>
+      <c r="FC3" s="25"/>
+      <c r="FD3" s="25"/>
+      <c r="FE3" s="25"/>
+      <c r="FF3" s="25"/>
+      <c r="FG3" s="25"/>
+      <c r="FH3" s="25"/>
+      <c r="FI3" s="25"/>
+      <c r="FJ3" s="25"/>
+      <c r="FK3" s="25"/>
+      <c r="FL3" s="25"/>
+      <c r="FM3" s="25"/>
+      <c r="FN3" s="25"/>
+      <c r="FO3" s="25"/>
+      <c r="FP3" s="25"/>
+      <c r="FQ3" s="25"/>
+      <c r="FR3" s="25"/>
+      <c r="FS3" s="25"/>
+      <c r="FT3" s="25"/>
+      <c r="FU3" s="25"/>
+      <c r="FV3" s="25"/>
+      <c r="FW3" s="25"/>
+      <c r="FX3" s="25"/>
+      <c r="FY3" s="25"/>
+      <c r="FZ3" s="25"/>
+      <c r="GA3" s="25"/>
+      <c r="GB3" s="25"/>
+      <c r="GC3" s="25"/>
+      <c r="GD3" s="25"/>
+      <c r="GE3" s="25"/>
+      <c r="GF3" s="25"/>
+      <c r="GG3" s="25"/>
+      <c r="GH3" s="25"/>
+      <c r="GI3" s="25"/>
+      <c r="GJ3" s="25"/>
+      <c r="GK3" s="25"/>
+      <c r="GL3" s="25"/>
+      <c r="GM3" s="25"/>
+      <c r="GN3" s="25"/>
+      <c r="GO3" s="25"/>
+      <c r="GP3" s="25"/>
+      <c r="GQ3" s="25"/>
+      <c r="GR3" s="25"/>
+      <c r="GS3" s="25"/>
+      <c r="GT3" s="25"/>
+      <c r="GU3" s="25"/>
+      <c r="GV3" s="25"/>
+      <c r="GW3" s="25"/>
+      <c r="GX3" s="25"/>
+      <c r="GY3" s="25"/>
+      <c r="GZ3" s="25"/>
+      <c r="HA3" s="25"/>
+      <c r="HB3" s="25"/>
+      <c r="HC3" s="25"/>
+      <c r="HD3" s="25"/>
+      <c r="HE3" s="25"/>
+      <c r="HF3" s="25"/>
+      <c r="HG3" s="25"/>
+      <c r="HH3" s="25"/>
+      <c r="HI3" s="25"/>
+      <c r="HJ3" s="25"/>
+      <c r="HK3" s="25"/>
+      <c r="HL3" s="25"/>
+      <c r="HM3" s="25"/>
+      <c r="HN3" s="25"/>
+      <c r="HO3" s="25"/>
+      <c r="HP3" s="25"/>
+      <c r="HQ3" s="25"/>
+      <c r="HR3" s="25"/>
+      <c r="HS3" s="25"/>
+      <c r="HT3" s="25"/>
+      <c r="HU3" s="25"/>
+      <c r="HV3" s="25"/>
+      <c r="HW3" s="25"/>
+      <c r="HX3" s="25"/>
+      <c r="HY3" s="25"/>
+      <c r="HZ3" s="25"/>
+      <c r="IA3" s="25"/>
+      <c r="IB3" s="25"/>
+      <c r="IC3" s="25"/>
+      <c r="ID3" s="25"/>
+      <c r="IE3" s="25"/>
+      <c r="IF3" s="25"/>
+      <c r="IG3" s="25"/>
+      <c r="IH3" s="25"/>
+      <c r="II3" s="25"/>
+      <c r="IJ3" s="25"/>
+      <c r="IK3" s="25"/>
+      <c r="IL3" s="25"/>
+      <c r="IM3" s="25"/>
+      <c r="IN3" s="25"/>
+      <c r="IO3" s="25"/>
+      <c r="IP3" s="25"/>
+      <c r="IQ3" s="25"/>
+      <c r="IR3" s="25"/>
+      <c r="IS3" s="25"/>
+      <c r="IT3" s="25"/>
+      <c r="IU3" s="25"/>
+      <c r="IV3" s="25"/>
+      <c r="IW3" s="25"/>
+      <c r="IX3" s="25"/>
+      <c r="IY3" s="25"/>
+      <c r="IZ3" s="25"/>
+      <c r="JA3" s="25"/>
+      <c r="JB3" s="25"/>
+      <c r="JC3" s="25"/>
+      <c r="JD3" s="25"/>
+      <c r="JE3" s="25"/>
+      <c r="JF3" s="25"/>
+      <c r="JG3" s="25"/>
+      <c r="JH3" s="25"/>
+      <c r="JI3" s="25"/>
+      <c r="JJ3" s="25"/>
+      <c r="JK3" s="25"/>
+      <c r="JL3" s="25"/>
+      <c r="JM3" s="25"/>
+      <c r="JN3" s="25"/>
+      <c r="JO3" s="25"/>
+      <c r="JP3" s="25"/>
+      <c r="JQ3" s="25"/>
+      <c r="JR3" s="25"/>
+      <c r="JS3" s="25"/>
+      <c r="JT3" s="25"/>
+      <c r="JU3" s="25"/>
+      <c r="JV3" s="25"/>
+      <c r="JW3" s="25"/>
+      <c r="JX3" s="25"/>
+      <c r="JY3" s="25"/>
+      <c r="JZ3" s="25"/>
+      <c r="KA3" s="25"/>
+      <c r="KB3" s="25"/>
+      <c r="KC3" s="25"/>
+      <c r="KD3" s="25"/>
+      <c r="KE3" s="25"/>
+      <c r="KF3" s="25"/>
+      <c r="KG3" s="25"/>
+      <c r="KH3" s="25"/>
+      <c r="KI3" s="25"/>
+      <c r="KJ3" s="25"/>
+      <c r="KK3" s="25"/>
+      <c r="KL3" s="25"/>
+      <c r="KM3" s="25"/>
+      <c r="KN3" s="25"/>
+      <c r="KO3" s="25"/>
+      <c r="KP3" s="25"/>
+      <c r="KQ3" s="25"/>
+      <c r="KR3" s="25"/>
+      <c r="KS3" s="25"/>
+      <c r="KT3" s="25"/>
+      <c r="KU3" s="25"/>
+      <c r="KV3" s="25"/>
+      <c r="KW3" s="25"/>
+      <c r="KX3" s="25"/>
+      <c r="KY3" s="25"/>
+      <c r="KZ3" s="25"/>
+      <c r="LA3" s="25"/>
+      <c r="LB3" s="25"/>
+      <c r="LC3" s="25"/>
+      <c r="LD3" s="25"/>
+      <c r="LE3" s="25"/>
+      <c r="LF3" s="25"/>
+      <c r="LG3" s="25"/>
+      <c r="LH3" s="25"/>
+      <c r="LI3" s="25"/>
+      <c r="LJ3" s="25"/>
+      <c r="LK3" s="25"/>
+      <c r="LL3" s="25"/>
+      <c r="LM3" s="25"/>
+      <c r="LN3" s="25"/>
+      <c r="LO3" s="25"/>
+      <c r="LP3" s="25"/>
+      <c r="LQ3" s="25"/>
+      <c r="LR3" s="25"/>
+      <c r="LS3" s="25"/>
+      <c r="LT3" s="25"/>
+      <c r="LU3" s="25"/>
+      <c r="LV3" s="25"/>
+      <c r="LW3" s="25"/>
+      <c r="LX3" s="25"/>
+      <c r="LY3" s="25"/>
+      <c r="LZ3" s="25"/>
+      <c r="MA3" s="25"/>
+      <c r="MB3" s="25"/>
+      <c r="MC3" s="25"/>
+      <c r="MD3" s="25"/>
+      <c r="ME3" s="25"/>
+      <c r="MF3" s="25"/>
+      <c r="MG3" s="25"/>
+      <c r="MH3" s="25"/>
+      <c r="MI3" s="25"/>
+      <c r="MJ3" s="25"/>
+      <c r="MK3" s="25"/>
+      <c r="ML3" s="25"/>
+      <c r="MM3" s="25"/>
+      <c r="MN3" s="25"/>
+      <c r="MO3" s="25"/>
+      <c r="MP3" s="25"/>
+      <c r="MQ3" s="25"/>
+      <c r="MR3" s="25"/>
+      <c r="MS3" s="25"/>
+      <c r="MT3" s="25"/>
+      <c r="MU3" s="25"/>
+      <c r="MV3" s="25"/>
+      <c r="MW3" s="15"/>
+      <c r="MX3" s="15"/>
+      <c r="MY3" s="15"/>
+      <c r="MZ3" s="15"/>
+      <c r="NA3" s="15"/>
+      <c r="NB3" s="15"/>
+      <c r="NC3" s="15"/>
+      <c r="ND3" s="15"/>
+      <c r="NE3" s="15"/>
+      <c r="NF3" s="15"/>
+      <c r="NG3" s="15"/>
+      <c r="NH3" s="15"/>
+      <c r="NI3" s="15"/>
+      <c r="NJ3" s="15"/>
     </row>
-    <row r="4" spans="1:373" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="12" t="s">
+    <row r="4" spans="1:374" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="75" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="11" t="s">
+      <c r="B4" s="75"/>
+      <c r="C4" s="76" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="11"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="10" t="s">
+      <c r="D4" s="76"/>
+      <c r="E4" s="76"/>
+      <c r="F4" s="76"/>
+      <c r="G4" s="76"/>
+      <c r="H4" s="76"/>
+      <c r="I4" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="J4" s="10"/>
-      <c r="K4" s="10"/>
-      <c r="L4" s="10"/>
-      <c r="M4" s="10"/>
-      <c r="N4" s="9" t="s">
+      <c r="J4" s="77"/>
+      <c r="K4" s="77"/>
+      <c r="L4" s="77"/>
+      <c r="M4" s="77"/>
+      <c r="N4" s="68" t="s">
         <v>4</v>
       </c>
-      <c r="O4" s="9"/>
-      <c r="P4" s="9"/>
-      <c r="Q4" s="8" t="s">
+      <c r="O4" s="68"/>
+      <c r="P4" s="68"/>
+      <c r="Q4" s="69" t="s">
         <v>5</v>
       </c>
-      <c r="R4" s="8"/>
-      <c r="S4" s="8"/>
-      <c r="T4" s="8"/>
-      <c r="U4" s="8"/>
-      <c r="V4" s="7" t="s">
+      <c r="R4" s="69"/>
+      <c r="S4" s="69"/>
+      <c r="T4" s="69"/>
+      <c r="U4" s="69"/>
+      <c r="V4" s="70" t="s">
         <v>6</v>
       </c>
-      <c r="W4" s="7"/>
-      <c r="X4" s="7"/>
-      <c r="Y4" s="7"/>
-      <c r="Z4" s="7"/>
-      <c r="AA4" s="7"/>
-      <c r="AB4" s="7"/>
-      <c r="AC4" s="6" t="s">
+      <c r="W4" s="70"/>
+      <c r="X4" s="70"/>
+      <c r="Y4" s="70"/>
+      <c r="Z4" s="70"/>
+      <c r="AA4" s="70"/>
+      <c r="AB4" s="70"/>
+      <c r="AC4" s="71" t="s">
         <v>7</v>
       </c>
-      <c r="AD4" s="6"/>
-      <c r="AE4" s="6"/>
-      <c r="AF4" s="5" t="s">
+      <c r="AD4" s="71"/>
+      <c r="AE4" s="71"/>
+      <c r="AF4" s="72" t="s">
         <v>8</v>
       </c>
-      <c r="AG4" s="5"/>
-      <c r="AH4" s="4"/>
-      <c r="AI4" s="4"/>
-      <c r="AJ4" s="4"/>
-      <c r="AK4" s="4"/>
-      <c r="AL4" s="4"/>
-      <c r="AM4" s="3" t="s">
+      <c r="AG4" s="72"/>
+      <c r="AH4" s="66"/>
+      <c r="AI4" s="66"/>
+      <c r="AJ4" s="66"/>
+      <c r="AK4" s="66"/>
+      <c r="AL4" s="66"/>
+      <c r="AM4" s="67" t="s">
         <v>9</v>
       </c>
-      <c r="AN4" s="3"/>
-      <c r="AO4" s="3"/>
-      <c r="AP4" s="3"/>
-      <c r="AQ4" s="3"/>
-      <c r="AR4" s="3"/>
-      <c r="AS4" s="3"/>
-      <c r="AT4" s="3"/>
-      <c r="AU4" s="3"/>
-      <c r="AV4" s="3"/>
-      <c r="AW4" s="3"/>
-      <c r="AX4" s="3"/>
-      <c r="AY4" s="3"/>
-      <c r="AZ4" s="3"/>
-      <c r="BA4" s="3"/>
-      <c r="BB4" s="3"/>
-      <c r="BC4" s="3"/>
-      <c r="BD4" s="3"/>
-      <c r="BE4" s="3"/>
-      <c r="BF4" s="3"/>
-      <c r="BG4" s="3"/>
-      <c r="BH4" s="3"/>
-      <c r="BI4" s="3"/>
-      <c r="BJ4" s="3"/>
-      <c r="BK4" s="3"/>
-      <c r="BL4" s="3"/>
-      <c r="BM4" s="3"/>
-      <c r="BN4" s="3"/>
-      <c r="BO4" s="2" t="s">
+      <c r="AN4" s="67"/>
+      <c r="AO4" s="67"/>
+      <c r="AP4" s="67"/>
+      <c r="AQ4" s="67"/>
+      <c r="AR4" s="67"/>
+      <c r="AS4" s="67"/>
+      <c r="AT4" s="67"/>
+      <c r="AU4" s="67"/>
+      <c r="AV4" s="67"/>
+      <c r="AW4" s="67"/>
+      <c r="AX4" s="67"/>
+      <c r="AY4" s="67"/>
+      <c r="AZ4" s="67"/>
+      <c r="BA4" s="67"/>
+      <c r="BB4" s="67"/>
+      <c r="BC4" s="67"/>
+      <c r="BD4" s="67"/>
+      <c r="BE4" s="67"/>
+      <c r="BF4" s="67"/>
+      <c r="BG4" s="67"/>
+      <c r="BH4" s="67"/>
+      <c r="BI4" s="67"/>
+      <c r="BJ4" s="67"/>
+      <c r="BK4" s="67"/>
+      <c r="BL4" s="67"/>
+      <c r="BM4" s="67"/>
+      <c r="BN4" s="67"/>
+      <c r="BO4" s="56" t="s">
         <v>10</v>
       </c>
-      <c r="BP4" s="2"/>
-      <c r="BQ4" s="2"/>
-      <c r="BR4" s="2"/>
-      <c r="BS4" s="2"/>
-      <c r="BT4" s="2"/>
-      <c r="BU4" s="2"/>
-      <c r="BV4" s="2"/>
-      <c r="BW4" s="2"/>
-      <c r="BX4" s="2"/>
-      <c r="BY4" s="1" t="s">
+      <c r="BP4" s="56"/>
+      <c r="BQ4" s="56"/>
+      <c r="BR4" s="56"/>
+      <c r="BS4" s="56"/>
+      <c r="BT4" s="56"/>
+      <c r="BU4" s="56"/>
+      <c r="BV4" s="56"/>
+      <c r="BW4" s="56"/>
+      <c r="BX4" s="56"/>
+      <c r="BY4" s="65" t="s">
         <v>11</v>
       </c>
-      <c r="BZ4" s="1"/>
-      <c r="CA4" s="1"/>
-      <c r="CB4" s="1"/>
-      <c r="CC4" s="1"/>
-      <c r="CD4" s="1"/>
-      <c r="CE4" s="1"/>
-      <c r="CF4" s="1"/>
-      <c r="CG4" s="1"/>
-      <c r="CH4" s="1"/>
-      <c r="CI4" s="68" t="s">
+      <c r="BZ4" s="65"/>
+      <c r="CA4" s="65"/>
+      <c r="CB4" s="65"/>
+      <c r="CC4" s="65"/>
+      <c r="CD4" s="65"/>
+      <c r="CE4" s="65"/>
+      <c r="CF4" s="65"/>
+      <c r="CG4" s="65"/>
+      <c r="CH4" s="65"/>
+      <c r="CI4" s="60" t="s">
         <v>12</v>
       </c>
-      <c r="CJ4" s="68"/>
-      <c r="CK4" s="68"/>
-      <c r="CL4" s="68"/>
-      <c r="CM4" s="68"/>
-      <c r="CN4" s="68"/>
-      <c r="CO4" s="68"/>
-      <c r="CP4" s="68"/>
-      <c r="CQ4" s="68"/>
-      <c r="CR4" s="68"/>
-      <c r="CS4" s="1" t="s">
+      <c r="CJ4" s="60"/>
+      <c r="CK4" s="60"/>
+      <c r="CL4" s="60"/>
+      <c r="CM4" s="60"/>
+      <c r="CN4" s="60"/>
+      <c r="CO4" s="60"/>
+      <c r="CP4" s="60"/>
+      <c r="CQ4" s="60"/>
+      <c r="CR4" s="60"/>
+      <c r="CS4" s="65" t="s">
         <v>13</v>
       </c>
-      <c r="CT4" s="1"/>
-      <c r="CU4" s="1"/>
-      <c r="CV4" s="1"/>
-      <c r="CW4" s="1"/>
-      <c r="CX4" s="1"/>
-      <c r="CY4" s="1"/>
-      <c r="CZ4" s="1"/>
-      <c r="DA4" s="1"/>
-      <c r="DB4" s="1"/>
-      <c r="DC4" s="68" t="s">
+      <c r="CT4" s="65"/>
+      <c r="CU4" s="65"/>
+      <c r="CV4" s="65"/>
+      <c r="CW4" s="65"/>
+      <c r="CX4" s="65"/>
+      <c r="CY4" s="65"/>
+      <c r="CZ4" s="65"/>
+      <c r="DA4" s="65"/>
+      <c r="DB4" s="65"/>
+      <c r="DC4" s="60" t="s">
         <v>14</v>
       </c>
-      <c r="DD4" s="68"/>
-      <c r="DE4" s="68"/>
-      <c r="DF4" s="68"/>
-      <c r="DG4" s="68"/>
-      <c r="DH4" s="68"/>
-      <c r="DI4" s="68"/>
-      <c r="DJ4" s="68"/>
-      <c r="DK4" s="68"/>
-      <c r="DL4" s="68"/>
-      <c r="DM4" s="1" t="s">
+      <c r="DD4" s="60"/>
+      <c r="DE4" s="60"/>
+      <c r="DF4" s="60"/>
+      <c r="DG4" s="60"/>
+      <c r="DH4" s="60"/>
+      <c r="DI4" s="60"/>
+      <c r="DJ4" s="60"/>
+      <c r="DK4" s="60"/>
+      <c r="DL4" s="60"/>
+      <c r="DM4" s="65" t="s">
         <v>15</v>
       </c>
-      <c r="DN4" s="1"/>
-      <c r="DO4" s="1"/>
-      <c r="DP4" s="1"/>
-      <c r="DQ4" s="1"/>
-      <c r="DR4" s="1"/>
-      <c r="DS4" s="1"/>
-      <c r="DT4" s="1"/>
-      <c r="DU4" s="1"/>
-      <c r="DV4" s="1"/>
-      <c r="DW4" s="68" t="s">
+      <c r="DN4" s="65"/>
+      <c r="DO4" s="65"/>
+      <c r="DP4" s="65"/>
+      <c r="DQ4" s="65"/>
+      <c r="DR4" s="65"/>
+      <c r="DS4" s="65"/>
+      <c r="DT4" s="65"/>
+      <c r="DU4" s="65"/>
+      <c r="DV4" s="65"/>
+      <c r="DW4" s="60" t="s">
         <v>16</v>
       </c>
-      <c r="DX4" s="68"/>
-      <c r="DY4" s="68"/>
-      <c r="DZ4" s="68"/>
-      <c r="EA4" s="68"/>
-      <c r="EB4" s="68"/>
-      <c r="EC4" s="68"/>
-      <c r="ED4" s="68"/>
-      <c r="EE4" s="68"/>
-      <c r="EF4" s="68"/>
-      <c r="EG4" s="1" t="s">
+      <c r="DX4" s="60"/>
+      <c r="DY4" s="60"/>
+      <c r="DZ4" s="60"/>
+      <c r="EA4" s="60"/>
+      <c r="EB4" s="60"/>
+      <c r="EC4" s="60"/>
+      <c r="ED4" s="60"/>
+      <c r="EE4" s="60"/>
+      <c r="EF4" s="60"/>
+      <c r="EG4" s="65" t="s">
         <v>17</v>
       </c>
-      <c r="EH4" s="1"/>
-      <c r="EI4" s="1"/>
-      <c r="EJ4" s="1"/>
-      <c r="EK4" s="1"/>
-      <c r="EL4" s="1"/>
-      <c r="EM4" s="1"/>
-      <c r="EN4" s="1"/>
-      <c r="EO4" s="1"/>
-      <c r="EP4" s="1"/>
-      <c r="EQ4" s="68" t="s">
+      <c r="EH4" s="65"/>
+      <c r="EI4" s="65"/>
+      <c r="EJ4" s="65"/>
+      <c r="EK4" s="65"/>
+      <c r="EL4" s="65"/>
+      <c r="EM4" s="65"/>
+      <c r="EN4" s="65"/>
+      <c r="EO4" s="65"/>
+      <c r="EP4" s="65"/>
+      <c r="EQ4" s="60" t="s">
         <v>18</v>
       </c>
-      <c r="ER4" s="68"/>
-      <c r="ES4" s="68"/>
-      <c r="ET4" s="68"/>
-      <c r="EU4" s="68"/>
-      <c r="EV4" s="68"/>
-      <c r="EW4" s="68"/>
-      <c r="EX4" s="68"/>
-      <c r="EY4" s="68"/>
-      <c r="EZ4" s="68"/>
-      <c r="FA4" s="69" t="s">
+      <c r="ER4" s="60"/>
+      <c r="ES4" s="60"/>
+      <c r="ET4" s="60"/>
+      <c r="EU4" s="60"/>
+      <c r="EV4" s="60"/>
+      <c r="EW4" s="60"/>
+      <c r="EX4" s="60"/>
+      <c r="EY4" s="60"/>
+      <c r="EZ4" s="60"/>
+      <c r="FA4" s="61" t="s">
         <v>19</v>
       </c>
-      <c r="FB4" s="69"/>
-      <c r="FC4" s="69"/>
-      <c r="FD4" s="69"/>
-      <c r="FE4" s="69"/>
-      <c r="FF4" s="69"/>
-      <c r="FG4" s="69"/>
-      <c r="FH4" s="69"/>
-      <c r="FI4" s="69"/>
-      <c r="FJ4" s="69"/>
-      <c r="FK4" s="70" t="s">
+      <c r="FB4" s="61"/>
+      <c r="FC4" s="61"/>
+      <c r="FD4" s="61"/>
+      <c r="FE4" s="61"/>
+      <c r="FF4" s="61"/>
+      <c r="FG4" s="61"/>
+      <c r="FH4" s="61"/>
+      <c r="FI4" s="61"/>
+      <c r="FJ4" s="61"/>
+      <c r="FK4" s="62" t="s">
         <v>20</v>
       </c>
-      <c r="FL4" s="70"/>
-      <c r="FM4" s="70"/>
-      <c r="FN4" s="70"/>
-      <c r="FO4" s="70"/>
-      <c r="FP4" s="70"/>
-      <c r="FQ4" s="70"/>
-      <c r="FR4" s="70"/>
-      <c r="FS4" s="70"/>
-      <c r="FT4" s="70"/>
-      <c r="FU4" s="71" t="s">
+      <c r="FL4" s="62"/>
+      <c r="FM4" s="62"/>
+      <c r="FN4" s="62"/>
+      <c r="FO4" s="62"/>
+      <c r="FP4" s="62"/>
+      <c r="FQ4" s="62"/>
+      <c r="FR4" s="62"/>
+      <c r="FS4" s="62"/>
+      <c r="FT4" s="62"/>
+      <c r="FU4" s="63" t="s">
         <v>21</v>
       </c>
-      <c r="FV4" s="71"/>
-      <c r="FW4" s="71"/>
-      <c r="FX4" s="71"/>
-      <c r="FY4" s="71"/>
-      <c r="FZ4" s="71"/>
-      <c r="GA4" s="71"/>
-      <c r="GB4" s="71"/>
-      <c r="GC4" s="71"/>
-      <c r="GD4" s="71"/>
-      <c r="GE4" s="72" t="s">
+      <c r="FV4" s="63"/>
+      <c r="FW4" s="63"/>
+      <c r="FX4" s="63"/>
+      <c r="FY4" s="63"/>
+      <c r="FZ4" s="63"/>
+      <c r="GA4" s="63"/>
+      <c r="GB4" s="63"/>
+      <c r="GC4" s="63"/>
+      <c r="GD4" s="63"/>
+      <c r="GE4" s="64" t="s">
         <v>22</v>
       </c>
-      <c r="GF4" s="72"/>
-      <c r="GG4" s="72"/>
-      <c r="GH4" s="72"/>
-      <c r="GI4" s="72"/>
-      <c r="GJ4" s="72"/>
-      <c r="GK4" s="72"/>
-      <c r="GL4" s="72"/>
-      <c r="GM4" s="72"/>
-      <c r="GN4" s="72"/>
-      <c r="GO4" s="73" t="s">
+      <c r="GF4" s="64"/>
+      <c r="GG4" s="64"/>
+      <c r="GH4" s="64"/>
+      <c r="GI4" s="64"/>
+      <c r="GJ4" s="64"/>
+      <c r="GK4" s="64"/>
+      <c r="GL4" s="64"/>
+      <c r="GM4" s="64"/>
+      <c r="GN4" s="64"/>
+      <c r="GO4" s="58" t="s">
         <v>23</v>
       </c>
-      <c r="GP4" s="73"/>
-      <c r="GQ4" s="73"/>
-      <c r="GR4" s="73"/>
-      <c r="GS4" s="73"/>
-      <c r="GT4" s="73"/>
-      <c r="GU4" s="73"/>
-      <c r="GV4" s="73"/>
-      <c r="GW4" s="73"/>
-      <c r="GX4" s="73"/>
-      <c r="GY4" s="74" t="s">
+      <c r="GP4" s="58"/>
+      <c r="GQ4" s="58"/>
+      <c r="GR4" s="58"/>
+      <c r="GS4" s="58"/>
+      <c r="GT4" s="58"/>
+      <c r="GU4" s="58"/>
+      <c r="GV4" s="58"/>
+      <c r="GW4" s="58"/>
+      <c r="GX4" s="58"/>
+      <c r="GY4" s="59" t="s">
         <v>24</v>
       </c>
-      <c r="GZ4" s="74"/>
-      <c r="HA4" s="74"/>
-      <c r="HB4" s="74"/>
-      <c r="HC4" s="74"/>
-      <c r="HD4" s="74"/>
-      <c r="HE4" s="74"/>
-      <c r="HF4" s="74"/>
-      <c r="HG4" s="74"/>
-      <c r="HH4" s="74"/>
-      <c r="HI4" s="2" t="s">
+      <c r="GZ4" s="59"/>
+      <c r="HA4" s="59"/>
+      <c r="HB4" s="59"/>
+      <c r="HC4" s="59"/>
+      <c r="HD4" s="59"/>
+      <c r="HE4" s="59"/>
+      <c r="HF4" s="59"/>
+      <c r="HG4" s="59"/>
+      <c r="HH4" s="59"/>
+      <c r="HI4" s="56" t="s">
         <v>25</v>
       </c>
-      <c r="HJ4" s="2"/>
-      <c r="HK4" s="2"/>
-      <c r="HL4" s="2"/>
-      <c r="HM4" s="2"/>
-      <c r="HN4" s="2"/>
-      <c r="HO4" s="2"/>
-      <c r="HP4" s="2"/>
-      <c r="HQ4" s="2"/>
-      <c r="HR4" s="2"/>
-      <c r="HS4" s="2" t="s">
+      <c r="HJ4" s="56"/>
+      <c r="HK4" s="56"/>
+      <c r="HL4" s="56"/>
+      <c r="HM4" s="56"/>
+      <c r="HN4" s="56"/>
+      <c r="HO4" s="56"/>
+      <c r="HP4" s="56"/>
+      <c r="HQ4" s="56"/>
+      <c r="HR4" s="56"/>
+      <c r="HS4" s="56" t="s">
         <v>26</v>
       </c>
-      <c r="HT4" s="2"/>
-      <c r="HU4" s="2"/>
-      <c r="HV4" s="2"/>
-      <c r="HW4" s="2"/>
-      <c r="HX4" s="2"/>
-      <c r="HY4" s="2"/>
-      <c r="HZ4" s="2"/>
-      <c r="IA4" s="2"/>
-      <c r="IB4" s="2"/>
-      <c r="IC4" s="2" t="s">
+      <c r="HT4" s="56"/>
+      <c r="HU4" s="56"/>
+      <c r="HV4" s="56"/>
+      <c r="HW4" s="56"/>
+      <c r="HX4" s="56"/>
+      <c r="HY4" s="56"/>
+      <c r="HZ4" s="56"/>
+      <c r="IA4" s="56"/>
+      <c r="IB4" s="56"/>
+      <c r="IC4" s="56" t="s">
         <v>27</v>
       </c>
-      <c r="ID4" s="2"/>
-      <c r="IE4" s="2"/>
-      <c r="IF4" s="2"/>
-      <c r="IG4" s="2"/>
-      <c r="IH4" s="2"/>
-      <c r="II4" s="2"/>
-      <c r="IJ4" s="2"/>
-      <c r="IK4" s="2"/>
-      <c r="IL4" s="2"/>
-      <c r="IM4" s="2" t="s">
+      <c r="ID4" s="56"/>
+      <c r="IE4" s="56"/>
+      <c r="IF4" s="56"/>
+      <c r="IG4" s="56"/>
+      <c r="IH4" s="56"/>
+      <c r="II4" s="56"/>
+      <c r="IJ4" s="56"/>
+      <c r="IK4" s="56"/>
+      <c r="IL4" s="56"/>
+      <c r="IM4" s="56" t="s">
         <v>28</v>
       </c>
-      <c r="IN4" s="2"/>
-      <c r="IO4" s="2"/>
-      <c r="IP4" s="2"/>
-      <c r="IQ4" s="2"/>
-      <c r="IR4" s="2"/>
-      <c r="IS4" s="2"/>
-      <c r="IT4" s="2"/>
-      <c r="IU4" s="2"/>
-      <c r="IV4" s="2"/>
-      <c r="IW4" s="2" t="s">
+      <c r="IN4" s="56"/>
+      <c r="IO4" s="56"/>
+      <c r="IP4" s="56"/>
+      <c r="IQ4" s="56"/>
+      <c r="IR4" s="56"/>
+      <c r="IS4" s="56"/>
+      <c r="IT4" s="56"/>
+      <c r="IU4" s="56"/>
+      <c r="IV4" s="56"/>
+      <c r="IW4" s="56" t="s">
         <v>29</v>
       </c>
-      <c r="IX4" s="2"/>
-      <c r="IY4" s="2"/>
-      <c r="IZ4" s="2"/>
-      <c r="JA4" s="2"/>
-      <c r="JB4" s="2"/>
-      <c r="JC4" s="2"/>
-      <c r="JD4" s="2"/>
-      <c r="JE4" s="2"/>
-      <c r="JF4" s="2"/>
-      <c r="JG4" s="2" t="s">
+      <c r="IX4" s="56"/>
+      <c r="IY4" s="56"/>
+      <c r="IZ4" s="56"/>
+      <c r="JA4" s="56"/>
+      <c r="JB4" s="56"/>
+      <c r="JC4" s="56"/>
+      <c r="JD4" s="56"/>
+      <c r="JE4" s="56"/>
+      <c r="JF4" s="56"/>
+      <c r="JG4" s="56" t="s">
         <v>30</v>
       </c>
-      <c r="JH4" s="2"/>
-      <c r="JI4" s="2"/>
-      <c r="JJ4" s="2"/>
-      <c r="JK4" s="2"/>
-      <c r="JL4" s="2"/>
-      <c r="JM4" s="2"/>
-      <c r="JN4" s="2"/>
-      <c r="JO4" s="2"/>
-      <c r="JP4" s="2"/>
-      <c r="JQ4" s="2" t="s">
+      <c r="JH4" s="56"/>
+      <c r="JI4" s="56"/>
+      <c r="JJ4" s="56"/>
+      <c r="JK4" s="56"/>
+      <c r="JL4" s="56"/>
+      <c r="JM4" s="56"/>
+      <c r="JN4" s="56"/>
+      <c r="JO4" s="56"/>
+      <c r="JP4" s="56"/>
+      <c r="JQ4" s="56" t="s">
         <v>31</v>
       </c>
-      <c r="JR4" s="2"/>
-      <c r="JS4" s="2"/>
-      <c r="JT4" s="2"/>
-      <c r="JU4" s="2"/>
-      <c r="JV4" s="2"/>
-      <c r="JW4" s="2"/>
-      <c r="JX4" s="2"/>
-      <c r="JY4" s="2"/>
-      <c r="JZ4" s="2"/>
-      <c r="KA4" s="2" t="s">
+      <c r="JR4" s="56"/>
+      <c r="JS4" s="56"/>
+      <c r="JT4" s="56"/>
+      <c r="JU4" s="56"/>
+      <c r="JV4" s="56"/>
+      <c r="JW4" s="56"/>
+      <c r="JX4" s="56"/>
+      <c r="JY4" s="56"/>
+      <c r="JZ4" s="56"/>
+      <c r="KA4" s="56" t="s">
         <v>32</v>
       </c>
-      <c r="KB4" s="2"/>
-      <c r="KC4" s="2"/>
-      <c r="KD4" s="2"/>
-      <c r="KE4" s="2"/>
-      <c r="KF4" s="2"/>
-      <c r="KG4" s="2"/>
-      <c r="KH4" s="2"/>
-      <c r="KI4" s="2"/>
-      <c r="KJ4" s="2"/>
-      <c r="KK4" s="2" t="s">
+      <c r="KB4" s="56"/>
+      <c r="KC4" s="56"/>
+      <c r="KD4" s="56"/>
+      <c r="KE4" s="56"/>
+      <c r="KF4" s="56"/>
+      <c r="KG4" s="56"/>
+      <c r="KH4" s="56"/>
+      <c r="KI4" s="56"/>
+      <c r="KJ4" s="56"/>
+      <c r="KK4" s="56" t="s">
         <v>33</v>
       </c>
-      <c r="KL4" s="2"/>
-      <c r="KM4" s="2"/>
-      <c r="KN4" s="2"/>
-      <c r="KO4" s="2"/>
-      <c r="KP4" s="2"/>
-      <c r="KQ4" s="2"/>
-      <c r="KR4" s="2"/>
-      <c r="KS4" s="2"/>
-      <c r="KT4" s="2"/>
-      <c r="KU4" s="75" t="s">
+      <c r="KL4" s="56"/>
+      <c r="KM4" s="56"/>
+      <c r="KN4" s="56"/>
+      <c r="KO4" s="56"/>
+      <c r="KP4" s="56"/>
+      <c r="KQ4" s="56"/>
+      <c r="KR4" s="56"/>
+      <c r="KS4" s="56"/>
+      <c r="KT4" s="56"/>
+      <c r="KU4" s="57" t="s">
         <v>34</v>
       </c>
-      <c r="KV4" s="75"/>
-      <c r="KW4" s="75"/>
-      <c r="KX4" s="75"/>
-      <c r="KY4" s="75"/>
-      <c r="KZ4" s="75"/>
-      <c r="LA4" s="75"/>
-      <c r="LB4" s="75"/>
-      <c r="LC4" s="75"/>
-      <c r="LD4" s="75"/>
-      <c r="LE4" s="75" t="s">
+      <c r="KV4" s="57"/>
+      <c r="KW4" s="57"/>
+      <c r="KX4" s="57"/>
+      <c r="KY4" s="57"/>
+      <c r="KZ4" s="57"/>
+      <c r="LA4" s="57"/>
+      <c r="LB4" s="57"/>
+      <c r="LC4" s="57"/>
+      <c r="LD4" s="57"/>
+      <c r="LE4" s="57" t="s">
         <v>35</v>
       </c>
-      <c r="LF4" s="75"/>
-      <c r="LG4" s="75"/>
-      <c r="LH4" s="75"/>
-      <c r="LI4" s="75"/>
-      <c r="LJ4" s="75"/>
-      <c r="LK4" s="75"/>
-      <c r="LL4" s="75"/>
-      <c r="LM4" s="75"/>
-      <c r="LN4" s="75"/>
-      <c r="LO4" s="75" t="s">
+      <c r="LF4" s="57"/>
+      <c r="LG4" s="57"/>
+      <c r="LH4" s="57"/>
+      <c r="LI4" s="57"/>
+      <c r="LJ4" s="57"/>
+      <c r="LK4" s="57"/>
+      <c r="LL4" s="57"/>
+      <c r="LM4" s="57"/>
+      <c r="LN4" s="57"/>
+      <c r="LO4" s="57" t="s">
         <v>36</v>
       </c>
-      <c r="LP4" s="75"/>
-      <c r="LQ4" s="75"/>
-      <c r="LR4" s="75"/>
-      <c r="LS4" s="75"/>
-      <c r="LT4" s="75"/>
-      <c r="LU4" s="75"/>
-      <c r="LV4" s="75"/>
-      <c r="LW4" s="75"/>
-      <c r="LX4" s="75"/>
-      <c r="LY4" s="75" t="s">
+      <c r="LP4" s="57"/>
+      <c r="LQ4" s="57"/>
+      <c r="LR4" s="57"/>
+      <c r="LS4" s="57"/>
+      <c r="LT4" s="57"/>
+      <c r="LU4" s="57"/>
+      <c r="LV4" s="57"/>
+      <c r="LW4" s="57"/>
+      <c r="LX4" s="57"/>
+      <c r="LY4" s="57" t="s">
         <v>37</v>
       </c>
-      <c r="LZ4" s="75"/>
-      <c r="MA4" s="75"/>
-      <c r="MB4" s="75"/>
-      <c r="MC4" s="75"/>
-      <c r="MD4" s="75"/>
-      <c r="ME4" s="75"/>
-      <c r="MF4" s="75"/>
-      <c r="MG4" s="75"/>
-      <c r="MH4" s="75"/>
-      <c r="MI4" s="76" t="s">
+      <c r="LZ4" s="57"/>
+      <c r="MA4" s="57"/>
+      <c r="MB4" s="57"/>
+      <c r="MC4" s="57"/>
+      <c r="MD4" s="57"/>
+      <c r="ME4" s="57"/>
+      <c r="MF4" s="57"/>
+      <c r="MG4" s="57"/>
+      <c r="MH4" s="57"/>
+      <c r="MI4" s="54" t="s">
         <v>38</v>
       </c>
-      <c r="MJ4" s="76"/>
-      <c r="MK4" s="76"/>
-      <c r="ML4" s="76"/>
-      <c r="MM4" s="76"/>
-      <c r="MN4" s="76"/>
-      <c r="MO4" s="76"/>
-      <c r="MP4" s="76"/>
-      <c r="MQ4" s="76"/>
-      <c r="MR4" s="76"/>
-      <c r="MS4" s="76"/>
-      <c r="MT4" s="76"/>
-      <c r="MU4" s="76"/>
-      <c r="MV4" s="76"/>
-      <c r="MW4" s="77" t="s">
+      <c r="MJ4" s="54"/>
+      <c r="MK4" s="54"/>
+      <c r="ML4" s="54"/>
+      <c r="MM4" s="54"/>
+      <c r="MN4" s="54"/>
+      <c r="MO4" s="54"/>
+      <c r="MP4" s="54"/>
+      <c r="MQ4" s="54"/>
+      <c r="MR4" s="54"/>
+      <c r="MS4" s="54"/>
+      <c r="MT4" s="54"/>
+      <c r="MU4" s="54"/>
+      <c r="MV4" s="54"/>
+      <c r="MW4" s="55" t="s">
         <v>39</v>
       </c>
-      <c r="MX4" s="77"/>
-      <c r="MY4" s="77"/>
-      <c r="MZ4" s="40"/>
-      <c r="NA4" s="77" t="s">
+      <c r="MX4" s="55"/>
+      <c r="MY4" s="55"/>
+      <c r="MZ4" s="26"/>
+      <c r="NA4" s="55" t="s">
         <v>40</v>
       </c>
-      <c r="NB4" s="77"/>
-      <c r="NC4" s="77"/>
-      <c r="ND4" s="77"/>
-      <c r="NE4" s="77"/>
-      <c r="NF4" s="77"/>
-      <c r="NG4" s="78" t="s">
+      <c r="NB4" s="55"/>
+      <c r="NC4" s="55"/>
+      <c r="ND4" s="55"/>
+      <c r="NE4" s="55"/>
+      <c r="NF4" s="55"/>
+      <c r="NG4" s="80" t="s">
         <v>41</v>
       </c>
-      <c r="NH4" s="78"/>
-      <c r="NI4" s="41"/>
+      <c r="NH4" s="84"/>
+      <c r="NI4" s="81"/>
+      <c r="NJ4" s="27"/>
     </row>
-    <row r="5" spans="1:373" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="12"/>
-      <c r="B5" s="12"/>
-      <c r="C5" s="11"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="11"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="10"/>
-      <c r="K5" s="10"/>
-      <c r="L5" s="10"/>
-      <c r="M5" s="10"/>
-      <c r="N5" s="9"/>
-      <c r="O5" s="9"/>
-      <c r="P5" s="9"/>
-      <c r="Q5" s="8"/>
-      <c r="R5" s="8"/>
-      <c r="S5" s="8"/>
-      <c r="T5" s="8"/>
-      <c r="U5" s="8"/>
-      <c r="V5" s="7"/>
-      <c r="W5" s="7"/>
-      <c r="X5" s="7"/>
-      <c r="Y5" s="7"/>
-      <c r="Z5" s="7"/>
-      <c r="AA5" s="7"/>
-      <c r="AB5" s="7"/>
-      <c r="AC5" s="6"/>
-      <c r="AD5" s="6"/>
-      <c r="AE5" s="6"/>
-      <c r="AF5" s="5"/>
-      <c r="AG5" s="5"/>
-      <c r="AH5" s="4"/>
-      <c r="AI5" s="4"/>
-      <c r="AJ5" s="4"/>
-      <c r="AK5" s="4"/>
-      <c r="AL5" s="4"/>
-      <c r="AM5" s="3"/>
-      <c r="AN5" s="3"/>
-      <c r="AO5" s="3"/>
-      <c r="AP5" s="3"/>
-      <c r="AQ5" s="3"/>
-      <c r="AR5" s="3"/>
-      <c r="AS5" s="3"/>
-      <c r="AT5" s="3"/>
-      <c r="AU5" s="3"/>
-      <c r="AV5" s="3"/>
-      <c r="AW5" s="3"/>
-      <c r="AX5" s="3"/>
-      <c r="AY5" s="3"/>
-      <c r="AZ5" s="3"/>
-      <c r="BA5" s="3"/>
-      <c r="BB5" s="3"/>
-      <c r="BC5" s="3"/>
-      <c r="BD5" s="3"/>
-      <c r="BE5" s="3"/>
-      <c r="BF5" s="3"/>
-      <c r="BG5" s="3"/>
-      <c r="BH5" s="3"/>
-      <c r="BI5" s="3"/>
-      <c r="BJ5" s="3"/>
-      <c r="BK5" s="3"/>
-      <c r="BL5" s="3"/>
-      <c r="BM5" s="3"/>
-      <c r="BN5" s="3"/>
-      <c r="BO5" s="42" t="s">
+    <row r="5" spans="1:374" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="75"/>
+      <c r="B5" s="75"/>
+      <c r="C5" s="76"/>
+      <c r="D5" s="76"/>
+      <c r="E5" s="76"/>
+      <c r="F5" s="76"/>
+      <c r="G5" s="76"/>
+      <c r="H5" s="76"/>
+      <c r="I5" s="77"/>
+      <c r="J5" s="77"/>
+      <c r="K5" s="77"/>
+      <c r="L5" s="77"/>
+      <c r="M5" s="77"/>
+      <c r="N5" s="68"/>
+      <c r="O5" s="68"/>
+      <c r="P5" s="68"/>
+      <c r="Q5" s="69"/>
+      <c r="R5" s="69"/>
+      <c r="S5" s="69"/>
+      <c r="T5" s="69"/>
+      <c r="U5" s="69"/>
+      <c r="V5" s="70"/>
+      <c r="W5" s="70"/>
+      <c r="X5" s="70"/>
+      <c r="Y5" s="70"/>
+      <c r="Z5" s="70"/>
+      <c r="AA5" s="70"/>
+      <c r="AB5" s="70"/>
+      <c r="AC5" s="71"/>
+      <c r="AD5" s="71"/>
+      <c r="AE5" s="71"/>
+      <c r="AF5" s="72"/>
+      <c r="AG5" s="72"/>
+      <c r="AH5" s="66"/>
+      <c r="AI5" s="66"/>
+      <c r="AJ5" s="66"/>
+      <c r="AK5" s="66"/>
+      <c r="AL5" s="66"/>
+      <c r="AM5" s="67"/>
+      <c r="AN5" s="67"/>
+      <c r="AO5" s="67"/>
+      <c r="AP5" s="67"/>
+      <c r="AQ5" s="67"/>
+      <c r="AR5" s="67"/>
+      <c r="AS5" s="67"/>
+      <c r="AT5" s="67"/>
+      <c r="AU5" s="67"/>
+      <c r="AV5" s="67"/>
+      <c r="AW5" s="67"/>
+      <c r="AX5" s="67"/>
+      <c r="AY5" s="67"/>
+      <c r="AZ5" s="67"/>
+      <c r="BA5" s="67"/>
+      <c r="BB5" s="67"/>
+      <c r="BC5" s="67"/>
+      <c r="BD5" s="67"/>
+      <c r="BE5" s="67"/>
+      <c r="BF5" s="67"/>
+      <c r="BG5" s="67"/>
+      <c r="BH5" s="67"/>
+      <c r="BI5" s="67"/>
+      <c r="BJ5" s="67"/>
+      <c r="BK5" s="67"/>
+      <c r="BL5" s="67"/>
+      <c r="BM5" s="67"/>
+      <c r="BN5" s="67"/>
+      <c r="BO5" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="BP5" s="42" t="s">
+      <c r="BP5" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="BQ5" s="42" t="s">
+      <c r="BQ5" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="BR5" s="42" t="s">
+      <c r="BR5" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="BS5" s="43" t="s">
+      <c r="BS5" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="BT5" s="43" t="s">
+      <c r="BT5" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="BU5" s="43" t="s">
+      <c r="BU5" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="BV5" s="43" t="s">
+      <c r="BV5" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="BW5" s="43" t="s">
+      <c r="BW5" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="BX5" s="43" t="s">
+      <c r="BX5" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="BY5" s="42" t="s">
+      <c r="BY5" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="BZ5" s="42" t="s">
+      <c r="BZ5" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="CA5" s="42" t="s">
+      <c r="CA5" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="CB5" s="42" t="s">
+      <c r="CB5" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="CC5" s="43" t="s">
+      <c r="CC5" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="CD5" s="43" t="s">
+      <c r="CD5" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="CE5" s="43" t="s">
+      <c r="CE5" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="CF5" s="43" t="s">
+      <c r="CF5" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="CG5" s="43" t="s">
+      <c r="CG5" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="CH5" s="43" t="s">
+      <c r="CH5" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="CI5" s="42" t="s">
+      <c r="CI5" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="CJ5" s="42" t="s">
+      <c r="CJ5" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="CK5" s="42" t="s">
+      <c r="CK5" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="CL5" s="42" t="s">
+      <c r="CL5" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="CM5" s="43" t="s">
+      <c r="CM5" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="CN5" s="43" t="s">
+      <c r="CN5" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="CO5" s="43" t="s">
+      <c r="CO5" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="CP5" s="43" t="s">
+      <c r="CP5" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="CQ5" s="43" t="s">
+      <c r="CQ5" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="CR5" s="43" t="s">
+      <c r="CR5" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="CS5" s="42" t="s">
+      <c r="CS5" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="CT5" s="42" t="s">
+      <c r="CT5" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="CU5" s="42" t="s">
+      <c r="CU5" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="CV5" s="42" t="s">
+      <c r="CV5" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="CW5" s="43" t="s">
+      <c r="CW5" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="CX5" s="43" t="s">
+      <c r="CX5" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="CY5" s="43" t="s">
+      <c r="CY5" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="CZ5" s="43" t="s">
+      <c r="CZ5" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="DA5" s="43" t="s">
+      <c r="DA5" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="DB5" s="43" t="s">
+      <c r="DB5" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="DC5" s="42" t="s">
+      <c r="DC5" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="DD5" s="42" t="s">
+      <c r="DD5" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="DE5" s="42" t="s">
+      <c r="DE5" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="DF5" s="42" t="s">
+      <c r="DF5" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="DG5" s="43" t="s">
+      <c r="DG5" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="DH5" s="43" t="s">
+      <c r="DH5" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="DI5" s="43" t="s">
+      <c r="DI5" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="DJ5" s="43" t="s">
+      <c r="DJ5" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="DK5" s="43" t="s">
+      <c r="DK5" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="DL5" s="43" t="s">
+      <c r="DL5" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="DM5" s="42" t="s">
+      <c r="DM5" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="DN5" s="42" t="s">
+      <c r="DN5" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="DO5" s="42" t="s">
+      <c r="DO5" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="DP5" s="42" t="s">
+      <c r="DP5" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="DQ5" s="43" t="s">
+      <c r="DQ5" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="DR5" s="43" t="s">
+      <c r="DR5" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="DS5" s="43" t="s">
+      <c r="DS5" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="DT5" s="43" t="s">
+      <c r="DT5" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="DU5" s="43" t="s">
+      <c r="DU5" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="DV5" s="43" t="s">
+      <c r="DV5" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="DW5" s="42" t="s">
+      <c r="DW5" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="DX5" s="42" t="s">
+      <c r="DX5" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="DY5" s="42" t="s">
+      <c r="DY5" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="DZ5" s="42" t="s">
+      <c r="DZ5" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="EA5" s="43" t="s">
+      <c r="EA5" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="EB5" s="43" t="s">
+      <c r="EB5" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="EC5" s="43" t="s">
+      <c r="EC5" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="ED5" s="43" t="s">
+      <c r="ED5" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="EE5" s="43" t="s">
+      <c r="EE5" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="EF5" s="43" t="s">
+      <c r="EF5" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="EG5" s="42" t="s">
+      <c r="EG5" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="EH5" s="42" t="s">
+      <c r="EH5" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="EI5" s="42" t="s">
+      <c r="EI5" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="EJ5" s="42" t="s">
+      <c r="EJ5" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="EK5" s="43" t="s">
+      <c r="EK5" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="EL5" s="43" t="s">
+      <c r="EL5" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="EM5" s="43" t="s">
+      <c r="EM5" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="EN5" s="43" t="s">
+      <c r="EN5" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="EO5" s="43" t="s">
+      <c r="EO5" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="EP5" s="43" t="s">
+      <c r="EP5" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="EQ5" s="42" t="s">
+      <c r="EQ5" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="ER5" s="42" t="s">
+      <c r="ER5" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="ES5" s="42" t="s">
+      <c r="ES5" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="ET5" s="42" t="s">
+      <c r="ET5" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="EU5" s="43" t="s">
+      <c r="EU5" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="EV5" s="43" t="s">
+      <c r="EV5" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="EW5" s="43" t="s">
+      <c r="EW5" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="EX5" s="43" t="s">
+      <c r="EX5" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="EY5" s="43" t="s">
+      <c r="EY5" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="EZ5" s="43" t="s">
+      <c r="EZ5" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="FA5" s="42" t="s">
+      <c r="FA5" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="FB5" s="42" t="s">
+      <c r="FB5" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="FC5" s="42" t="s">
+      <c r="FC5" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="FD5" s="42" t="s">
+      <c r="FD5" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="FE5" s="43" t="s">
+      <c r="FE5" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="FF5" s="43" t="s">
+      <c r="FF5" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="FG5" s="43" t="s">
+      <c r="FG5" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="FH5" s="43" t="s">
+      <c r="FH5" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="FI5" s="43" t="s">
+      <c r="FI5" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="FJ5" s="43" t="s">
+      <c r="FJ5" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="FK5" s="42" t="s">
+      <c r="FK5" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="FL5" s="42" t="s">
+      <c r="FL5" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="FM5" s="42" t="s">
+      <c r="FM5" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="FN5" s="42" t="s">
+      <c r="FN5" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="FO5" s="43" t="s">
+      <c r="FO5" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="FP5" s="43" t="s">
+      <c r="FP5" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="FQ5" s="43" t="s">
+      <c r="FQ5" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="FR5" s="43" t="s">
+      <c r="FR5" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="FS5" s="43" t="s">
+      <c r="FS5" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="FT5" s="43" t="s">
+      <c r="FT5" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="FU5" s="42" t="s">
+      <c r="FU5" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="FV5" s="42" t="s">
+      <c r="FV5" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="FW5" s="42" t="s">
+      <c r="FW5" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="FX5" s="42" t="s">
+      <c r="FX5" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="FY5" s="43" t="s">
+      <c r="FY5" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="FZ5" s="43" t="s">
+      <c r="FZ5" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="GA5" s="43" t="s">
+      <c r="GA5" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="GB5" s="43" t="s">
+      <c r="GB5" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="GC5" s="43" t="s">
+      <c r="GC5" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="GD5" s="43" t="s">
+      <c r="GD5" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="GE5" s="42" t="s">
+      <c r="GE5" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="GF5" s="42" t="s">
+      <c r="GF5" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="GG5" s="42" t="s">
+      <c r="GG5" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="GH5" s="42" t="s">
+      <c r="GH5" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="GI5" s="43" t="s">
+      <c r="GI5" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="GJ5" s="43" t="s">
+      <c r="GJ5" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="GK5" s="43" t="s">
+      <c r="GK5" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="GL5" s="43" t="s">
+      <c r="GL5" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="GM5" s="43" t="s">
+      <c r="GM5" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="GN5" s="43" t="s">
+      <c r="GN5" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="GO5" s="42" t="s">
+      <c r="GO5" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="GP5" s="42" t="s">
+      <c r="GP5" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="GQ5" s="42" t="s">
+      <c r="GQ5" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="GR5" s="42" t="s">
+      <c r="GR5" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="GS5" s="43" t="s">
+      <c r="GS5" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="GT5" s="43" t="s">
+      <c r="GT5" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="GU5" s="43" t="s">
+      <c r="GU5" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="GV5" s="43" t="s">
+      <c r="GV5" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="GW5" s="43" t="s">
+      <c r="GW5" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="GX5" s="43" t="s">
+      <c r="GX5" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="GY5" s="42" t="s">
+      <c r="GY5" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="GZ5" s="42" t="s">
+      <c r="GZ5" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="HA5" s="42" t="s">
+      <c r="HA5" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="HB5" s="42" t="s">
+      <c r="HB5" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="HC5" s="43" t="s">
+      <c r="HC5" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="HD5" s="43" t="s">
+      <c r="HD5" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="HE5" s="43" t="s">
+      <c r="HE5" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="HF5" s="43" t="s">
+      <c r="HF5" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="HG5" s="43" t="s">
+      <c r="HG5" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="HH5" s="43" t="s">
+      <c r="HH5" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="HI5" s="42" t="s">
+      <c r="HI5" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="HJ5" s="42" t="s">
+      <c r="HJ5" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="HK5" s="42" t="s">
+      <c r="HK5" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="HL5" s="42" t="s">
+      <c r="HL5" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="HM5" s="43" t="s">
+      <c r="HM5" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="HN5" s="43" t="s">
+      <c r="HN5" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="HO5" s="43" t="s">
+      <c r="HO5" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="HP5" s="43" t="s">
+      <c r="HP5" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="HQ5" s="43" t="s">
+      <c r="HQ5" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="HR5" s="43" t="s">
+      <c r="HR5" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="HS5" s="42" t="s">
+      <c r="HS5" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="HT5" s="42" t="s">
+      <c r="HT5" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="HU5" s="42" t="s">
+      <c r="HU5" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="HV5" s="42" t="s">
+      <c r="HV5" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="HW5" s="43" t="s">
+      <c r="HW5" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="HX5" s="43" t="s">
+      <c r="HX5" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="HY5" s="43" t="s">
+      <c r="HY5" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="HZ5" s="43" t="s">
+      <c r="HZ5" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="IA5" s="43" t="s">
+      <c r="IA5" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="IB5" s="43" t="s">
+      <c r="IB5" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="IC5" s="42" t="s">
+      <c r="IC5" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="ID5" s="42" t="s">
+      <c r="ID5" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="IE5" s="42" t="s">
+      <c r="IE5" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="IF5" s="42" t="s">
+      <c r="IF5" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="IG5" s="43" t="s">
+      <c r="IG5" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="IH5" s="43" t="s">
+      <c r="IH5" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="II5" s="43" t="s">
+      <c r="II5" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="IJ5" s="43" t="s">
+      <c r="IJ5" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="IK5" s="43" t="s">
+      <c r="IK5" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="IL5" s="43" t="s">
+      <c r="IL5" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="IM5" s="42" t="s">
+      <c r="IM5" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="IN5" s="42" t="s">
+      <c r="IN5" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="IO5" s="42" t="s">
+      <c r="IO5" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="IP5" s="42" t="s">
+      <c r="IP5" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="IQ5" s="43" t="s">
+      <c r="IQ5" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="IR5" s="43" t="s">
+      <c r="IR5" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="IS5" s="43" t="s">
+      <c r="IS5" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="IT5" s="43" t="s">
+      <c r="IT5" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="IU5" s="43" t="s">
+      <c r="IU5" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="IV5" s="43" t="s">
+      <c r="IV5" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="IW5" s="42" t="s">
+      <c r="IW5" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="IX5" s="42" t="s">
+      <c r="IX5" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="IY5" s="42" t="s">
+      <c r="IY5" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="IZ5" s="42" t="s">
+      <c r="IZ5" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="JA5" s="43" t="s">
+      <c r="JA5" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="JB5" s="43" t="s">
+      <c r="JB5" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="JC5" s="43" t="s">
+      <c r="JC5" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="JD5" s="43" t="s">
+      <c r="JD5" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="JE5" s="43" t="s">
+      <c r="JE5" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="JF5" s="43" t="s">
+      <c r="JF5" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="JG5" s="42" t="s">
+      <c r="JG5" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="JH5" s="42" t="s">
+      <c r="JH5" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="JI5" s="42" t="s">
+      <c r="JI5" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="JJ5" s="42" t="s">
+      <c r="JJ5" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="JK5" s="43" t="s">
+      <c r="JK5" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="JL5" s="43" t="s">
+      <c r="JL5" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="JM5" s="43" t="s">
+      <c r="JM5" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="JN5" s="43" t="s">
+      <c r="JN5" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="JO5" s="43" t="s">
+      <c r="JO5" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="JP5" s="43" t="s">
+      <c r="JP5" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="JQ5" s="42" t="s">
+      <c r="JQ5" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="JR5" s="42" t="s">
+      <c r="JR5" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="JS5" s="42" t="s">
+      <c r="JS5" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="JT5" s="42" t="s">
+      <c r="JT5" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="JU5" s="43" t="s">
+      <c r="JU5" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="JV5" s="43" t="s">
+      <c r="JV5" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="JW5" s="43" t="s">
+      <c r="JW5" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="JX5" s="43" t="s">
+      <c r="JX5" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="JY5" s="43" t="s">
+      <c r="JY5" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="JZ5" s="43" t="s">
+      <c r="JZ5" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="KA5" s="42" t="s">
+      <c r="KA5" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="KB5" s="42" t="s">
+      <c r="KB5" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="KC5" s="42" t="s">
+      <c r="KC5" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="KD5" s="42" t="s">
+      <c r="KD5" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="KE5" s="43" t="s">
+      <c r="KE5" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="KF5" s="43" t="s">
+      <c r="KF5" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="KG5" s="43" t="s">
+      <c r="KG5" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="KH5" s="43" t="s">
+      <c r="KH5" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="KI5" s="43" t="s">
+      <c r="KI5" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="KJ5" s="43" t="s">
+      <c r="KJ5" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="KK5" s="42" t="s">
+      <c r="KK5" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="KL5" s="42" t="s">
+      <c r="KL5" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="KM5" s="42" t="s">
+      <c r="KM5" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="KN5" s="42" t="s">
+      <c r="KN5" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="KO5" s="43" t="s">
+      <c r="KO5" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="KP5" s="43" t="s">
+      <c r="KP5" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="KQ5" s="43" t="s">
+      <c r="KQ5" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="KR5" s="43" t="s">
+      <c r="KR5" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="KS5" s="43" t="s">
+      <c r="KS5" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="KT5" s="43" t="s">
+      <c r="KT5" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="KU5" s="42" t="s">
+      <c r="KU5" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="KV5" s="42" t="s">
+      <c r="KV5" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="KW5" s="42" t="s">
+      <c r="KW5" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="KX5" s="42" t="s">
+      <c r="KX5" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="KY5" s="43" t="s">
+      <c r="KY5" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="KZ5" s="43" t="s">
+      <c r="KZ5" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="LA5" s="43" t="s">
+      <c r="LA5" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="LB5" s="43" t="s">
+      <c r="LB5" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="LC5" s="43" t="s">
+      <c r="LC5" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="LD5" s="43" t="s">
+      <c r="LD5" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="LE5" s="42" t="s">
+      <c r="LE5" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="LF5" s="42" t="s">
+      <c r="LF5" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="LG5" s="42" t="s">
+      <c r="LG5" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="LH5" s="42" t="s">
+      <c r="LH5" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="LI5" s="43" t="s">
+      <c r="LI5" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="LJ5" s="43" t="s">
+      <c r="LJ5" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="LK5" s="43" t="s">
+      <c r="LK5" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="LL5" s="43" t="s">
+      <c r="LL5" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="LM5" s="43" t="s">
+      <c r="LM5" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="LN5" s="43" t="s">
+      <c r="LN5" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="LO5" s="42" t="s">
+      <c r="LO5" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="LP5" s="42" t="s">
+      <c r="LP5" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="LQ5" s="42" t="s">
+      <c r="LQ5" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="LR5" s="42" t="s">
+      <c r="LR5" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="LS5" s="43" t="s">
+      <c r="LS5" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="LT5" s="43" t="s">
+      <c r="LT5" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="LU5" s="43" t="s">
+      <c r="LU5" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="LV5" s="43" t="s">
+      <c r="LV5" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="LW5" s="43" t="s">
+      <c r="LW5" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="LX5" s="43" t="s">
+      <c r="LX5" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="LY5" s="42" t="s">
+      <c r="LY5" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="LZ5" s="42" t="s">
+      <c r="LZ5" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="MA5" s="42" t="s">
+      <c r="MA5" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="MB5" s="42" t="s">
+      <c r="MB5" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="MC5" s="43" t="s">
+      <c r="MC5" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="MD5" s="43" t="s">
+      <c r="MD5" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="ME5" s="43" t="s">
+      <c r="ME5" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="MF5" s="43" t="s">
+      <c r="MF5" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="MG5" s="43" t="s">
+      <c r="MG5" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="MH5" s="43" t="s">
+      <c r="MH5" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="MI5" s="76"/>
-      <c r="MJ5" s="76"/>
-      <c r="MK5" s="76"/>
-      <c r="ML5" s="76"/>
-      <c r="MM5" s="76"/>
-      <c r="MN5" s="76"/>
-      <c r="MO5" s="76"/>
-      <c r="MP5" s="76"/>
-      <c r="MQ5" s="76"/>
-      <c r="MR5" s="76"/>
-      <c r="MS5" s="76"/>
-      <c r="MT5" s="76"/>
-      <c r="MU5" s="76"/>
-      <c r="MV5" s="76"/>
-      <c r="MW5" s="77"/>
-      <c r="MX5" s="77"/>
-      <c r="MY5" s="77"/>
-      <c r="MZ5" s="40"/>
-      <c r="NA5" s="77"/>
-      <c r="NB5" s="77"/>
-      <c r="NC5" s="77"/>
-      <c r="ND5" s="77"/>
-      <c r="NE5" s="77"/>
-      <c r="NF5" s="77"/>
-      <c r="NG5" s="78"/>
-      <c r="NH5" s="78"/>
-      <c r="NI5" s="44"/>
+      <c r="MI5" s="54"/>
+      <c r="MJ5" s="54"/>
+      <c r="MK5" s="54"/>
+      <c r="ML5" s="54"/>
+      <c r="MM5" s="54"/>
+      <c r="MN5" s="54"/>
+      <c r="MO5" s="54"/>
+      <c r="MP5" s="54"/>
+      <c r="MQ5" s="54"/>
+      <c r="MR5" s="54"/>
+      <c r="MS5" s="54"/>
+      <c r="MT5" s="54"/>
+      <c r="MU5" s="54"/>
+      <c r="MV5" s="54"/>
+      <c r="MW5" s="55"/>
+      <c r="MX5" s="55"/>
+      <c r="MY5" s="55"/>
+      <c r="MZ5" s="26"/>
+      <c r="NA5" s="55"/>
+      <c r="NB5" s="55"/>
+      <c r="NC5" s="55"/>
+      <c r="ND5" s="55"/>
+      <c r="NE5" s="55"/>
+      <c r="NF5" s="55"/>
+      <c r="NG5" s="82"/>
+      <c r="NH5" s="85"/>
+      <c r="NI5" s="83"/>
+      <c r="NJ5" s="30"/>
     </row>
-    <row r="6" spans="1:373" ht="81.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="45" t="s">
+    <row r="6" spans="1:374" ht="81.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="B6" s="46" t="s">
+      <c r="B6" s="32" t="s">
         <v>49</v>
       </c>
-      <c r="C6" s="45" t="s">
+      <c r="C6" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="D6" s="45" t="s">
+      <c r="D6" s="31" t="s">
         <v>51</v>
       </c>
-      <c r="E6" s="45" t="s">
+      <c r="E6" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="F6" s="47" t="s">
+      <c r="F6" s="33" t="s">
         <v>53</v>
       </c>
-      <c r="G6" s="47" t="s">
+      <c r="G6" s="33" t="s">
         <v>54</v>
       </c>
-      <c r="H6" s="47" t="s">
+      <c r="H6" s="33" t="s">
         <v>55</v>
       </c>
-      <c r="I6" s="45" t="s">
+      <c r="I6" s="31" t="s">
         <v>56</v>
       </c>
-      <c r="J6" s="45" t="s">
+      <c r="J6" s="31" t="s">
         <v>57</v>
       </c>
-      <c r="K6" s="45" t="s">
+      <c r="K6" s="31" t="s">
         <v>58</v>
       </c>
-      <c r="L6" s="45" t="s">
+      <c r="L6" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="M6" s="45" t="s">
+      <c r="M6" s="31" t="s">
         <v>60</v>
       </c>
-      <c r="N6" s="48" t="s">
+      <c r="N6" s="34" t="s">
         <v>61</v>
       </c>
-      <c r="O6" s="49" t="s">
+      <c r="O6" s="35" t="s">
         <v>62</v>
       </c>
-      <c r="P6" s="48" t="s">
+      <c r="P6" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="Q6" s="50" t="s">
+      <c r="Q6" s="36" t="s">
         <v>64</v>
       </c>
-      <c r="R6" s="51" t="s">
+      <c r="R6" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="S6" s="51" t="s">
+      <c r="S6" s="37" t="s">
         <v>66</v>
       </c>
-      <c r="T6" s="45" t="s">
+      <c r="T6" s="31" t="s">
         <v>67</v>
       </c>
-      <c r="U6" s="45" t="s">
+      <c r="U6" s="31" t="s">
         <v>68</v>
       </c>
-      <c r="V6" s="45" t="s">
+      <c r="V6" s="31" t="s">
         <v>69</v>
       </c>
-      <c r="W6" s="51" t="s">
+      <c r="W6" s="37" t="s">
         <v>70</v>
       </c>
-      <c r="X6" s="51" t="s">
+      <c r="X6" s="37" t="s">
         <v>71</v>
       </c>
-      <c r="Y6" s="45" t="s">
+      <c r="Y6" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="Z6" s="45" t="s">
+      <c r="Z6" s="31" t="s">
         <v>73</v>
       </c>
-      <c r="AA6" s="45" t="s">
+      <c r="AA6" s="31" t="s">
         <v>74</v>
       </c>
-      <c r="AB6" s="45" t="s">
+      <c r="AB6" s="31" t="s">
         <v>75</v>
       </c>
-      <c r="AC6" s="45" t="s">
+      <c r="AC6" s="31" t="s">
         <v>76</v>
       </c>
-      <c r="AD6" s="45" t="s">
+      <c r="AD6" s="31" t="s">
         <v>77</v>
       </c>
-      <c r="AE6" s="45" t="s">
+      <c r="AE6" s="31" t="s">
         <v>78</v>
       </c>
-      <c r="AF6" s="45" t="s">
+      <c r="AF6" s="31" t="s">
         <v>79</v>
       </c>
-      <c r="AG6" s="52" t="s">
+      <c r="AG6" s="38" t="s">
         <v>80</v>
       </c>
-      <c r="AH6" s="53" t="s">
+      <c r="AH6" s="39" t="s">
         <v>81</v>
       </c>
-      <c r="AI6" s="53" t="s">
+      <c r="AI6" s="39" t="s">
         <v>82</v>
       </c>
-      <c r="AJ6" s="53" t="s">
+      <c r="AJ6" s="39" t="s">
         <v>83</v>
       </c>
-      <c r="AK6" s="53" t="s">
+      <c r="AK6" s="39" t="s">
         <v>84</v>
       </c>
-      <c r="AL6" s="53" t="s">
+      <c r="AL6" s="39" t="s">
         <v>85</v>
       </c>
-      <c r="AM6" s="54" t="s">
+      <c r="AM6" s="40" t="s">
         <v>86</v>
       </c>
-      <c r="AN6" s="54" t="s">
+      <c r="AN6" s="40" t="s">
         <v>87</v>
       </c>
-      <c r="AO6" s="54" t="s">
+      <c r="AO6" s="40" t="s">
         <v>88</v>
       </c>
-      <c r="AP6" s="54" t="s">
+      <c r="AP6" s="40" t="s">
         <v>89</v>
       </c>
-      <c r="AQ6" s="54" t="s">
+      <c r="AQ6" s="40" t="s">
         <v>90</v>
       </c>
-      <c r="AR6" s="54" t="s">
+      <c r="AR6" s="40" t="s">
         <v>91</v>
       </c>
-      <c r="AS6" s="54" t="s">
+      <c r="AS6" s="40" t="s">
         <v>92</v>
       </c>
-      <c r="AT6" s="54" t="s">
+      <c r="AT6" s="40" t="s">
         <v>93</v>
       </c>
-      <c r="AU6" s="54" t="s">
+      <c r="AU6" s="40" t="s">
         <v>94</v>
       </c>
-      <c r="AV6" s="54" t="s">
+      <c r="AV6" s="40" t="s">
         <v>95</v>
       </c>
-      <c r="AW6" s="54" t="s">
+      <c r="AW6" s="40" t="s">
         <v>96</v>
       </c>
-      <c r="AX6" s="54" t="s">
+      <c r="AX6" s="40" t="s">
         <v>97</v>
       </c>
-      <c r="AY6" s="54" t="s">
+      <c r="AY6" s="40" t="s">
         <v>98</v>
       </c>
-      <c r="AZ6" s="54" t="s">
+      <c r="AZ6" s="40" t="s">
         <v>99</v>
       </c>
-      <c r="BA6" s="54" t="s">
+      <c r="BA6" s="40" t="s">
         <v>100</v>
       </c>
-      <c r="BB6" s="54" t="s">
+      <c r="BB6" s="40" t="s">
         <v>101</v>
       </c>
-      <c r="BC6" s="54" t="s">
+      <c r="BC6" s="40" t="s">
         <v>102</v>
       </c>
-      <c r="BD6" s="54" t="s">
+      <c r="BD6" s="40" t="s">
         <v>103</v>
       </c>
-      <c r="BE6" s="54" t="s">
+      <c r="BE6" s="40" t="s">
         <v>104</v>
       </c>
-      <c r="BF6" s="54" t="s">
+      <c r="BF6" s="40" t="s">
         <v>105</v>
       </c>
-      <c r="BG6" s="54" t="s">
+      <c r="BG6" s="40" t="s">
         <v>106</v>
       </c>
-      <c r="BH6" s="54" t="s">
+      <c r="BH6" s="40" t="s">
         <v>107</v>
       </c>
-      <c r="BI6" s="54" t="s">
+      <c r="BI6" s="40" t="s">
         <v>108</v>
       </c>
-      <c r="BJ6" s="54" t="s">
+      <c r="BJ6" s="40" t="s">
         <v>109</v>
       </c>
-      <c r="BK6" s="54" t="s">
+      <c r="BK6" s="40" t="s">
         <v>110</v>
       </c>
-      <c r="BL6" s="54" t="s">
+      <c r="BL6" s="40" t="s">
         <v>111</v>
       </c>
-      <c r="BM6" s="54" t="s">
+      <c r="BM6" s="40" t="s">
         <v>112</v>
       </c>
-      <c r="BN6" s="54" t="s">
+      <c r="BN6" s="40" t="s">
         <v>113</v>
       </c>
-      <c r="BO6" s="54" t="s">
+      <c r="BO6" s="40" t="s">
         <v>114</v>
       </c>
-      <c r="BP6" s="54" t="s">
+      <c r="BP6" s="40" t="s">
         <v>115</v>
       </c>
-      <c r="BQ6" s="54" t="s">
+      <c r="BQ6" s="40" t="s">
         <v>116</v>
       </c>
-      <c r="BR6" s="54" t="s">
+      <c r="BR6" s="40" t="s">
         <v>117</v>
       </c>
-      <c r="BS6" s="54" t="s">
+      <c r="BS6" s="40" t="s">
         <v>118</v>
       </c>
-      <c r="BT6" s="54" t="s">
+      <c r="BT6" s="40" t="s">
         <v>119</v>
       </c>
-      <c r="BU6" s="54" t="s">
+      <c r="BU6" s="40" t="s">
         <v>120</v>
       </c>
-      <c r="BV6" s="54" t="s">
+      <c r="BV6" s="40" t="s">
         <v>121</v>
       </c>
-      <c r="BW6" s="54" t="s">
+      <c r="BW6" s="40" t="s">
         <v>122</v>
       </c>
-      <c r="BX6" s="54" t="s">
+      <c r="BX6" s="40" t="s">
         <v>123</v>
       </c>
-      <c r="BY6" s="54" t="s">
+      <c r="BY6" s="40" t="s">
         <v>124</v>
       </c>
-      <c r="BZ6" s="54" t="s">
+      <c r="BZ6" s="40" t="s">
         <v>125</v>
       </c>
-      <c r="CA6" s="54" t="s">
+      <c r="CA6" s="40" t="s">
         <v>126</v>
       </c>
-      <c r="CB6" s="54" t="s">
+      <c r="CB6" s="40" t="s">
         <v>127</v>
       </c>
-      <c r="CC6" s="54" t="s">
+      <c r="CC6" s="40" t="s">
         <v>128</v>
       </c>
-      <c r="CD6" s="54" t="s">
+      <c r="CD6" s="40" t="s">
         <v>129</v>
       </c>
-      <c r="CE6" s="54" t="s">
+      <c r="CE6" s="40" t="s">
         <v>130</v>
       </c>
-      <c r="CF6" s="54" t="s">
+      <c r="CF6" s="40" t="s">
         <v>131</v>
       </c>
-      <c r="CG6" s="54" t="s">
+      <c r="CG6" s="40" t="s">
         <v>132</v>
       </c>
-      <c r="CH6" s="54" t="s">
+      <c r="CH6" s="40" t="s">
         <v>133</v>
       </c>
-      <c r="CI6" s="54" t="s">
+      <c r="CI6" s="40" t="s">
         <v>134</v>
       </c>
-      <c r="CJ6" s="54" t="s">
+      <c r="CJ6" s="40" t="s">
         <v>135</v>
       </c>
-      <c r="CK6" s="54" t="s">
+      <c r="CK6" s="40" t="s">
         <v>136</v>
       </c>
-      <c r="CL6" s="54" t="s">
+      <c r="CL6" s="40" t="s">
         <v>137</v>
       </c>
-      <c r="CM6" s="54" t="s">
+      <c r="CM6" s="40" t="s">
         <v>138</v>
       </c>
-      <c r="CN6" s="54" t="s">
+      <c r="CN6" s="40" t="s">
         <v>139</v>
       </c>
-      <c r="CO6" s="54" t="s">
+      <c r="CO6" s="40" t="s">
         <v>140</v>
       </c>
-      <c r="CP6" s="54" t="s">
+      <c r="CP6" s="40" t="s">
         <v>141</v>
       </c>
-      <c r="CQ6" s="54" t="s">
+      <c r="CQ6" s="40" t="s">
         <v>142</v>
       </c>
-      <c r="CR6" s="54" t="s">
+      <c r="CR6" s="40" t="s">
         <v>143</v>
       </c>
-      <c r="CS6" s="54" t="s">
+      <c r="CS6" s="40" t="s">
         <v>144</v>
       </c>
-      <c r="CT6" s="54" t="s">
+      <c r="CT6" s="40" t="s">
         <v>145</v>
       </c>
-      <c r="CU6" s="54" t="s">
+      <c r="CU6" s="40" t="s">
         <v>146</v>
       </c>
-      <c r="CV6" s="54" t="s">
+      <c r="CV6" s="40" t="s">
         <v>147</v>
       </c>
-      <c r="CW6" s="54" t="s">
+      <c r="CW6" s="40" t="s">
         <v>148</v>
       </c>
-      <c r="CX6" s="54" t="s">
+      <c r="CX6" s="40" t="s">
         <v>149</v>
       </c>
-      <c r="CY6" s="54" t="s">
+      <c r="CY6" s="40" t="s">
         <v>150</v>
       </c>
-      <c r="CZ6" s="54" t="s">
+      <c r="CZ6" s="40" t="s">
         <v>151</v>
       </c>
-      <c r="DA6" s="54" t="s">
+      <c r="DA6" s="40" t="s">
         <v>152</v>
       </c>
-      <c r="DB6" s="54" t="s">
+      <c r="DB6" s="40" t="s">
         <v>153</v>
       </c>
-      <c r="DC6" s="54" t="s">
+      <c r="DC6" s="40" t="s">
         <v>154</v>
       </c>
-      <c r="DD6" s="54" t="s">
+      <c r="DD6" s="40" t="s">
         <v>155</v>
       </c>
-      <c r="DE6" s="54" t="s">
+      <c r="DE6" s="40" t="s">
         <v>156</v>
       </c>
-      <c r="DF6" s="54" t="s">
+      <c r="DF6" s="40" t="s">
         <v>157</v>
       </c>
-      <c r="DG6" s="54" t="s">
+      <c r="DG6" s="40" t="s">
         <v>158</v>
       </c>
-      <c r="DH6" s="54" t="s">
+      <c r="DH6" s="40" t="s">
         <v>159</v>
       </c>
-      <c r="DI6" s="54" t="s">
+      <c r="DI6" s="40" t="s">
         <v>160</v>
       </c>
-      <c r="DJ6" s="54" t="s">
+      <c r="DJ6" s="40" t="s">
         <v>161</v>
       </c>
-      <c r="DK6" s="54" t="s">
+      <c r="DK6" s="40" t="s">
         <v>162</v>
       </c>
-      <c r="DL6" s="54" t="s">
+      <c r="DL6" s="40" t="s">
         <v>163</v>
       </c>
-      <c r="DM6" s="54" t="s">
+      <c r="DM6" s="40" t="s">
         <v>164</v>
       </c>
-      <c r="DN6" s="54" t="s">
+      <c r="DN6" s="40" t="s">
         <v>165</v>
       </c>
-      <c r="DO6" s="54" t="s">
+      <c r="DO6" s="40" t="s">
         <v>166</v>
       </c>
-      <c r="DP6" s="54" t="s">
+      <c r="DP6" s="40" t="s">
         <v>167</v>
       </c>
-      <c r="DQ6" s="54" t="s">
+      <c r="DQ6" s="40" t="s">
         <v>168</v>
       </c>
-      <c r="DR6" s="54" t="s">
+      <c r="DR6" s="40" t="s">
         <v>169</v>
       </c>
-      <c r="DS6" s="54" t="s">
+      <c r="DS6" s="40" t="s">
         <v>170</v>
       </c>
-      <c r="DT6" s="54" t="s">
+      <c r="DT6" s="40" t="s">
         <v>171</v>
       </c>
-      <c r="DU6" s="54" t="s">
+      <c r="DU6" s="40" t="s">
         <v>172</v>
       </c>
-      <c r="DV6" s="54" t="s">
+      <c r="DV6" s="40" t="s">
         <v>173</v>
       </c>
-      <c r="DW6" s="54" t="s">
+      <c r="DW6" s="40" t="s">
         <v>174</v>
       </c>
-      <c r="DX6" s="54" t="s">
+      <c r="DX6" s="40" t="s">
         <v>175</v>
       </c>
-      <c r="DY6" s="54" t="s">
+      <c r="DY6" s="40" t="s">
         <v>176</v>
       </c>
-      <c r="DZ6" s="54" t="s">
+      <c r="DZ6" s="40" t="s">
         <v>177</v>
       </c>
-      <c r="EA6" s="54" t="s">
+      <c r="EA6" s="40" t="s">
         <v>178</v>
       </c>
-      <c r="EB6" s="54" t="s">
+      <c r="EB6" s="40" t="s">
         <v>179</v>
       </c>
-      <c r="EC6" s="54" t="s">
+      <c r="EC6" s="40" t="s">
         <v>180</v>
       </c>
-      <c r="ED6" s="54" t="s">
+      <c r="ED6" s="40" t="s">
         <v>181</v>
       </c>
-      <c r="EE6" s="54" t="s">
+      <c r="EE6" s="40" t="s">
         <v>182</v>
       </c>
-      <c r="EF6" s="54" t="s">
+      <c r="EF6" s="40" t="s">
         <v>183</v>
       </c>
-      <c r="EG6" s="54" t="s">
+      <c r="EG6" s="40" t="s">
         <v>184</v>
       </c>
-      <c r="EH6" s="54" t="s">
+      <c r="EH6" s="40" t="s">
         <v>185</v>
       </c>
-      <c r="EI6" s="54" t="s">
+      <c r="EI6" s="40" t="s">
         <v>186</v>
       </c>
-      <c r="EJ6" s="54" t="s">
+      <c r="EJ6" s="40" t="s">
         <v>187</v>
       </c>
-      <c r="EK6" s="54" t="s">
+      <c r="EK6" s="40" t="s">
         <v>188</v>
       </c>
-      <c r="EL6" s="54" t="s">
+      <c r="EL6" s="40" t="s">
         <v>189</v>
       </c>
-      <c r="EM6" s="54" t="s">
+      <c r="EM6" s="40" t="s">
         <v>190</v>
       </c>
-      <c r="EN6" s="54" t="s">
+      <c r="EN6" s="40" t="s">
         <v>191</v>
       </c>
-      <c r="EO6" s="54" t="s">
+      <c r="EO6" s="40" t="s">
         <v>192</v>
       </c>
-      <c r="EP6" s="54" t="s">
+      <c r="EP6" s="40" t="s">
         <v>193</v>
       </c>
-      <c r="EQ6" s="54" t="s">
+      <c r="EQ6" s="40" t="s">
         <v>194</v>
       </c>
-      <c r="ER6" s="54" t="s">
+      <c r="ER6" s="40" t="s">
         <v>195</v>
       </c>
-      <c r="ES6" s="54" t="s">
+      <c r="ES6" s="40" t="s">
         <v>196</v>
       </c>
-      <c r="ET6" s="54" t="s">
+      <c r="ET6" s="40" t="s">
         <v>197</v>
       </c>
-      <c r="EU6" s="54" t="s">
+      <c r="EU6" s="40" t="s">
         <v>198</v>
       </c>
-      <c r="EV6" s="54" t="s">
+      <c r="EV6" s="40" t="s">
         <v>199</v>
       </c>
-      <c r="EW6" s="54" t="s">
+      <c r="EW6" s="40" t="s">
         <v>200</v>
       </c>
-      <c r="EX6" s="54" t="s">
+      <c r="EX6" s="40" t="s">
         <v>201</v>
       </c>
-      <c r="EY6" s="54" t="s">
+      <c r="EY6" s="40" t="s">
         <v>202</v>
       </c>
-      <c r="EZ6" s="54" t="s">
+      <c r="EZ6" s="40" t="s">
         <v>203</v>
       </c>
-      <c r="FA6" s="54" t="s">
+      <c r="FA6" s="40" t="s">
         <v>204</v>
       </c>
-      <c r="FB6" s="54" t="s">
+      <c r="FB6" s="40" t="s">
         <v>205</v>
       </c>
-      <c r="FC6" s="54" t="s">
+      <c r="FC6" s="40" t="s">
         <v>206</v>
       </c>
-      <c r="FD6" s="54" t="s">
+      <c r="FD6" s="40" t="s">
         <v>207</v>
       </c>
-      <c r="FE6" s="54" t="s">
+      <c r="FE6" s="40" t="s">
         <v>208</v>
       </c>
-      <c r="FF6" s="54" t="s">
+      <c r="FF6" s="40" t="s">
         <v>209</v>
       </c>
-      <c r="FG6" s="54" t="s">
+      <c r="FG6" s="40" t="s">
         <v>210</v>
       </c>
-      <c r="FH6" s="54" t="s">
+      <c r="FH6" s="40" t="s">
         <v>211</v>
       </c>
-      <c r="FI6" s="54" t="s">
+      <c r="FI6" s="40" t="s">
         <v>212</v>
       </c>
-      <c r="FJ6" s="54" t="s">
+      <c r="FJ6" s="40" t="s">
         <v>213</v>
       </c>
-      <c r="FK6" s="54" t="s">
+      <c r="FK6" s="40" t="s">
         <v>214</v>
       </c>
-      <c r="FL6" s="54" t="s">
+      <c r="FL6" s="40" t="s">
         <v>215</v>
       </c>
-      <c r="FM6" s="54" t="s">
+      <c r="FM6" s="40" t="s">
         <v>216</v>
       </c>
-      <c r="FN6" s="54" t="s">
+      <c r="FN6" s="40" t="s">
         <v>217</v>
       </c>
-      <c r="FO6" s="54" t="s">
+      <c r="FO6" s="40" t="s">
         <v>218</v>
       </c>
-      <c r="FP6" s="54" t="s">
+      <c r="FP6" s="40" t="s">
         <v>219</v>
       </c>
-      <c r="FQ6" s="54" t="s">
+      <c r="FQ6" s="40" t="s">
         <v>220</v>
       </c>
-      <c r="FR6" s="54" t="s">
+      <c r="FR6" s="40" t="s">
         <v>221</v>
       </c>
-      <c r="FS6" s="54" t="s">
+      <c r="FS6" s="40" t="s">
         <v>222</v>
       </c>
-      <c r="FT6" s="54" t="s">
+      <c r="FT6" s="40" t="s">
         <v>223</v>
       </c>
-      <c r="FU6" s="45" t="s">
+      <c r="FU6" s="31" t="s">
         <v>224</v>
       </c>
-      <c r="FV6" s="45" t="s">
+      <c r="FV6" s="31" t="s">
         <v>225</v>
       </c>
-      <c r="FW6" s="45" t="s">
+      <c r="FW6" s="31" t="s">
         <v>226</v>
       </c>
-      <c r="FX6" s="45" t="s">
+      <c r="FX6" s="31" t="s">
         <v>227</v>
       </c>
-      <c r="FY6" s="45" t="s">
+      <c r="FY6" s="31" t="s">
         <v>228</v>
       </c>
-      <c r="FZ6" s="45" t="s">
+      <c r="FZ6" s="31" t="s">
         <v>229</v>
       </c>
-      <c r="GA6" s="45" t="s">
+      <c r="GA6" s="31" t="s">
         <v>230</v>
       </c>
-      <c r="GB6" s="45" t="s">
+      <c r="GB6" s="31" t="s">
         <v>231</v>
       </c>
-      <c r="GC6" s="45" t="s">
+      <c r="GC6" s="31" t="s">
         <v>232</v>
       </c>
-      <c r="GD6" s="45" t="s">
+      <c r="GD6" s="31" t="s">
         <v>233</v>
       </c>
-      <c r="GE6" s="45" t="s">
+      <c r="GE6" s="31" t="s">
         <v>234</v>
       </c>
-      <c r="GF6" s="45" t="s">
+      <c r="GF6" s="31" t="s">
         <v>235</v>
       </c>
-      <c r="GG6" s="45" t="s">
+      <c r="GG6" s="31" t="s">
         <v>236</v>
       </c>
-      <c r="GH6" s="45" t="s">
+      <c r="GH6" s="31" t="s">
         <v>237</v>
       </c>
-      <c r="GI6" s="45" t="s">
+      <c r="GI6" s="31" t="s">
         <v>238</v>
       </c>
-      <c r="GJ6" s="45" t="s">
+      <c r="GJ6" s="31" t="s">
         <v>239</v>
       </c>
-      <c r="GK6" s="45" t="s">
+      <c r="GK6" s="31" t="s">
         <v>240</v>
       </c>
-      <c r="GL6" s="45" t="s">
+      <c r="GL6" s="31" t="s">
         <v>241</v>
       </c>
-      <c r="GM6" s="45" t="s">
+      <c r="GM6" s="31" t="s">
         <v>242</v>
       </c>
-      <c r="GN6" s="45" t="s">
+      <c r="GN6" s="31" t="s">
         <v>243</v>
       </c>
-      <c r="GO6" s="45" t="s">
+      <c r="GO6" s="31" t="s">
         <v>244</v>
       </c>
-      <c r="GP6" s="45" t="s">
+      <c r="GP6" s="31" t="s">
         <v>245</v>
       </c>
-      <c r="GQ6" s="45" t="s">
+      <c r="GQ6" s="31" t="s">
         <v>246</v>
       </c>
-      <c r="GR6" s="45" t="s">
+      <c r="GR6" s="31" t="s">
         <v>247</v>
       </c>
-      <c r="GS6" s="45" t="s">
+      <c r="GS6" s="31" t="s">
         <v>248</v>
       </c>
-      <c r="GT6" s="45" t="s">
+      <c r="GT6" s="31" t="s">
         <v>249</v>
       </c>
-      <c r="GU6" s="45" t="s">
+      <c r="GU6" s="31" t="s">
         <v>250</v>
       </c>
-      <c r="GV6" s="45" t="s">
+      <c r="GV6" s="31" t="s">
         <v>251</v>
       </c>
-      <c r="GW6" s="45" t="s">
+      <c r="GW6" s="31" t="s">
         <v>252</v>
       </c>
-      <c r="GX6" s="45" t="s">
+      <c r="GX6" s="31" t="s">
         <v>253</v>
       </c>
-      <c r="GY6" s="54" t="s">
+      <c r="GY6" s="40" t="s">
         <v>254</v>
       </c>
-      <c r="GZ6" s="54" t="s">
+      <c r="GZ6" s="40" t="s">
         <v>255</v>
       </c>
-      <c r="HA6" s="54" t="s">
+      <c r="HA6" s="40" t="s">
         <v>256</v>
       </c>
-      <c r="HB6" s="54" t="s">
+      <c r="HB6" s="40" t="s">
         <v>257</v>
       </c>
-      <c r="HC6" s="54" t="s">
+      <c r="HC6" s="40" t="s">
         <v>258</v>
       </c>
-      <c r="HD6" s="54" t="s">
+      <c r="HD6" s="40" t="s">
         <v>259</v>
       </c>
-      <c r="HE6" s="54" t="s">
+      <c r="HE6" s="40" t="s">
         <v>260</v>
       </c>
-      <c r="HF6" s="54" t="s">
+      <c r="HF6" s="40" t="s">
         <v>261</v>
       </c>
-      <c r="HG6" s="54" t="s">
+      <c r="HG6" s="40" t="s">
         <v>262</v>
       </c>
-      <c r="HH6" s="54" t="s">
+      <c r="HH6" s="40" t="s">
         <v>263</v>
       </c>
-      <c r="HI6" s="54" t="s">
+      <c r="HI6" s="40" t="s">
         <v>264</v>
       </c>
-      <c r="HJ6" s="54" t="s">
+      <c r="HJ6" s="40" t="s">
         <v>265</v>
       </c>
-      <c r="HK6" s="54" t="s">
+      <c r="HK6" s="40" t="s">
         <v>266</v>
       </c>
-      <c r="HL6" s="54" t="s">
+      <c r="HL6" s="40" t="s">
         <v>267</v>
       </c>
-      <c r="HM6" s="54" t="s">
+      <c r="HM6" s="40" t="s">
         <v>268</v>
       </c>
-      <c r="HN6" s="54" t="s">
+      <c r="HN6" s="40" t="s">
         <v>269</v>
       </c>
-      <c r="HO6" s="54" t="s">
+      <c r="HO6" s="40" t="s">
         <v>270</v>
       </c>
-      <c r="HP6" s="54" t="s">
+      <c r="HP6" s="40" t="s">
         <v>271</v>
       </c>
-      <c r="HQ6" s="54" t="s">
+      <c r="HQ6" s="40" t="s">
         <v>272</v>
       </c>
-      <c r="HR6" s="54" t="s">
+      <c r="HR6" s="40" t="s">
         <v>273</v>
       </c>
-      <c r="HS6" s="54" t="s">
+      <c r="HS6" s="40" t="s">
         <v>274</v>
       </c>
-      <c r="HT6" s="54" t="s">
+      <c r="HT6" s="40" t="s">
         <v>275</v>
       </c>
-      <c r="HU6" s="54" t="s">
+      <c r="HU6" s="40" t="s">
         <v>276</v>
       </c>
-      <c r="HV6" s="54" t="s">
+      <c r="HV6" s="40" t="s">
         <v>277</v>
       </c>
-      <c r="HW6" s="54" t="s">
+      <c r="HW6" s="40" t="s">
         <v>278</v>
       </c>
-      <c r="HX6" s="54" t="s">
+      <c r="HX6" s="40" t="s">
         <v>279</v>
       </c>
-      <c r="HY6" s="54" t="s">
+      <c r="HY6" s="40" t="s">
         <v>280</v>
       </c>
-      <c r="HZ6" s="54" t="s">
+      <c r="HZ6" s="40" t="s">
         <v>281</v>
       </c>
-      <c r="IA6" s="54" t="s">
+      <c r="IA6" s="40" t="s">
         <v>282</v>
       </c>
-      <c r="IB6" s="54" t="s">
+      <c r="IB6" s="40" t="s">
         <v>283</v>
       </c>
-      <c r="IC6" s="54" t="s">
+      <c r="IC6" s="40" t="s">
         <v>284</v>
       </c>
-      <c r="ID6" s="54" t="s">
+      <c r="ID6" s="40" t="s">
         <v>285</v>
       </c>
-      <c r="IE6" s="54" t="s">
+      <c r="IE6" s="40" t="s">
         <v>286</v>
       </c>
-      <c r="IF6" s="54" t="s">
+      <c r="IF6" s="40" t="s">
         <v>287</v>
       </c>
-      <c r="IG6" s="54" t="s">
+      <c r="IG6" s="40" t="s">
         <v>288</v>
       </c>
-      <c r="IH6" s="54" t="s">
+      <c r="IH6" s="40" t="s">
         <v>289</v>
       </c>
-      <c r="II6" s="54" t="s">
+      <c r="II6" s="40" t="s">
         <v>290</v>
       </c>
-      <c r="IJ6" s="54" t="s">
+      <c r="IJ6" s="40" t="s">
         <v>291</v>
       </c>
-      <c r="IK6" s="54" t="s">
+      <c r="IK6" s="40" t="s">
         <v>292</v>
       </c>
-      <c r="IL6" s="54" t="s">
+      <c r="IL6" s="40" t="s">
         <v>293</v>
       </c>
-      <c r="IM6" s="54" t="s">
+      <c r="IM6" s="40" t="s">
         <v>294</v>
       </c>
-      <c r="IN6" s="54" t="s">
+      <c r="IN6" s="40" t="s">
         <v>295</v>
       </c>
-      <c r="IO6" s="54" t="s">
+      <c r="IO6" s="40" t="s">
         <v>296</v>
       </c>
-      <c r="IP6" s="54" t="s">
+      <c r="IP6" s="40" t="s">
         <v>297</v>
       </c>
-      <c r="IQ6" s="54" t="s">
+      <c r="IQ6" s="40" t="s">
         <v>298</v>
       </c>
-      <c r="IR6" s="54" t="s">
+      <c r="IR6" s="40" t="s">
         <v>299</v>
       </c>
-      <c r="IS6" s="54" t="s">
+      <c r="IS6" s="40" t="s">
         <v>300</v>
       </c>
-      <c r="IT6" s="54" t="s">
+      <c r="IT6" s="40" t="s">
         <v>301</v>
       </c>
-      <c r="IU6" s="54" t="s">
+      <c r="IU6" s="40" t="s">
         <v>302</v>
       </c>
-      <c r="IV6" s="54" t="s">
+      <c r="IV6" s="40" t="s">
         <v>303</v>
       </c>
-      <c r="IW6" s="54" t="s">
+      <c r="IW6" s="40" t="s">
         <v>304</v>
       </c>
-      <c r="IX6" s="54" t="s">
+      <c r="IX6" s="40" t="s">
         <v>305</v>
       </c>
-      <c r="IY6" s="54" t="s">
+      <c r="IY6" s="40" t="s">
         <v>306</v>
       </c>
-      <c r="IZ6" s="54" t="s">
+      <c r="IZ6" s="40" t="s">
         <v>307</v>
       </c>
-      <c r="JA6" s="54" t="s">
+      <c r="JA6" s="40" t="s">
         <v>308</v>
       </c>
-      <c r="JB6" s="54" t="s">
+      <c r="JB6" s="40" t="s">
         <v>309</v>
       </c>
-      <c r="JC6" s="54" t="s">
+      <c r="JC6" s="40" t="s">
         <v>310</v>
       </c>
-      <c r="JD6" s="54" t="s">
+      <c r="JD6" s="40" t="s">
         <v>311</v>
       </c>
-      <c r="JE6" s="54" t="s">
+      <c r="JE6" s="40" t="s">
         <v>312</v>
       </c>
-      <c r="JF6" s="54" t="s">
+      <c r="JF6" s="40" t="s">
         <v>313</v>
       </c>
-      <c r="JG6" s="54" t="s">
+      <c r="JG6" s="40" t="s">
         <v>314</v>
       </c>
-      <c r="JH6" s="54" t="s">
+      <c r="JH6" s="40" t="s">
         <v>315</v>
       </c>
-      <c r="JI6" s="54" t="s">
+      <c r="JI6" s="40" t="s">
         <v>316</v>
       </c>
-      <c r="JJ6" s="54" t="s">
+      <c r="JJ6" s="40" t="s">
         <v>317</v>
       </c>
-      <c r="JK6" s="54" t="s">
+      <c r="JK6" s="40" t="s">
         <v>318</v>
       </c>
-      <c r="JL6" s="54" t="s">
+      <c r="JL6" s="40" t="s">
         <v>319</v>
       </c>
-      <c r="JM6" s="54" t="s">
+      <c r="JM6" s="40" t="s">
         <v>320</v>
       </c>
-      <c r="JN6" s="54" t="s">
+      <c r="JN6" s="40" t="s">
         <v>321</v>
       </c>
-      <c r="JO6" s="54" t="s">
+      <c r="JO6" s="40" t="s">
         <v>322</v>
       </c>
-      <c r="JP6" s="54" t="s">
+      <c r="JP6" s="40" t="s">
         <v>323</v>
       </c>
-      <c r="JQ6" s="54" t="s">
+      <c r="JQ6" s="40" t="s">
         <v>324</v>
       </c>
-      <c r="JR6" s="54" t="s">
+      <c r="JR6" s="40" t="s">
         <v>325</v>
       </c>
-      <c r="JS6" s="54" t="s">
+      <c r="JS6" s="40" t="s">
         <v>326</v>
       </c>
-      <c r="JT6" s="54" t="s">
+      <c r="JT6" s="40" t="s">
         <v>327</v>
       </c>
-      <c r="JU6" s="54" t="s">
+      <c r="JU6" s="40" t="s">
         <v>328</v>
       </c>
-      <c r="JV6" s="54" t="s">
+      <c r="JV6" s="40" t="s">
         <v>329</v>
       </c>
-      <c r="JW6" s="54" t="s">
+      <c r="JW6" s="40" t="s">
         <v>330</v>
       </c>
-      <c r="JX6" s="54" t="s">
+      <c r="JX6" s="40" t="s">
         <v>331</v>
       </c>
-      <c r="JY6" s="54" t="s">
+      <c r="JY6" s="40" t="s">
         <v>332</v>
       </c>
-      <c r="JZ6" s="54" t="s">
+      <c r="JZ6" s="40" t="s">
         <v>333</v>
       </c>
-      <c r="KA6" s="54" t="s">
+      <c r="KA6" s="40" t="s">
         <v>334</v>
       </c>
-      <c r="KB6" s="54" t="s">
+      <c r="KB6" s="40" t="s">
         <v>335</v>
       </c>
-      <c r="KC6" s="54" t="s">
+      <c r="KC6" s="40" t="s">
         <v>336</v>
       </c>
-      <c r="KD6" s="54" t="s">
+      <c r="KD6" s="40" t="s">
         <v>337</v>
       </c>
-      <c r="KE6" s="54" t="s">
+      <c r="KE6" s="40" t="s">
         <v>338</v>
       </c>
-      <c r="KF6" s="54" t="s">
+      <c r="KF6" s="40" t="s">
         <v>339</v>
       </c>
-      <c r="KG6" s="54" t="s">
+      <c r="KG6" s="40" t="s">
         <v>340</v>
       </c>
-      <c r="KH6" s="54" t="s">
+      <c r="KH6" s="40" t="s">
         <v>341</v>
       </c>
-      <c r="KI6" s="54" t="s">
+      <c r="KI6" s="40" t="s">
         <v>342</v>
       </c>
-      <c r="KJ6" s="54" t="s">
+      <c r="KJ6" s="40" t="s">
         <v>343</v>
       </c>
-      <c r="KK6" s="54" t="s">
+      <c r="KK6" s="40" t="s">
         <v>344</v>
       </c>
-      <c r="KL6" s="54" t="s">
+      <c r="KL6" s="40" t="s">
         <v>345</v>
       </c>
-      <c r="KM6" s="54" t="s">
+      <c r="KM6" s="40" t="s">
         <v>346</v>
       </c>
-      <c r="KN6" s="54" t="s">
+      <c r="KN6" s="40" t="s">
         <v>347</v>
       </c>
-      <c r="KO6" s="54" t="s">
+      <c r="KO6" s="40" t="s">
         <v>348</v>
       </c>
-      <c r="KP6" s="54" t="s">
+      <c r="KP6" s="40" t="s">
         <v>349</v>
       </c>
-      <c r="KQ6" s="54" t="s">
+      <c r="KQ6" s="40" t="s">
         <v>350</v>
       </c>
-      <c r="KR6" s="54" t="s">
+      <c r="KR6" s="40" t="s">
         <v>351</v>
       </c>
-      <c r="KS6" s="54" t="s">
+      <c r="KS6" s="40" t="s">
         <v>352</v>
       </c>
-      <c r="KT6" s="54" t="s">
+      <c r="KT6" s="40" t="s">
         <v>353</v>
       </c>
-      <c r="KU6" s="54" t="s">
+      <c r="KU6" s="40" t="s">
         <v>354</v>
       </c>
-      <c r="KV6" s="54" t="s">
+      <c r="KV6" s="40" t="s">
         <v>355</v>
       </c>
-      <c r="KW6" s="54" t="s">
+      <c r="KW6" s="40" t="s">
         <v>356</v>
       </c>
-      <c r="KX6" s="54" t="s">
+      <c r="KX6" s="40" t="s">
         <v>357</v>
       </c>
-      <c r="KY6" s="54" t="s">
+      <c r="KY6" s="40" t="s">
         <v>358</v>
       </c>
-      <c r="KZ6" s="54" t="s">
+      <c r="KZ6" s="40" t="s">
         <v>359</v>
       </c>
-      <c r="LA6" s="54" t="s">
+      <c r="LA6" s="40" t="s">
         <v>360</v>
       </c>
-      <c r="LB6" s="54" t="s">
+      <c r="LB6" s="40" t="s">
         <v>361</v>
       </c>
-      <c r="LC6" s="54" t="s">
+      <c r="LC6" s="40" t="s">
         <v>362</v>
       </c>
-      <c r="LD6" s="54" t="s">
+      <c r="LD6" s="40" t="s">
         <v>363</v>
       </c>
-      <c r="LE6" s="54" t="s">
+      <c r="LE6" s="40" t="s">
         <v>364</v>
       </c>
-      <c r="LF6" s="54" t="s">
+      <c r="LF6" s="40" t="s">
         <v>365</v>
       </c>
-      <c r="LG6" s="54" t="s">
+      <c r="LG6" s="40" t="s">
         <v>366</v>
       </c>
-      <c r="LH6" s="54" t="s">
+      <c r="LH6" s="40" t="s">
         <v>367</v>
       </c>
-      <c r="LI6" s="54" t="s">
+      <c r="LI6" s="40" t="s">
         <v>368</v>
       </c>
-      <c r="LJ6" s="54" t="s">
+      <c r="LJ6" s="40" t="s">
         <v>369</v>
       </c>
-      <c r="LK6" s="54" t="s">
+      <c r="LK6" s="40" t="s">
         <v>370</v>
       </c>
-      <c r="LL6" s="54" t="s">
+      <c r="LL6" s="40" t="s">
         <v>371</v>
       </c>
-      <c r="LM6" s="54" t="s">
+      <c r="LM6" s="40" t="s">
         <v>372</v>
       </c>
-      <c r="LN6" s="54" t="s">
+      <c r="LN6" s="40" t="s">
         <v>373</v>
       </c>
-      <c r="LO6" s="54" t="s">
+      <c r="LO6" s="40" t="s">
         <v>374</v>
       </c>
-      <c r="LP6" s="54" t="s">
+      <c r="LP6" s="40" t="s">
         <v>375</v>
       </c>
-      <c r="LQ6" s="54" t="s">
+      <c r="LQ6" s="40" t="s">
         <v>376</v>
       </c>
-      <c r="LR6" s="54" t="s">
+      <c r="LR6" s="40" t="s">
         <v>377</v>
       </c>
-      <c r="LS6" s="54" t="s">
+      <c r="LS6" s="40" t="s">
         <v>378</v>
       </c>
-      <c r="LT6" s="54" t="s">
+      <c r="LT6" s="40" t="s">
         <v>379</v>
       </c>
-      <c r="LU6" s="54" t="s">
+      <c r="LU6" s="40" t="s">
         <v>380</v>
       </c>
-      <c r="LV6" s="54" t="s">
+      <c r="LV6" s="40" t="s">
         <v>381</v>
       </c>
-      <c r="LW6" s="54" t="s">
+      <c r="LW6" s="40" t="s">
         <v>382</v>
       </c>
-      <c r="LX6" s="54" t="s">
+      <c r="LX6" s="40" t="s">
         <v>383</v>
       </c>
-      <c r="LY6" s="54" t="s">
+      <c r="LY6" s="40" t="s">
         <v>384</v>
       </c>
-      <c r="LZ6" s="54" t="s">
+      <c r="LZ6" s="40" t="s">
         <v>385</v>
       </c>
-      <c r="MA6" s="54" t="s">
+      <c r="MA6" s="40" t="s">
         <v>386</v>
       </c>
-      <c r="MB6" s="54" t="s">
+      <c r="MB6" s="40" t="s">
         <v>387</v>
       </c>
-      <c r="MC6" s="54" t="s">
+      <c r="MC6" s="40" t="s">
         <v>388</v>
       </c>
-      <c r="MD6" s="54" t="s">
+      <c r="MD6" s="40" t="s">
         <v>389</v>
       </c>
-      <c r="ME6" s="54" t="s">
+      <c r="ME6" s="40" t="s">
         <v>390</v>
       </c>
-      <c r="MF6" s="54" t="s">
+      <c r="MF6" s="40" t="s">
         <v>391</v>
       </c>
-      <c r="MG6" s="54" t="s">
+      <c r="MG6" s="40" t="s">
         <v>392</v>
       </c>
-      <c r="MH6" s="54" t="s">
+      <c r="MH6" s="40" t="s">
         <v>393</v>
       </c>
-      <c r="MI6" s="54" t="s">
+      <c r="MI6" s="40" t="s">
         <v>394</v>
       </c>
-      <c r="MJ6" s="54" t="s">
+      <c r="MJ6" s="40" t="s">
         <v>395</v>
       </c>
-      <c r="MK6" s="54" t="s">
+      <c r="MK6" s="40" t="s">
         <v>396</v>
       </c>
-      <c r="ML6" s="54" t="s">
+      <c r="ML6" s="40" t="s">
         <v>397</v>
       </c>
-      <c r="MM6" s="54" t="s">
+      <c r="MM6" s="40" t="s">
         <v>398</v>
       </c>
-      <c r="MN6" s="54" t="s">
+      <c r="MN6" s="40" t="s">
         <v>399</v>
       </c>
-      <c r="MO6" s="54" t="s">
+      <c r="MO6" s="40" t="s">
         <v>400</v>
       </c>
-      <c r="MP6" s="54" t="s">
+      <c r="MP6" s="40" t="s">
         <v>401</v>
       </c>
-      <c r="MQ6" s="54" t="s">
+      <c r="MQ6" s="40" t="s">
         <v>402</v>
       </c>
-      <c r="MR6" s="54" t="s">
+      <c r="MR6" s="40" t="s">
         <v>403</v>
       </c>
-      <c r="MS6" s="54" t="s">
+      <c r="MS6" s="40" t="s">
         <v>404</v>
       </c>
-      <c r="MT6" s="54" t="s">
+      <c r="MT6" s="40" t="s">
         <v>405</v>
       </c>
-      <c r="MU6" s="54" t="s">
+      <c r="MU6" s="40" t="s">
         <v>406</v>
       </c>
-      <c r="MV6" s="54" t="s">
+      <c r="MV6" s="40" t="s">
         <v>407</v>
       </c>
-      <c r="MW6" s="54" t="s">
+      <c r="MW6" s="40" t="s">
         <v>408</v>
       </c>
-      <c r="MX6" s="54" t="s">
+      <c r="MX6" s="40" t="s">
         <v>409</v>
       </c>
-      <c r="MY6" s="54" t="s">
+      <c r="MY6" s="40" t="s">
         <v>410</v>
       </c>
-      <c r="MZ6" s="54" t="s">
+      <c r="MZ6" s="40" t="s">
         <v>411</v>
       </c>
-      <c r="NA6" s="54" t="s">
+      <c r="NA6" s="40" t="s">
         <v>412</v>
       </c>
-      <c r="NB6" s="54" t="s">
+      <c r="NB6" s="40" t="s">
         <v>413</v>
       </c>
-      <c r="NC6" s="54" t="s">
+      <c r="NC6" s="40" t="s">
         <v>414</v>
       </c>
-      <c r="ND6" s="54" t="s">
+      <c r="ND6" s="40" t="s">
         <v>415</v>
       </c>
-      <c r="NE6" s="54" t="s">
+      <c r="NE6" s="40" t="s">
         <v>416</v>
       </c>
-      <c r="NF6" s="54" t="s">
+      <c r="NF6" s="40" t="s">
         <v>417</v>
       </c>
-      <c r="NG6" s="54" t="s">
+      <c r="NG6" s="40" t="s">
         <v>418</v>
       </c>
-      <c r="NH6" s="54" t="s">
+      <c r="NH6" s="78" t="s">
         <v>419</v>
       </c>
-      <c r="NI6" s="54" t="s">
+      <c r="NI6" s="79"/>
+      <c r="NJ6" s="40" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="7" spans="1:373" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="55"/>
-      <c r="B7" s="55"/>
-      <c r="C7" s="55"/>
-      <c r="D7" s="55"/>
-      <c r="E7" s="55"/>
-      <c r="F7" s="55"/>
-      <c r="G7" s="56"/>
-      <c r="H7" s="56"/>
-      <c r="I7" s="57"/>
-      <c r="J7" s="57"/>
-      <c r="K7" s="57"/>
-      <c r="L7" s="57"/>
-      <c r="M7" s="57"/>
-      <c r="N7" s="57"/>
-      <c r="O7" s="57"/>
-      <c r="P7" s="57"/>
-      <c r="Q7" s="57"/>
-      <c r="R7" s="58"/>
-      <c r="S7" s="58"/>
-      <c r="T7" s="57"/>
-      <c r="U7" s="57"/>
-      <c r="V7" s="59"/>
-      <c r="W7" s="60"/>
-      <c r="X7" s="60"/>
-      <c r="Y7" s="61"/>
-      <c r="Z7" s="61"/>
-      <c r="AA7" s="62"/>
-      <c r="AB7" s="61"/>
-      <c r="AC7" s="56"/>
-      <c r="AD7" s="56"/>
-      <c r="AE7" s="56"/>
-      <c r="AF7" s="57"/>
-      <c r="AG7" s="63"/>
-      <c r="AH7" s="64"/>
-      <c r="AI7" s="64"/>
-      <c r="AJ7" s="64"/>
-      <c r="AK7" s="64"/>
-      <c r="AL7" s="64"/>
-      <c r="AM7" s="65">
+    <row r="7" spans="1:374" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="41"/>
+      <c r="B7" s="41"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="41"/>
+      <c r="E7" s="41"/>
+      <c r="F7" s="41"/>
+      <c r="G7" s="42"/>
+      <c r="H7" s="42"/>
+      <c r="I7" s="43"/>
+      <c r="J7" s="43"/>
+      <c r="K7" s="43"/>
+      <c r="L7" s="43"/>
+      <c r="M7" s="43"/>
+      <c r="N7" s="43"/>
+      <c r="O7" s="43"/>
+      <c r="P7" s="43"/>
+      <c r="Q7" s="43"/>
+      <c r="R7" s="44"/>
+      <c r="S7" s="44"/>
+      <c r="T7" s="43"/>
+      <c r="U7" s="43"/>
+      <c r="V7" s="45"/>
+      <c r="W7" s="46"/>
+      <c r="X7" s="46"/>
+      <c r="Y7" s="47"/>
+      <c r="Z7" s="47"/>
+      <c r="AA7" s="48"/>
+      <c r="AB7" s="47"/>
+      <c r="AC7" s="42"/>
+      <c r="AD7" s="42"/>
+      <c r="AE7" s="42"/>
+      <c r="AF7" s="43"/>
+      <c r="AG7" s="49"/>
+      <c r="AH7" s="50"/>
+      <c r="AI7" s="50"/>
+      <c r="AJ7" s="50"/>
+      <c r="AK7" s="50"/>
+      <c r="AL7" s="50"/>
+      <c r="AM7" s="51">
         <f>SUM(BO7:BX7)</f>
         <v>0</v>
       </c>
-      <c r="AN7" s="66">
+      <c r="AN7" s="52">
         <f>SUM(BY7:CH7)</f>
         <v>0</v>
       </c>
-      <c r="AO7" s="66">
+      <c r="AO7" s="52">
         <f>SUM(CI7:CR7)</f>
         <v>0</v>
       </c>
-      <c r="AP7" s="66">
+      <c r="AP7" s="52">
         <f>SUM(CS7:DB7)</f>
         <v>0</v>
       </c>
-      <c r="AQ7" s="66">
+      <c r="AQ7" s="52">
         <f>SUM(DC7:DL7)</f>
         <v>0</v>
       </c>
-      <c r="AR7" s="66">
+      <c r="AR7" s="52">
         <f>SUM(DM7:DV7)</f>
         <v>0</v>
       </c>
-      <c r="AS7" s="66">
+      <c r="AS7" s="52">
         <f>SUM(DW7:EF7)</f>
         <v>0</v>
       </c>
-      <c r="AT7" s="66">
+      <c r="AT7" s="52">
         <f>SUM(EG7:EP7)</f>
         <v>0</v>
       </c>
-      <c r="AU7" s="66">
+      <c r="AU7" s="52">
         <f>SUM(EQ7:EZ7)</f>
         <v>0</v>
       </c>
-      <c r="AV7" s="66">
+      <c r="AV7" s="52">
         <f>SUM(FA7:FJ7)</f>
         <v>0</v>
       </c>
-      <c r="AW7" s="66">
+      <c r="AW7" s="52">
         <f>SUM(FK7:FT7)</f>
         <v>0</v>
       </c>
-      <c r="AX7" s="66">
+      <c r="AX7" s="52">
         <f>SUM(FU7:GD7)</f>
         <v>0</v>
       </c>
-      <c r="AY7" s="66">
+      <c r="AY7" s="52">
         <f>SUM(GE7:GN7)</f>
         <v>0</v>
       </c>
-      <c r="AZ7" s="66">
+      <c r="AZ7" s="52">
         <f>SUM(GO7:GX7)</f>
         <v>0</v>
       </c>
-      <c r="BA7" s="66">
+      <c r="BA7" s="52">
         <f>SUM(GY7:HH7)</f>
         <v>0</v>
       </c>
-      <c r="BB7" s="66">
+      <c r="BB7" s="52">
         <f>SUM(HI7:HR7)</f>
         <v>0</v>
       </c>
-      <c r="BC7" s="66">
+      <c r="BC7" s="52">
         <f>SUM(HS7:IB7)</f>
         <v>0</v>
       </c>
-      <c r="BD7" s="66">
+      <c r="BD7" s="52">
         <f>SUM(IC7:IL7)</f>
         <v>0</v>
       </c>
-      <c r="BE7" s="66">
+      <c r="BE7" s="52">
         <f>SUM(IM7:IV7)</f>
         <v>0</v>
       </c>
-      <c r="BF7" s="66">
+      <c r="BF7" s="52">
         <f>SUM(IW7:JF7)</f>
         <v>0</v>
       </c>
-      <c r="BG7" s="66">
+      <c r="BG7" s="52">
         <f>SUM(JG7:JP7)</f>
         <v>0</v>
       </c>
-      <c r="BH7" s="66">
+      <c r="BH7" s="52">
         <f>SUM(JQ7:JZ7)</f>
         <v>0</v>
       </c>
-      <c r="BI7" s="66">
+      <c r="BI7" s="52">
         <f>SUM(KA7:KJ7)</f>
         <v>0</v>
       </c>
-      <c r="BJ7" s="66">
+      <c r="BJ7" s="52">
         <f>SUM(KK7:KT7)</f>
         <v>0</v>
       </c>
-      <c r="BK7" s="66">
+      <c r="BK7" s="52">
         <f>SUM(KU7:LD7)</f>
         <v>0</v>
       </c>
-      <c r="BL7" s="66">
+      <c r="BL7" s="52">
         <f>SUM(LE7:LN7)</f>
         <v>0</v>
       </c>
-      <c r="BM7" s="66">
+      <c r="BM7" s="52">
         <f>SUM(LO7:LX7)</f>
         <v>0</v>
       </c>
-      <c r="BN7" s="66">
+      <c r="BN7" s="52">
         <f>SUM(LY7:MH7)</f>
         <v>0</v>
       </c>
-      <c r="BO7" s="66">
-        <f t="shared" ref="BO7:BX7" si="0">BY7+CI7+CS7+DC7+DM7+DW7+EG7+EQ7+FA7+FK7+FU7+GE7+GO7+GY7</f>
+      <c r="BO7" s="52">
+        <f>BY7+CI7+CS7+DC7+DM7+DW7+EG7+EQ7+FA7+FK7+FU7+GE7+GO7+GY7</f>
         <v>0</v>
       </c>
-      <c r="BP7" s="66">
-        <f t="shared" si="0"/>
+      <c r="BP7" s="52">
+        <f>BZ7+CJ7+CT7+DD7+DN7+DX7+EH7+ER7+FB7+FL7+FV7+GF7+GP7+GZ7</f>
         <v>0</v>
       </c>
-      <c r="BQ7" s="66">
-        <f t="shared" si="0"/>
+      <c r="BQ7" s="52">
+        <f>CA7+CK7+CU7+DE7+DO7+DY7+EI7+ES7+FC7+FM7+FW7+GG7+GQ7+HA7</f>
         <v>0</v>
       </c>
-      <c r="BR7" s="66">
-        <f t="shared" si="0"/>
+      <c r="BR7" s="52">
+        <f>CB7+CL7+CV7+DF7+DP7+DZ7+EJ7+ET7+FD7+FN7+FX7+GH7+GR7+HB7</f>
         <v>0</v>
       </c>
-      <c r="BS7" s="66">
-        <f t="shared" si="0"/>
+      <c r="BS7" s="52">
+        <f>CC7+CM7+CW7+DG7+DQ7+EA7+EK7+EU7+FE7+FO7+FY7+GI7+GS7+HC7</f>
         <v>0</v>
       </c>
-      <c r="BT7" s="66">
-        <f t="shared" si="0"/>
+      <c r="BT7" s="52">
+        <f>CD7+CN7+CX7+DH7+DR7+EB7+EL7+EV7+FF7+FP7+FZ7+GJ7+GT7+HD7</f>
         <v>0</v>
       </c>
-      <c r="BU7" s="66">
-        <f t="shared" si="0"/>
+      <c r="BU7" s="52">
+        <f>CE7+CO7+CY7+DI7+DS7+EC7+EM7+EW7+FG7+FQ7+GA7+GK7+GU7+HE7</f>
         <v>0</v>
       </c>
-      <c r="BV7" s="66">
-        <f t="shared" si="0"/>
+      <c r="BV7" s="52">
+        <f>CF7+CP7+CZ7+DJ7+DT7+ED7+EN7+EX7+FH7+FR7+GB7+GL7+GV7+HF7</f>
         <v>0</v>
       </c>
-      <c r="BW7" s="66">
-        <f t="shared" si="0"/>
+      <c r="BW7" s="52">
+        <f>CG7+CQ7+DA7+DK7+DU7+EE7+EO7+EY7+FI7+FS7+GC7+GM7+GW7+HG7</f>
         <v>0</v>
       </c>
-      <c r="BX7" s="66">
-        <f t="shared" si="0"/>
+      <c r="BX7" s="52">
+        <f>CH7+CR7+DB7+DL7+DV7+EF7+EP7+EZ7+FJ7+FT7+GD7+GN7+GX7+HH7</f>
         <v>0</v>
       </c>
-      <c r="BY7" s="61"/>
-      <c r="BZ7" s="61"/>
-      <c r="CA7" s="61"/>
-      <c r="CB7" s="61"/>
-      <c r="CC7" s="61"/>
-      <c r="CD7" s="61"/>
-      <c r="CE7" s="61"/>
-      <c r="CF7" s="61"/>
-      <c r="CG7" s="61"/>
-      <c r="CH7" s="61"/>
-      <c r="CI7" s="61"/>
-      <c r="CJ7" s="61"/>
-      <c r="CK7" s="61"/>
-      <c r="CL7" s="61"/>
-      <c r="CM7" s="61"/>
-      <c r="CN7" s="61"/>
-      <c r="CO7" s="61"/>
-      <c r="CP7" s="61"/>
-      <c r="CQ7" s="61"/>
-      <c r="CR7" s="61"/>
-      <c r="CS7" s="61"/>
-      <c r="CT7" s="61"/>
-      <c r="CU7" s="61"/>
-      <c r="CV7" s="61"/>
-      <c r="CW7" s="61"/>
-      <c r="CX7" s="61"/>
-      <c r="CY7" s="61"/>
-      <c r="CZ7" s="61"/>
-      <c r="DA7" s="61"/>
-      <c r="DB7" s="61"/>
-      <c r="DC7" s="61"/>
-      <c r="DD7" s="61"/>
-      <c r="DE7" s="61"/>
-      <c r="DF7" s="61"/>
-      <c r="DG7" s="61"/>
-      <c r="DH7" s="61"/>
-      <c r="DI7" s="61"/>
-      <c r="DJ7" s="61"/>
-      <c r="DK7" s="61"/>
-      <c r="DL7" s="61"/>
-      <c r="DM7" s="61"/>
-      <c r="DN7" s="61"/>
-      <c r="DO7" s="61"/>
-      <c r="DP7" s="61"/>
-      <c r="DQ7" s="61"/>
-      <c r="DR7" s="61"/>
-      <c r="DS7" s="61"/>
-      <c r="DT7" s="61"/>
-      <c r="DU7" s="61"/>
-      <c r="DV7" s="61"/>
-      <c r="DW7" s="61"/>
-      <c r="DX7" s="61"/>
-      <c r="DY7" s="61"/>
-      <c r="DZ7" s="61"/>
-      <c r="EA7" s="61"/>
-      <c r="EB7" s="61"/>
-      <c r="EC7" s="61"/>
-      <c r="ED7" s="61"/>
-      <c r="EE7" s="61"/>
-      <c r="EF7" s="61"/>
-      <c r="EG7" s="61"/>
-      <c r="EH7" s="61"/>
-      <c r="EI7" s="61"/>
-      <c r="EJ7" s="61"/>
-      <c r="EK7" s="61"/>
-      <c r="EL7" s="61"/>
-      <c r="EM7" s="61"/>
-      <c r="EN7" s="61"/>
-      <c r="EO7" s="61"/>
-      <c r="EP7" s="61"/>
-      <c r="EQ7" s="61"/>
-      <c r="ER7" s="61"/>
-      <c r="ES7" s="61"/>
-      <c r="ET7" s="61"/>
-      <c r="EU7" s="61"/>
-      <c r="EV7" s="61"/>
-      <c r="EW7" s="61"/>
-      <c r="EX7" s="61"/>
-      <c r="EY7" s="61"/>
-      <c r="EZ7" s="61"/>
-      <c r="FA7" s="61"/>
-      <c r="FB7" s="61"/>
-      <c r="FC7" s="61"/>
-      <c r="FD7" s="61"/>
-      <c r="FE7" s="61"/>
-      <c r="FF7" s="61"/>
-      <c r="FG7" s="61"/>
-      <c r="FH7" s="61"/>
-      <c r="FI7" s="61"/>
-      <c r="FJ7" s="61"/>
-      <c r="FK7" s="61"/>
-      <c r="FL7" s="61"/>
-      <c r="FM7" s="61"/>
-      <c r="FN7" s="61"/>
-      <c r="FO7" s="61"/>
-      <c r="FP7" s="61"/>
-      <c r="FQ7" s="61"/>
-      <c r="FR7" s="61"/>
-      <c r="FS7" s="61"/>
-      <c r="FT7" s="61"/>
-      <c r="FU7" s="61"/>
-      <c r="FV7" s="61"/>
-      <c r="FW7" s="61"/>
-      <c r="FX7" s="61"/>
-      <c r="FY7" s="61"/>
-      <c r="FZ7" s="61"/>
-      <c r="GA7" s="61"/>
-      <c r="GB7" s="61"/>
-      <c r="GC7" s="61"/>
-      <c r="GD7" s="61"/>
-      <c r="GE7" s="61"/>
-      <c r="GF7" s="61"/>
-      <c r="GG7" s="61"/>
-      <c r="GH7" s="61"/>
-      <c r="GI7" s="61"/>
-      <c r="GJ7" s="61"/>
-      <c r="GK7" s="61"/>
-      <c r="GL7" s="61"/>
-      <c r="GM7" s="61"/>
-      <c r="GN7" s="61"/>
-      <c r="GO7" s="61"/>
-      <c r="GP7" s="61"/>
-      <c r="GQ7" s="61"/>
-      <c r="GR7" s="61"/>
-      <c r="GS7" s="61"/>
-      <c r="GT7" s="61"/>
-      <c r="GU7" s="61"/>
-      <c r="GV7" s="61"/>
-      <c r="GW7" s="61"/>
-      <c r="GX7" s="61"/>
-      <c r="GY7" s="61"/>
-      <c r="GZ7" s="61"/>
-      <c r="HA7" s="61"/>
-      <c r="HB7" s="61"/>
-      <c r="HC7" s="61"/>
-      <c r="HD7" s="61"/>
-      <c r="HE7" s="61"/>
-      <c r="HF7" s="61"/>
-      <c r="HG7" s="61"/>
-      <c r="HH7" s="61"/>
-      <c r="HI7" s="61"/>
-      <c r="HJ7" s="61"/>
-      <c r="HK7" s="61"/>
-      <c r="HL7" s="61"/>
-      <c r="HM7" s="61"/>
-      <c r="HN7" s="61"/>
-      <c r="HO7" s="61"/>
-      <c r="HP7" s="61"/>
-      <c r="HQ7" s="61"/>
-      <c r="HR7" s="61"/>
-      <c r="HS7" s="61"/>
-      <c r="HT7" s="61"/>
-      <c r="HU7" s="61"/>
-      <c r="HV7" s="61"/>
-      <c r="HW7" s="61"/>
-      <c r="HX7" s="61"/>
-      <c r="HY7" s="61"/>
-      <c r="HZ7" s="61"/>
-      <c r="IA7" s="61"/>
-      <c r="IB7" s="61"/>
-      <c r="IC7" s="61"/>
-      <c r="ID7" s="61"/>
-      <c r="IE7" s="61"/>
-      <c r="IF7" s="61"/>
-      <c r="IG7" s="61"/>
-      <c r="IH7" s="61"/>
-      <c r="II7" s="61"/>
-      <c r="IJ7" s="61"/>
-      <c r="IK7" s="61"/>
-      <c r="IL7" s="61"/>
-      <c r="IM7" s="61"/>
-      <c r="IN7" s="61"/>
-      <c r="IO7" s="61"/>
-      <c r="IP7" s="61"/>
-      <c r="IQ7" s="61"/>
-      <c r="IR7" s="61"/>
-      <c r="IS7" s="61"/>
-      <c r="IT7" s="61"/>
-      <c r="IU7" s="61"/>
-      <c r="IV7" s="61"/>
-      <c r="IW7" s="61"/>
-      <c r="IX7" s="61"/>
-      <c r="IY7" s="61"/>
-      <c r="IZ7" s="61"/>
-      <c r="JA7" s="61"/>
-      <c r="JB7" s="61"/>
-      <c r="JC7" s="61"/>
-      <c r="JD7" s="61"/>
-      <c r="JE7" s="61"/>
-      <c r="JF7" s="61"/>
-      <c r="JG7" s="61"/>
-      <c r="JH7" s="61"/>
-      <c r="JI7" s="61"/>
-      <c r="JJ7" s="61"/>
-      <c r="JK7" s="61"/>
-      <c r="JL7" s="61"/>
-      <c r="JM7" s="61"/>
-      <c r="JN7" s="61"/>
-      <c r="JO7" s="61"/>
-      <c r="JP7" s="61"/>
-      <c r="JQ7" s="61"/>
-      <c r="JR7" s="61"/>
-      <c r="JS7" s="61"/>
-      <c r="JT7" s="61"/>
-      <c r="JU7" s="61"/>
-      <c r="JV7" s="61"/>
-      <c r="JW7" s="61"/>
-      <c r="JX7" s="61"/>
-      <c r="JY7" s="61"/>
-      <c r="JZ7" s="61"/>
-      <c r="KA7" s="61"/>
-      <c r="KB7" s="61"/>
-      <c r="KC7" s="61"/>
-      <c r="KD7" s="61"/>
-      <c r="KE7" s="61"/>
-      <c r="KF7" s="61"/>
-      <c r="KG7" s="61"/>
-      <c r="KH7" s="61"/>
-      <c r="KI7" s="61"/>
-      <c r="KJ7" s="61"/>
-      <c r="KK7" s="61"/>
-      <c r="KL7" s="61"/>
-      <c r="KM7" s="61"/>
-      <c r="KN7" s="61"/>
-      <c r="KO7" s="61"/>
-      <c r="KP7" s="61"/>
-      <c r="KQ7" s="61"/>
-      <c r="KR7" s="61"/>
-      <c r="KS7" s="61"/>
-      <c r="KT7" s="61"/>
-      <c r="KU7" s="61"/>
-      <c r="KV7" s="61"/>
-      <c r="KW7" s="61"/>
-      <c r="KX7" s="61"/>
-      <c r="KY7" s="61"/>
-      <c r="KZ7" s="61"/>
-      <c r="LA7" s="61"/>
-      <c r="LB7" s="61"/>
-      <c r="LC7" s="61"/>
-      <c r="LD7" s="61"/>
-      <c r="LE7" s="61"/>
-      <c r="LF7" s="61"/>
-      <c r="LG7" s="61"/>
-      <c r="LH7" s="61"/>
-      <c r="LI7" s="61"/>
-      <c r="LJ7" s="61"/>
-      <c r="LK7" s="61"/>
-      <c r="LL7" s="61"/>
-      <c r="LM7" s="61"/>
-      <c r="LN7" s="61"/>
-      <c r="LO7" s="61"/>
-      <c r="LP7" s="61"/>
-      <c r="LQ7" s="61"/>
-      <c r="LR7" s="61"/>
-      <c r="LS7" s="61"/>
-      <c r="LT7" s="61"/>
-      <c r="LU7" s="61"/>
-      <c r="LV7" s="61"/>
-      <c r="LW7" s="61"/>
-      <c r="LX7" s="61"/>
-      <c r="LY7" s="61"/>
-      <c r="LZ7" s="61"/>
-      <c r="MA7" s="61"/>
-      <c r="MB7" s="61"/>
-      <c r="MC7" s="61"/>
-      <c r="MD7" s="61"/>
-      <c r="ME7" s="61"/>
-      <c r="MF7" s="61"/>
-      <c r="MG7" s="61"/>
-      <c r="MH7" s="61"/>
-      <c r="MI7" s="56"/>
-      <c r="MJ7" s="56"/>
-      <c r="MK7" s="56"/>
-      <c r="ML7" s="56"/>
-      <c r="MM7" s="56"/>
-      <c r="MN7" s="56"/>
-      <c r="MO7" s="56"/>
-      <c r="MP7" s="56"/>
-      <c r="MQ7" s="56"/>
-      <c r="MR7" s="56"/>
-      <c r="MS7" s="56"/>
-      <c r="MT7" s="56"/>
-      <c r="MU7" s="56"/>
-      <c r="MV7" s="56"/>
-      <c r="MW7" s="29"/>
-      <c r="MX7" s="29"/>
-      <c r="MY7" s="29"/>
-      <c r="MZ7" s="29"/>
-      <c r="NA7" s="67"/>
-      <c r="NB7" s="67"/>
-      <c r="NC7" s="67"/>
-      <c r="ND7" s="67"/>
-      <c r="NE7" s="67"/>
-      <c r="NF7" s="67"/>
-      <c r="NG7" s="67"/>
-      <c r="NH7" s="67"/>
-      <c r="NI7" s="67"/>
+      <c r="BY7" s="47"/>
+      <c r="BZ7" s="47"/>
+      <c r="CA7" s="47"/>
+      <c r="CB7" s="47"/>
+      <c r="CC7" s="47"/>
+      <c r="CD7" s="47"/>
+      <c r="CE7" s="47"/>
+      <c r="CF7" s="47"/>
+      <c r="CG7" s="47"/>
+      <c r="CH7" s="47"/>
+      <c r="CI7" s="47"/>
+      <c r="CJ7" s="47"/>
+      <c r="CK7" s="47"/>
+      <c r="CL7" s="47"/>
+      <c r="CM7" s="47"/>
+      <c r="CN7" s="47"/>
+      <c r="CO7" s="47"/>
+      <c r="CP7" s="47"/>
+      <c r="CQ7" s="47"/>
+      <c r="CR7" s="47"/>
+      <c r="CS7" s="47"/>
+      <c r="CT7" s="47"/>
+      <c r="CU7" s="47"/>
+      <c r="CV7" s="47"/>
+      <c r="CW7" s="47"/>
+      <c r="CX7" s="47"/>
+      <c r="CY7" s="47"/>
+      <c r="CZ7" s="47"/>
+      <c r="DA7" s="47"/>
+      <c r="DB7" s="47"/>
+      <c r="DC7" s="47"/>
+      <c r="DD7" s="47"/>
+      <c r="DE7" s="47"/>
+      <c r="DF7" s="47"/>
+      <c r="DG7" s="47"/>
+      <c r="DH7" s="47"/>
+      <c r="DI7" s="47"/>
+      <c r="DJ7" s="47"/>
+      <c r="DK7" s="47"/>
+      <c r="DL7" s="47"/>
+      <c r="DM7" s="47"/>
+      <c r="DN7" s="47"/>
+      <c r="DO7" s="47"/>
+      <c r="DP7" s="47"/>
+      <c r="DQ7" s="47"/>
+      <c r="DR7" s="47"/>
+      <c r="DS7" s="47"/>
+      <c r="DT7" s="47"/>
+      <c r="DU7" s="47"/>
+      <c r="DV7" s="47"/>
+      <c r="DW7" s="47"/>
+      <c r="DX7" s="47"/>
+      <c r="DY7" s="47"/>
+      <c r="DZ7" s="47"/>
+      <c r="EA7" s="47"/>
+      <c r="EB7" s="47"/>
+      <c r="EC7" s="47"/>
+      <c r="ED7" s="47"/>
+      <c r="EE7" s="47"/>
+      <c r="EF7" s="47"/>
+      <c r="EG7" s="47"/>
+      <c r="EH7" s="47"/>
+      <c r="EI7" s="47"/>
+      <c r="EJ7" s="47"/>
+      <c r="EK7" s="47"/>
+      <c r="EL7" s="47"/>
+      <c r="EM7" s="47"/>
+      <c r="EN7" s="47"/>
+      <c r="EO7" s="47"/>
+      <c r="EP7" s="47"/>
+      <c r="EQ7" s="47"/>
+      <c r="ER7" s="47"/>
+      <c r="ES7" s="47"/>
+      <c r="ET7" s="47"/>
+      <c r="EU7" s="47"/>
+      <c r="EV7" s="47"/>
+      <c r="EW7" s="47"/>
+      <c r="EX7" s="47"/>
+      <c r="EY7" s="47"/>
+      <c r="EZ7" s="47"/>
+      <c r="FA7" s="47"/>
+      <c r="FB7" s="47"/>
+      <c r="FC7" s="47"/>
+      <c r="FD7" s="47"/>
+      <c r="FE7" s="47"/>
+      <c r="FF7" s="47"/>
+      <c r="FG7" s="47"/>
+      <c r="FH7" s="47"/>
+      <c r="FI7" s="47"/>
+      <c r="FJ7" s="47"/>
+      <c r="FK7" s="47"/>
+      <c r="FL7" s="47"/>
+      <c r="FM7" s="47"/>
+      <c r="FN7" s="47"/>
+      <c r="FO7" s="47"/>
+      <c r="FP7" s="47"/>
+      <c r="FQ7" s="47"/>
+      <c r="FR7" s="47"/>
+      <c r="FS7" s="47"/>
+      <c r="FT7" s="47"/>
+      <c r="FU7" s="47"/>
+      <c r="FV7" s="47"/>
+      <c r="FW7" s="47"/>
+      <c r="FX7" s="47"/>
+      <c r="FY7" s="47"/>
+      <c r="FZ7" s="47"/>
+      <c r="GA7" s="47"/>
+      <c r="GB7" s="47"/>
+      <c r="GC7" s="47"/>
+      <c r="GD7" s="47"/>
+      <c r="GE7" s="47"/>
+      <c r="GF7" s="47"/>
+      <c r="GG7" s="47"/>
+      <c r="GH7" s="47"/>
+      <c r="GI7" s="47"/>
+      <c r="GJ7" s="47"/>
+      <c r="GK7" s="47"/>
+      <c r="GL7" s="47"/>
+      <c r="GM7" s="47"/>
+      <c r="GN7" s="47"/>
+      <c r="GO7" s="47"/>
+      <c r="GP7" s="47"/>
+      <c r="GQ7" s="47"/>
+      <c r="GR7" s="47"/>
+      <c r="GS7" s="47"/>
+      <c r="GT7" s="47"/>
+      <c r="GU7" s="47"/>
+      <c r="GV7" s="47"/>
+      <c r="GW7" s="47"/>
+      <c r="GX7" s="47"/>
+      <c r="GY7" s="47"/>
+      <c r="GZ7" s="47"/>
+      <c r="HA7" s="47"/>
+      <c r="HB7" s="47"/>
+      <c r="HC7" s="47"/>
+      <c r="HD7" s="47"/>
+      <c r="HE7" s="47"/>
+      <c r="HF7" s="47"/>
+      <c r="HG7" s="47"/>
+      <c r="HH7" s="47"/>
+      <c r="HI7" s="47"/>
+      <c r="HJ7" s="47"/>
+      <c r="HK7" s="47"/>
+      <c r="HL7" s="47"/>
+      <c r="HM7" s="47"/>
+      <c r="HN7" s="47"/>
+      <c r="HO7" s="47"/>
+      <c r="HP7" s="47"/>
+      <c r="HQ7" s="47"/>
+      <c r="HR7" s="47"/>
+      <c r="HS7" s="47"/>
+      <c r="HT7" s="47"/>
+      <c r="HU7" s="47"/>
+      <c r="HV7" s="47"/>
+      <c r="HW7" s="47"/>
+      <c r="HX7" s="47"/>
+      <c r="HY7" s="47"/>
+      <c r="HZ7" s="47"/>
+      <c r="IA7" s="47"/>
+      <c r="IB7" s="47"/>
+      <c r="IC7" s="47"/>
+      <c r="ID7" s="47"/>
+      <c r="IE7" s="47"/>
+      <c r="IF7" s="47"/>
+      <c r="IG7" s="47"/>
+      <c r="IH7" s="47"/>
+      <c r="II7" s="47"/>
+      <c r="IJ7" s="47"/>
+      <c r="IK7" s="47"/>
+      <c r="IL7" s="47"/>
+      <c r="IM7" s="47"/>
+      <c r="IN7" s="47"/>
+      <c r="IO7" s="47"/>
+      <c r="IP7" s="47"/>
+      <c r="IQ7" s="47"/>
+      <c r="IR7" s="47"/>
+      <c r="IS7" s="47"/>
+      <c r="IT7" s="47"/>
+      <c r="IU7" s="47"/>
+      <c r="IV7" s="47"/>
+      <c r="IW7" s="47"/>
+      <c r="IX7" s="47"/>
+      <c r="IY7" s="47"/>
+      <c r="IZ7" s="47"/>
+      <c r="JA7" s="47"/>
+      <c r="JB7" s="47"/>
+      <c r="JC7" s="47"/>
+      <c r="JD7" s="47"/>
+      <c r="JE7" s="47"/>
+      <c r="JF7" s="47"/>
+      <c r="JG7" s="47"/>
+      <c r="JH7" s="47"/>
+      <c r="JI7" s="47"/>
+      <c r="JJ7" s="47"/>
+      <c r="JK7" s="47"/>
+      <c r="JL7" s="47"/>
+      <c r="JM7" s="47"/>
+      <c r="JN7" s="47"/>
+      <c r="JO7" s="47"/>
+      <c r="JP7" s="47"/>
+      <c r="JQ7" s="47"/>
+      <c r="JR7" s="47"/>
+      <c r="JS7" s="47"/>
+      <c r="JT7" s="47"/>
+      <c r="JU7" s="47"/>
+      <c r="JV7" s="47"/>
+      <c r="JW7" s="47"/>
+      <c r="JX7" s="47"/>
+      <c r="JY7" s="47"/>
+      <c r="JZ7" s="47"/>
+      <c r="KA7" s="47"/>
+      <c r="KB7" s="47"/>
+      <c r="KC7" s="47"/>
+      <c r="KD7" s="47"/>
+      <c r="KE7" s="47"/>
+      <c r="KF7" s="47"/>
+      <c r="KG7" s="47"/>
+      <c r="KH7" s="47"/>
+      <c r="KI7" s="47"/>
+      <c r="KJ7" s="47"/>
+      <c r="KK7" s="47"/>
+      <c r="KL7" s="47"/>
+      <c r="KM7" s="47"/>
+      <c r="KN7" s="47"/>
+      <c r="KO7" s="47"/>
+      <c r="KP7" s="47"/>
+      <c r="KQ7" s="47"/>
+      <c r="KR7" s="47"/>
+      <c r="KS7" s="47"/>
+      <c r="KT7" s="47"/>
+      <c r="KU7" s="47"/>
+      <c r="KV7" s="47"/>
+      <c r="KW7" s="47"/>
+      <c r="KX7" s="47"/>
+      <c r="KY7" s="47"/>
+      <c r="KZ7" s="47"/>
+      <c r="LA7" s="47"/>
+      <c r="LB7" s="47"/>
+      <c r="LC7" s="47"/>
+      <c r="LD7" s="47"/>
+      <c r="LE7" s="47"/>
+      <c r="LF7" s="47"/>
+      <c r="LG7" s="47"/>
+      <c r="LH7" s="47"/>
+      <c r="LI7" s="47"/>
+      <c r="LJ7" s="47"/>
+      <c r="LK7" s="47"/>
+      <c r="LL7" s="47"/>
+      <c r="LM7" s="47"/>
+      <c r="LN7" s="47"/>
+      <c r="LO7" s="47"/>
+      <c r="LP7" s="47"/>
+      <c r="LQ7" s="47"/>
+      <c r="LR7" s="47"/>
+      <c r="LS7" s="47"/>
+      <c r="LT7" s="47"/>
+      <c r="LU7" s="47"/>
+      <c r="LV7" s="47"/>
+      <c r="LW7" s="47"/>
+      <c r="LX7" s="47"/>
+      <c r="LY7" s="47"/>
+      <c r="LZ7" s="47"/>
+      <c r="MA7" s="47"/>
+      <c r="MB7" s="47"/>
+      <c r="MC7" s="47"/>
+      <c r="MD7" s="47"/>
+      <c r="ME7" s="47"/>
+      <c r="MF7" s="47"/>
+      <c r="MG7" s="47"/>
+      <c r="MH7" s="47"/>
+      <c r="MI7" s="42"/>
+      <c r="MJ7" s="42"/>
+      <c r="MK7" s="42"/>
+      <c r="ML7" s="42"/>
+      <c r="MM7" s="42"/>
+      <c r="MN7" s="42"/>
+      <c r="MO7" s="42"/>
+      <c r="MP7" s="42"/>
+      <c r="MQ7" s="42"/>
+      <c r="MR7" s="42"/>
+      <c r="MS7" s="42"/>
+      <c r="MT7" s="42"/>
+      <c r="MU7" s="42"/>
+      <c r="MV7" s="42"/>
+      <c r="MW7" s="15"/>
+      <c r="MX7" s="15"/>
+      <c r="MY7" s="15"/>
+      <c r="MZ7" s="15"/>
+      <c r="NA7" s="53"/>
+      <c r="NB7" s="53"/>
+      <c r="NC7" s="53"/>
+      <c r="ND7" s="53"/>
+      <c r="NE7" s="53"/>
+      <c r="NF7" s="53"/>
+      <c r="NG7" s="53"/>
+      <c r="NH7" s="53"/>
+      <c r="NI7" s="53"/>
+      <c r="NJ7" s="53"/>
     </row>
   </sheetData>
   <autoFilter ref="A6:MZ6" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <mergeCells count="44">
+  <mergeCells count="45">
+    <mergeCell ref="NH6:NI6"/>
+    <mergeCell ref="NG4:NI5"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A4:B5"/>
+    <mergeCell ref="C4:H5"/>
+    <mergeCell ref="I4:M5"/>
+    <mergeCell ref="N4:P5"/>
+    <mergeCell ref="Q4:U5"/>
+    <mergeCell ref="V4:AB5"/>
+    <mergeCell ref="AC4:AE5"/>
+    <mergeCell ref="AF4:AG5"/>
+    <mergeCell ref="AH4:AL5"/>
+    <mergeCell ref="AM4:BN5"/>
+    <mergeCell ref="BO4:BX4"/>
+    <mergeCell ref="BY4:CH4"/>
+    <mergeCell ref="CI4:CR4"/>
+    <mergeCell ref="CS4:DB4"/>
+    <mergeCell ref="DC4:DL4"/>
+    <mergeCell ref="DM4:DV4"/>
+    <mergeCell ref="DW4:EF4"/>
+    <mergeCell ref="EG4:EP4"/>
+    <mergeCell ref="EQ4:EZ4"/>
+    <mergeCell ref="FA4:FJ4"/>
+    <mergeCell ref="FK4:FT4"/>
+    <mergeCell ref="FU4:GD4"/>
+    <mergeCell ref="GE4:GN4"/>
+    <mergeCell ref="GO4:GX4"/>
+    <mergeCell ref="GY4:HH4"/>
+    <mergeCell ref="HI4:HR4"/>
+    <mergeCell ref="HS4:IB4"/>
+    <mergeCell ref="IC4:IL4"/>
+    <mergeCell ref="IM4:IV4"/>
+    <mergeCell ref="IW4:JF4"/>
+    <mergeCell ref="JG4:JP4"/>
+    <mergeCell ref="JQ4:JZ4"/>
+    <mergeCell ref="KA4:KJ4"/>
     <mergeCell ref="MI4:MV5"/>
     <mergeCell ref="MW4:MY5"/>
     <mergeCell ref="NA4:NF5"/>
-    <mergeCell ref="NG4:NH5"/>
     <mergeCell ref="KK4:KT4"/>
     <mergeCell ref="KU4:LD4"/>
     <mergeCell ref="LE4:LN4"/>
     <mergeCell ref="LO4:LX4"/>
     <mergeCell ref="LY4:MH4"/>
-    <mergeCell ref="IM4:IV4"/>
-    <mergeCell ref="IW4:JF4"/>
-    <mergeCell ref="JG4:JP4"/>
-    <mergeCell ref="JQ4:JZ4"/>
-    <mergeCell ref="KA4:KJ4"/>
-    <mergeCell ref="GO4:GX4"/>
-    <mergeCell ref="GY4:HH4"/>
-    <mergeCell ref="HI4:HR4"/>
-    <mergeCell ref="HS4:IB4"/>
-    <mergeCell ref="IC4:IL4"/>
-    <mergeCell ref="EQ4:EZ4"/>
-    <mergeCell ref="FA4:FJ4"/>
-    <mergeCell ref="FK4:FT4"/>
-    <mergeCell ref="FU4:GD4"/>
-    <mergeCell ref="GE4:GN4"/>
-    <mergeCell ref="CS4:DB4"/>
-    <mergeCell ref="DC4:DL4"/>
-    <mergeCell ref="DM4:DV4"/>
-    <mergeCell ref="DW4:EF4"/>
-    <mergeCell ref="EG4:EP4"/>
-    <mergeCell ref="AH4:AL5"/>
-    <mergeCell ref="AM4:BN5"/>
-    <mergeCell ref="BO4:BX4"/>
-    <mergeCell ref="BY4:CH4"/>
-    <mergeCell ref="CI4:CR4"/>
-    <mergeCell ref="N4:P5"/>
-    <mergeCell ref="Q4:U5"/>
-    <mergeCell ref="V4:AB5"/>
-    <mergeCell ref="AC4:AE5"/>
-    <mergeCell ref="AF4:AG5"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A4:B5"/>
-    <mergeCell ref="C4:H5"/>
-    <mergeCell ref="I4:M5"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:A6">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>

--- a/src/plugins/downloads/helpers/fcerm1/fcerm1_template.xlsx
+++ b/src/plugins/downloads/helpers/fcerm1/fcerm1_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/795110/Documents/Fujale-Space/Work/Projects/EA/FCRM/PAFs/Remote/migration/pafs-backend-api/src/plugins/downloads/helpers/fcerm1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF37731B-D2B5-9F44-A18A-33B688FC8F50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED701F2F-7F91-5245-B119-531D733FD5E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-2800" yWindow="-21000" windowWidth="38400" windowHeight="21000" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Master local choices'!$A$6:$MZ$6</definedName>
   </definedNames>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1332,7 +1332,7 @@
     <t>PSO Name</t>
   </si>
   <si>
-    <t>PAFS Base 2026/27</t>
+    <t>PAFS Base 2023/24</t>
   </si>
 </sst>
 </file>
@@ -1862,101 +1862,101 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="11" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="21" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="20" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="11" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="10">
@@ -2269,10 +2269,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:374" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="62" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="73"/>
+      <c r="B1" s="62"/>
       <c r="C1" s="7"/>
       <c r="D1" s="7"/>
       <c r="E1" s="8"/>
@@ -2647,10 +2647,10 @@
       <c r="NJ1" s="15"/>
     </row>
     <row r="2" spans="1:374" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="74" t="s">
+      <c r="A2" s="63" t="s">
         <v>421</v>
       </c>
-      <c r="B2" s="74"/>
+      <c r="B2" s="63"/>
       <c r="C2" s="7"/>
       <c r="D2" s="16"/>
       <c r="E2" s="8"/>
@@ -3401,530 +3401,530 @@
       <c r="NJ3" s="15"/>
     </row>
     <row r="4" spans="1:374" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="75" t="s">
+      <c r="A4" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="75"/>
-      <c r="C4" s="76" t="s">
+      <c r="B4" s="64"/>
+      <c r="C4" s="65" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="76"/>
-      <c r="E4" s="76"/>
-      <c r="F4" s="76"/>
-      <c r="G4" s="76"/>
-      <c r="H4" s="76"/>
-      <c r="I4" s="77" t="s">
+      <c r="D4" s="65"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="66" t="s">
         <v>3</v>
       </c>
-      <c r="J4" s="77"/>
-      <c r="K4" s="77"/>
-      <c r="L4" s="77"/>
-      <c r="M4" s="77"/>
-      <c r="N4" s="68" t="s">
+      <c r="J4" s="66"/>
+      <c r="K4" s="66"/>
+      <c r="L4" s="66"/>
+      <c r="M4" s="66"/>
+      <c r="N4" s="67" t="s">
         <v>4</v>
       </c>
-      <c r="O4" s="68"/>
-      <c r="P4" s="68"/>
-      <c r="Q4" s="69" t="s">
+      <c r="O4" s="67"/>
+      <c r="P4" s="67"/>
+      <c r="Q4" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="R4" s="69"/>
-      <c r="S4" s="69"/>
-      <c r="T4" s="69"/>
-      <c r="U4" s="69"/>
-      <c r="V4" s="70" t="s">
+      <c r="R4" s="68"/>
+      <c r="S4" s="68"/>
+      <c r="T4" s="68"/>
+      <c r="U4" s="68"/>
+      <c r="V4" s="69" t="s">
         <v>6</v>
       </c>
-      <c r="W4" s="70"/>
-      <c r="X4" s="70"/>
-      <c r="Y4" s="70"/>
-      <c r="Z4" s="70"/>
-      <c r="AA4" s="70"/>
-      <c r="AB4" s="70"/>
-      <c r="AC4" s="71" t="s">
+      <c r="W4" s="69"/>
+      <c r="X4" s="69"/>
+      <c r="Y4" s="69"/>
+      <c r="Z4" s="69"/>
+      <c r="AA4" s="69"/>
+      <c r="AB4" s="69"/>
+      <c r="AC4" s="70" t="s">
         <v>7</v>
       </c>
-      <c r="AD4" s="71"/>
-      <c r="AE4" s="71"/>
-      <c r="AF4" s="72" t="s">
+      <c r="AD4" s="70"/>
+      <c r="AE4" s="70"/>
+      <c r="AF4" s="71" t="s">
         <v>8</v>
       </c>
-      <c r="AG4" s="72"/>
-      <c r="AH4" s="66"/>
-      <c r="AI4" s="66"/>
-      <c r="AJ4" s="66"/>
-      <c r="AK4" s="66"/>
-      <c r="AL4" s="66"/>
-      <c r="AM4" s="67" t="s">
+      <c r="AG4" s="71"/>
+      <c r="AH4" s="72"/>
+      <c r="AI4" s="72"/>
+      <c r="AJ4" s="72"/>
+      <c r="AK4" s="72"/>
+      <c r="AL4" s="72"/>
+      <c r="AM4" s="73" t="s">
         <v>9</v>
       </c>
-      <c r="AN4" s="67"/>
-      <c r="AO4" s="67"/>
-      <c r="AP4" s="67"/>
-      <c r="AQ4" s="67"/>
-      <c r="AR4" s="67"/>
-      <c r="AS4" s="67"/>
-      <c r="AT4" s="67"/>
-      <c r="AU4" s="67"/>
-      <c r="AV4" s="67"/>
-      <c r="AW4" s="67"/>
-      <c r="AX4" s="67"/>
-      <c r="AY4" s="67"/>
-      <c r="AZ4" s="67"/>
-      <c r="BA4" s="67"/>
-      <c r="BB4" s="67"/>
-      <c r="BC4" s="67"/>
-      <c r="BD4" s="67"/>
-      <c r="BE4" s="67"/>
-      <c r="BF4" s="67"/>
-      <c r="BG4" s="67"/>
-      <c r="BH4" s="67"/>
-      <c r="BI4" s="67"/>
-      <c r="BJ4" s="67"/>
-      <c r="BK4" s="67"/>
-      <c r="BL4" s="67"/>
-      <c r="BM4" s="67"/>
-      <c r="BN4" s="67"/>
-      <c r="BO4" s="56" t="s">
+      <c r="AN4" s="73"/>
+      <c r="AO4" s="73"/>
+      <c r="AP4" s="73"/>
+      <c r="AQ4" s="73"/>
+      <c r="AR4" s="73"/>
+      <c r="AS4" s="73"/>
+      <c r="AT4" s="73"/>
+      <c r="AU4" s="73"/>
+      <c r="AV4" s="73"/>
+      <c r="AW4" s="73"/>
+      <c r="AX4" s="73"/>
+      <c r="AY4" s="73"/>
+      <c r="AZ4" s="73"/>
+      <c r="BA4" s="73"/>
+      <c r="BB4" s="73"/>
+      <c r="BC4" s="73"/>
+      <c r="BD4" s="73"/>
+      <c r="BE4" s="73"/>
+      <c r="BF4" s="73"/>
+      <c r="BG4" s="73"/>
+      <c r="BH4" s="73"/>
+      <c r="BI4" s="73"/>
+      <c r="BJ4" s="73"/>
+      <c r="BK4" s="73"/>
+      <c r="BL4" s="73"/>
+      <c r="BM4" s="73"/>
+      <c r="BN4" s="73"/>
+      <c r="BO4" s="74" t="s">
         <v>10</v>
       </c>
-      <c r="BP4" s="56"/>
-      <c r="BQ4" s="56"/>
-      <c r="BR4" s="56"/>
-      <c r="BS4" s="56"/>
-      <c r="BT4" s="56"/>
-      <c r="BU4" s="56"/>
-      <c r="BV4" s="56"/>
-      <c r="BW4" s="56"/>
-      <c r="BX4" s="56"/>
-      <c r="BY4" s="65" t="s">
+      <c r="BP4" s="74"/>
+      <c r="BQ4" s="74"/>
+      <c r="BR4" s="74"/>
+      <c r="BS4" s="74"/>
+      <c r="BT4" s="74"/>
+      <c r="BU4" s="74"/>
+      <c r="BV4" s="74"/>
+      <c r="BW4" s="74"/>
+      <c r="BX4" s="74"/>
+      <c r="BY4" s="75" t="s">
         <v>11</v>
       </c>
-      <c r="BZ4" s="65"/>
-      <c r="CA4" s="65"/>
-      <c r="CB4" s="65"/>
-      <c r="CC4" s="65"/>
-      <c r="CD4" s="65"/>
-      <c r="CE4" s="65"/>
-      <c r="CF4" s="65"/>
-      <c r="CG4" s="65"/>
-      <c r="CH4" s="65"/>
-      <c r="CI4" s="60" t="s">
+      <c r="BZ4" s="75"/>
+      <c r="CA4" s="75"/>
+      <c r="CB4" s="75"/>
+      <c r="CC4" s="75"/>
+      <c r="CD4" s="75"/>
+      <c r="CE4" s="75"/>
+      <c r="CF4" s="75"/>
+      <c r="CG4" s="75"/>
+      <c r="CH4" s="75"/>
+      <c r="CI4" s="76" t="s">
         <v>12</v>
       </c>
-      <c r="CJ4" s="60"/>
-      <c r="CK4" s="60"/>
-      <c r="CL4" s="60"/>
-      <c r="CM4" s="60"/>
-      <c r="CN4" s="60"/>
-      <c r="CO4" s="60"/>
-      <c r="CP4" s="60"/>
-      <c r="CQ4" s="60"/>
-      <c r="CR4" s="60"/>
-      <c r="CS4" s="65" t="s">
+      <c r="CJ4" s="76"/>
+      <c r="CK4" s="76"/>
+      <c r="CL4" s="76"/>
+      <c r="CM4" s="76"/>
+      <c r="CN4" s="76"/>
+      <c r="CO4" s="76"/>
+      <c r="CP4" s="76"/>
+      <c r="CQ4" s="76"/>
+      <c r="CR4" s="76"/>
+      <c r="CS4" s="75" t="s">
         <v>13</v>
       </c>
-      <c r="CT4" s="65"/>
-      <c r="CU4" s="65"/>
-      <c r="CV4" s="65"/>
-      <c r="CW4" s="65"/>
-      <c r="CX4" s="65"/>
-      <c r="CY4" s="65"/>
-      <c r="CZ4" s="65"/>
-      <c r="DA4" s="65"/>
-      <c r="DB4" s="65"/>
-      <c r="DC4" s="60" t="s">
+      <c r="CT4" s="75"/>
+      <c r="CU4" s="75"/>
+      <c r="CV4" s="75"/>
+      <c r="CW4" s="75"/>
+      <c r="CX4" s="75"/>
+      <c r="CY4" s="75"/>
+      <c r="CZ4" s="75"/>
+      <c r="DA4" s="75"/>
+      <c r="DB4" s="75"/>
+      <c r="DC4" s="76" t="s">
         <v>14</v>
       </c>
-      <c r="DD4" s="60"/>
-      <c r="DE4" s="60"/>
-      <c r="DF4" s="60"/>
-      <c r="DG4" s="60"/>
-      <c r="DH4" s="60"/>
-      <c r="DI4" s="60"/>
-      <c r="DJ4" s="60"/>
-      <c r="DK4" s="60"/>
-      <c r="DL4" s="60"/>
-      <c r="DM4" s="65" t="s">
+      <c r="DD4" s="76"/>
+      <c r="DE4" s="76"/>
+      <c r="DF4" s="76"/>
+      <c r="DG4" s="76"/>
+      <c r="DH4" s="76"/>
+      <c r="DI4" s="76"/>
+      <c r="DJ4" s="76"/>
+      <c r="DK4" s="76"/>
+      <c r="DL4" s="76"/>
+      <c r="DM4" s="75" t="s">
         <v>15</v>
       </c>
-      <c r="DN4" s="65"/>
-      <c r="DO4" s="65"/>
-      <c r="DP4" s="65"/>
-      <c r="DQ4" s="65"/>
-      <c r="DR4" s="65"/>
-      <c r="DS4" s="65"/>
-      <c r="DT4" s="65"/>
-      <c r="DU4" s="65"/>
-      <c r="DV4" s="65"/>
-      <c r="DW4" s="60" t="s">
+      <c r="DN4" s="75"/>
+      <c r="DO4" s="75"/>
+      <c r="DP4" s="75"/>
+      <c r="DQ4" s="75"/>
+      <c r="DR4" s="75"/>
+      <c r="DS4" s="75"/>
+      <c r="DT4" s="75"/>
+      <c r="DU4" s="75"/>
+      <c r="DV4" s="75"/>
+      <c r="DW4" s="76" t="s">
         <v>16</v>
       </c>
-      <c r="DX4" s="60"/>
-      <c r="DY4" s="60"/>
-      <c r="DZ4" s="60"/>
-      <c r="EA4" s="60"/>
-      <c r="EB4" s="60"/>
-      <c r="EC4" s="60"/>
-      <c r="ED4" s="60"/>
-      <c r="EE4" s="60"/>
-      <c r="EF4" s="60"/>
-      <c r="EG4" s="65" t="s">
+      <c r="DX4" s="76"/>
+      <c r="DY4" s="76"/>
+      <c r="DZ4" s="76"/>
+      <c r="EA4" s="76"/>
+      <c r="EB4" s="76"/>
+      <c r="EC4" s="76"/>
+      <c r="ED4" s="76"/>
+      <c r="EE4" s="76"/>
+      <c r="EF4" s="76"/>
+      <c r="EG4" s="75" t="s">
         <v>17</v>
       </c>
-      <c r="EH4" s="65"/>
-      <c r="EI4" s="65"/>
-      <c r="EJ4" s="65"/>
-      <c r="EK4" s="65"/>
-      <c r="EL4" s="65"/>
-      <c r="EM4" s="65"/>
-      <c r="EN4" s="65"/>
-      <c r="EO4" s="65"/>
-      <c r="EP4" s="65"/>
-      <c r="EQ4" s="60" t="s">
+      <c r="EH4" s="75"/>
+      <c r="EI4" s="75"/>
+      <c r="EJ4" s="75"/>
+      <c r="EK4" s="75"/>
+      <c r="EL4" s="75"/>
+      <c r="EM4" s="75"/>
+      <c r="EN4" s="75"/>
+      <c r="EO4" s="75"/>
+      <c r="EP4" s="75"/>
+      <c r="EQ4" s="76" t="s">
         <v>18</v>
       </c>
-      <c r="ER4" s="60"/>
-      <c r="ES4" s="60"/>
-      <c r="ET4" s="60"/>
-      <c r="EU4" s="60"/>
-      <c r="EV4" s="60"/>
-      <c r="EW4" s="60"/>
-      <c r="EX4" s="60"/>
-      <c r="EY4" s="60"/>
-      <c r="EZ4" s="60"/>
-      <c r="FA4" s="61" t="s">
+      <c r="ER4" s="76"/>
+      <c r="ES4" s="76"/>
+      <c r="ET4" s="76"/>
+      <c r="EU4" s="76"/>
+      <c r="EV4" s="76"/>
+      <c r="EW4" s="76"/>
+      <c r="EX4" s="76"/>
+      <c r="EY4" s="76"/>
+      <c r="EZ4" s="76"/>
+      <c r="FA4" s="77" t="s">
         <v>19</v>
       </c>
-      <c r="FB4" s="61"/>
-      <c r="FC4" s="61"/>
-      <c r="FD4" s="61"/>
-      <c r="FE4" s="61"/>
-      <c r="FF4" s="61"/>
-      <c r="FG4" s="61"/>
-      <c r="FH4" s="61"/>
-      <c r="FI4" s="61"/>
-      <c r="FJ4" s="61"/>
-      <c r="FK4" s="62" t="s">
+      <c r="FB4" s="77"/>
+      <c r="FC4" s="77"/>
+      <c r="FD4" s="77"/>
+      <c r="FE4" s="77"/>
+      <c r="FF4" s="77"/>
+      <c r="FG4" s="77"/>
+      <c r="FH4" s="77"/>
+      <c r="FI4" s="77"/>
+      <c r="FJ4" s="77"/>
+      <c r="FK4" s="78" t="s">
         <v>20</v>
       </c>
-      <c r="FL4" s="62"/>
-      <c r="FM4" s="62"/>
-      <c r="FN4" s="62"/>
-      <c r="FO4" s="62"/>
-      <c r="FP4" s="62"/>
-      <c r="FQ4" s="62"/>
-      <c r="FR4" s="62"/>
-      <c r="FS4" s="62"/>
-      <c r="FT4" s="62"/>
-      <c r="FU4" s="63" t="s">
+      <c r="FL4" s="78"/>
+      <c r="FM4" s="78"/>
+      <c r="FN4" s="78"/>
+      <c r="FO4" s="78"/>
+      <c r="FP4" s="78"/>
+      <c r="FQ4" s="78"/>
+      <c r="FR4" s="78"/>
+      <c r="FS4" s="78"/>
+      <c r="FT4" s="78"/>
+      <c r="FU4" s="79" t="s">
         <v>21</v>
       </c>
-      <c r="FV4" s="63"/>
-      <c r="FW4" s="63"/>
-      <c r="FX4" s="63"/>
-      <c r="FY4" s="63"/>
-      <c r="FZ4" s="63"/>
-      <c r="GA4" s="63"/>
-      <c r="GB4" s="63"/>
-      <c r="GC4" s="63"/>
-      <c r="GD4" s="63"/>
-      <c r="GE4" s="64" t="s">
+      <c r="FV4" s="79"/>
+      <c r="FW4" s="79"/>
+      <c r="FX4" s="79"/>
+      <c r="FY4" s="79"/>
+      <c r="FZ4" s="79"/>
+      <c r="GA4" s="79"/>
+      <c r="GB4" s="79"/>
+      <c r="GC4" s="79"/>
+      <c r="GD4" s="79"/>
+      <c r="GE4" s="80" t="s">
         <v>22</v>
       </c>
-      <c r="GF4" s="64"/>
-      <c r="GG4" s="64"/>
-      <c r="GH4" s="64"/>
-      <c r="GI4" s="64"/>
-      <c r="GJ4" s="64"/>
-      <c r="GK4" s="64"/>
-      <c r="GL4" s="64"/>
-      <c r="GM4" s="64"/>
-      <c r="GN4" s="64"/>
-      <c r="GO4" s="58" t="s">
+      <c r="GF4" s="80"/>
+      <c r="GG4" s="80"/>
+      <c r="GH4" s="80"/>
+      <c r="GI4" s="80"/>
+      <c r="GJ4" s="80"/>
+      <c r="GK4" s="80"/>
+      <c r="GL4" s="80"/>
+      <c r="GM4" s="80"/>
+      <c r="GN4" s="80"/>
+      <c r="GO4" s="81" t="s">
         <v>23</v>
       </c>
-      <c r="GP4" s="58"/>
-      <c r="GQ4" s="58"/>
-      <c r="GR4" s="58"/>
-      <c r="GS4" s="58"/>
-      <c r="GT4" s="58"/>
-      <c r="GU4" s="58"/>
-      <c r="GV4" s="58"/>
-      <c r="GW4" s="58"/>
-      <c r="GX4" s="58"/>
-      <c r="GY4" s="59" t="s">
+      <c r="GP4" s="81"/>
+      <c r="GQ4" s="81"/>
+      <c r="GR4" s="81"/>
+      <c r="GS4" s="81"/>
+      <c r="GT4" s="81"/>
+      <c r="GU4" s="81"/>
+      <c r="GV4" s="81"/>
+      <c r="GW4" s="81"/>
+      <c r="GX4" s="81"/>
+      <c r="GY4" s="82" t="s">
         <v>24</v>
       </c>
-      <c r="GZ4" s="59"/>
-      <c r="HA4" s="59"/>
-      <c r="HB4" s="59"/>
-      <c r="HC4" s="59"/>
-      <c r="HD4" s="59"/>
-      <c r="HE4" s="59"/>
-      <c r="HF4" s="59"/>
-      <c r="HG4" s="59"/>
-      <c r="HH4" s="59"/>
-      <c r="HI4" s="56" t="s">
+      <c r="GZ4" s="82"/>
+      <c r="HA4" s="82"/>
+      <c r="HB4" s="82"/>
+      <c r="HC4" s="82"/>
+      <c r="HD4" s="82"/>
+      <c r="HE4" s="82"/>
+      <c r="HF4" s="82"/>
+      <c r="HG4" s="82"/>
+      <c r="HH4" s="82"/>
+      <c r="HI4" s="74" t="s">
         <v>25</v>
       </c>
-      <c r="HJ4" s="56"/>
-      <c r="HK4" s="56"/>
-      <c r="HL4" s="56"/>
-      <c r="HM4" s="56"/>
-      <c r="HN4" s="56"/>
-      <c r="HO4" s="56"/>
-      <c r="HP4" s="56"/>
-      <c r="HQ4" s="56"/>
-      <c r="HR4" s="56"/>
-      <c r="HS4" s="56" t="s">
+      <c r="HJ4" s="74"/>
+      <c r="HK4" s="74"/>
+      <c r="HL4" s="74"/>
+      <c r="HM4" s="74"/>
+      <c r="HN4" s="74"/>
+      <c r="HO4" s="74"/>
+      <c r="HP4" s="74"/>
+      <c r="HQ4" s="74"/>
+      <c r="HR4" s="74"/>
+      <c r="HS4" s="74" t="s">
         <v>26</v>
       </c>
-      <c r="HT4" s="56"/>
-      <c r="HU4" s="56"/>
-      <c r="HV4" s="56"/>
-      <c r="HW4" s="56"/>
-      <c r="HX4" s="56"/>
-      <c r="HY4" s="56"/>
-      <c r="HZ4" s="56"/>
-      <c r="IA4" s="56"/>
-      <c r="IB4" s="56"/>
-      <c r="IC4" s="56" t="s">
+      <c r="HT4" s="74"/>
+      <c r="HU4" s="74"/>
+      <c r="HV4" s="74"/>
+      <c r="HW4" s="74"/>
+      <c r="HX4" s="74"/>
+      <c r="HY4" s="74"/>
+      <c r="HZ4" s="74"/>
+      <c r="IA4" s="74"/>
+      <c r="IB4" s="74"/>
+      <c r="IC4" s="74" t="s">
         <v>27</v>
       </c>
-      <c r="ID4" s="56"/>
-      <c r="IE4" s="56"/>
-      <c r="IF4" s="56"/>
-      <c r="IG4" s="56"/>
-      <c r="IH4" s="56"/>
-      <c r="II4" s="56"/>
-      <c r="IJ4" s="56"/>
-      <c r="IK4" s="56"/>
-      <c r="IL4" s="56"/>
-      <c r="IM4" s="56" t="s">
+      <c r="ID4" s="74"/>
+      <c r="IE4" s="74"/>
+      <c r="IF4" s="74"/>
+      <c r="IG4" s="74"/>
+      <c r="IH4" s="74"/>
+      <c r="II4" s="74"/>
+      <c r="IJ4" s="74"/>
+      <c r="IK4" s="74"/>
+      <c r="IL4" s="74"/>
+      <c r="IM4" s="74" t="s">
         <v>28</v>
       </c>
-      <c r="IN4" s="56"/>
-      <c r="IO4" s="56"/>
-      <c r="IP4" s="56"/>
-      <c r="IQ4" s="56"/>
-      <c r="IR4" s="56"/>
-      <c r="IS4" s="56"/>
-      <c r="IT4" s="56"/>
-      <c r="IU4" s="56"/>
-      <c r="IV4" s="56"/>
-      <c r="IW4" s="56" t="s">
+      <c r="IN4" s="74"/>
+      <c r="IO4" s="74"/>
+      <c r="IP4" s="74"/>
+      <c r="IQ4" s="74"/>
+      <c r="IR4" s="74"/>
+      <c r="IS4" s="74"/>
+      <c r="IT4" s="74"/>
+      <c r="IU4" s="74"/>
+      <c r="IV4" s="74"/>
+      <c r="IW4" s="74" t="s">
         <v>29</v>
       </c>
-      <c r="IX4" s="56"/>
-      <c r="IY4" s="56"/>
-      <c r="IZ4" s="56"/>
-      <c r="JA4" s="56"/>
-      <c r="JB4" s="56"/>
-      <c r="JC4" s="56"/>
-      <c r="JD4" s="56"/>
-      <c r="JE4" s="56"/>
-      <c r="JF4" s="56"/>
-      <c r="JG4" s="56" t="s">
+      <c r="IX4" s="74"/>
+      <c r="IY4" s="74"/>
+      <c r="IZ4" s="74"/>
+      <c r="JA4" s="74"/>
+      <c r="JB4" s="74"/>
+      <c r="JC4" s="74"/>
+      <c r="JD4" s="74"/>
+      <c r="JE4" s="74"/>
+      <c r="JF4" s="74"/>
+      <c r="JG4" s="74" t="s">
         <v>30</v>
       </c>
-      <c r="JH4" s="56"/>
-      <c r="JI4" s="56"/>
-      <c r="JJ4" s="56"/>
-      <c r="JK4" s="56"/>
-      <c r="JL4" s="56"/>
-      <c r="JM4" s="56"/>
-      <c r="JN4" s="56"/>
-      <c r="JO4" s="56"/>
-      <c r="JP4" s="56"/>
-      <c r="JQ4" s="56" t="s">
+      <c r="JH4" s="74"/>
+      <c r="JI4" s="74"/>
+      <c r="JJ4" s="74"/>
+      <c r="JK4" s="74"/>
+      <c r="JL4" s="74"/>
+      <c r="JM4" s="74"/>
+      <c r="JN4" s="74"/>
+      <c r="JO4" s="74"/>
+      <c r="JP4" s="74"/>
+      <c r="JQ4" s="74" t="s">
         <v>31</v>
       </c>
-      <c r="JR4" s="56"/>
-      <c r="JS4" s="56"/>
-      <c r="JT4" s="56"/>
-      <c r="JU4" s="56"/>
-      <c r="JV4" s="56"/>
-      <c r="JW4" s="56"/>
-      <c r="JX4" s="56"/>
-      <c r="JY4" s="56"/>
-      <c r="JZ4" s="56"/>
-      <c r="KA4" s="56" t="s">
+      <c r="JR4" s="74"/>
+      <c r="JS4" s="74"/>
+      <c r="JT4" s="74"/>
+      <c r="JU4" s="74"/>
+      <c r="JV4" s="74"/>
+      <c r="JW4" s="74"/>
+      <c r="JX4" s="74"/>
+      <c r="JY4" s="74"/>
+      <c r="JZ4" s="74"/>
+      <c r="KA4" s="74" t="s">
         <v>32</v>
       </c>
-      <c r="KB4" s="56"/>
-      <c r="KC4" s="56"/>
-      <c r="KD4" s="56"/>
-      <c r="KE4" s="56"/>
-      <c r="KF4" s="56"/>
-      <c r="KG4" s="56"/>
-      <c r="KH4" s="56"/>
-      <c r="KI4" s="56"/>
-      <c r="KJ4" s="56"/>
-      <c r="KK4" s="56" t="s">
+      <c r="KB4" s="74"/>
+      <c r="KC4" s="74"/>
+      <c r="KD4" s="74"/>
+      <c r="KE4" s="74"/>
+      <c r="KF4" s="74"/>
+      <c r="KG4" s="74"/>
+      <c r="KH4" s="74"/>
+      <c r="KI4" s="74"/>
+      <c r="KJ4" s="74"/>
+      <c r="KK4" s="74" t="s">
         <v>33</v>
       </c>
-      <c r="KL4" s="56"/>
-      <c r="KM4" s="56"/>
-      <c r="KN4" s="56"/>
-      <c r="KO4" s="56"/>
-      <c r="KP4" s="56"/>
-      <c r="KQ4" s="56"/>
-      <c r="KR4" s="56"/>
-      <c r="KS4" s="56"/>
-      <c r="KT4" s="56"/>
-      <c r="KU4" s="57" t="s">
+      <c r="KL4" s="74"/>
+      <c r="KM4" s="74"/>
+      <c r="KN4" s="74"/>
+      <c r="KO4" s="74"/>
+      <c r="KP4" s="74"/>
+      <c r="KQ4" s="74"/>
+      <c r="KR4" s="74"/>
+      <c r="KS4" s="74"/>
+      <c r="KT4" s="74"/>
+      <c r="KU4" s="85" t="s">
         <v>34</v>
       </c>
-      <c r="KV4" s="57"/>
-      <c r="KW4" s="57"/>
-      <c r="KX4" s="57"/>
-      <c r="KY4" s="57"/>
-      <c r="KZ4" s="57"/>
-      <c r="LA4" s="57"/>
-      <c r="LB4" s="57"/>
-      <c r="LC4" s="57"/>
-      <c r="LD4" s="57"/>
-      <c r="LE4" s="57" t="s">
+      <c r="KV4" s="85"/>
+      <c r="KW4" s="85"/>
+      <c r="KX4" s="85"/>
+      <c r="KY4" s="85"/>
+      <c r="KZ4" s="85"/>
+      <c r="LA4" s="85"/>
+      <c r="LB4" s="85"/>
+      <c r="LC4" s="85"/>
+      <c r="LD4" s="85"/>
+      <c r="LE4" s="85" t="s">
         <v>35</v>
       </c>
-      <c r="LF4" s="57"/>
-      <c r="LG4" s="57"/>
-      <c r="LH4" s="57"/>
-      <c r="LI4" s="57"/>
-      <c r="LJ4" s="57"/>
-      <c r="LK4" s="57"/>
-      <c r="LL4" s="57"/>
-      <c r="LM4" s="57"/>
-      <c r="LN4" s="57"/>
-      <c r="LO4" s="57" t="s">
+      <c r="LF4" s="85"/>
+      <c r="LG4" s="85"/>
+      <c r="LH4" s="85"/>
+      <c r="LI4" s="85"/>
+      <c r="LJ4" s="85"/>
+      <c r="LK4" s="85"/>
+      <c r="LL4" s="85"/>
+      <c r="LM4" s="85"/>
+      <c r="LN4" s="85"/>
+      <c r="LO4" s="85" t="s">
         <v>36</v>
       </c>
-      <c r="LP4" s="57"/>
-      <c r="LQ4" s="57"/>
-      <c r="LR4" s="57"/>
-      <c r="LS4" s="57"/>
-      <c r="LT4" s="57"/>
-      <c r="LU4" s="57"/>
-      <c r="LV4" s="57"/>
-      <c r="LW4" s="57"/>
-      <c r="LX4" s="57"/>
-      <c r="LY4" s="57" t="s">
+      <c r="LP4" s="85"/>
+      <c r="LQ4" s="85"/>
+      <c r="LR4" s="85"/>
+      <c r="LS4" s="85"/>
+      <c r="LT4" s="85"/>
+      <c r="LU4" s="85"/>
+      <c r="LV4" s="85"/>
+      <c r="LW4" s="85"/>
+      <c r="LX4" s="85"/>
+      <c r="LY4" s="85" t="s">
         <v>37</v>
       </c>
-      <c r="LZ4" s="57"/>
-      <c r="MA4" s="57"/>
-      <c r="MB4" s="57"/>
-      <c r="MC4" s="57"/>
-      <c r="MD4" s="57"/>
-      <c r="ME4" s="57"/>
-      <c r="MF4" s="57"/>
-      <c r="MG4" s="57"/>
-      <c r="MH4" s="57"/>
-      <c r="MI4" s="54" t="s">
+      <c r="LZ4" s="85"/>
+      <c r="MA4" s="85"/>
+      <c r="MB4" s="85"/>
+      <c r="MC4" s="85"/>
+      <c r="MD4" s="85"/>
+      <c r="ME4" s="85"/>
+      <c r="MF4" s="85"/>
+      <c r="MG4" s="85"/>
+      <c r="MH4" s="85"/>
+      <c r="MI4" s="83" t="s">
         <v>38</v>
       </c>
-      <c r="MJ4" s="54"/>
-      <c r="MK4" s="54"/>
-      <c r="ML4" s="54"/>
-      <c r="MM4" s="54"/>
-      <c r="MN4" s="54"/>
-      <c r="MO4" s="54"/>
-      <c r="MP4" s="54"/>
-      <c r="MQ4" s="54"/>
-      <c r="MR4" s="54"/>
-      <c r="MS4" s="54"/>
-      <c r="MT4" s="54"/>
-      <c r="MU4" s="54"/>
-      <c r="MV4" s="54"/>
-      <c r="MW4" s="55" t="s">
+      <c r="MJ4" s="83"/>
+      <c r="MK4" s="83"/>
+      <c r="ML4" s="83"/>
+      <c r="MM4" s="83"/>
+      <c r="MN4" s="83"/>
+      <c r="MO4" s="83"/>
+      <c r="MP4" s="83"/>
+      <c r="MQ4" s="83"/>
+      <c r="MR4" s="83"/>
+      <c r="MS4" s="83"/>
+      <c r="MT4" s="83"/>
+      <c r="MU4" s="83"/>
+      <c r="MV4" s="83"/>
+      <c r="MW4" s="84" t="s">
         <v>39</v>
       </c>
-      <c r="MX4" s="55"/>
-      <c r="MY4" s="55"/>
+      <c r="MX4" s="84"/>
+      <c r="MY4" s="84"/>
       <c r="MZ4" s="26"/>
-      <c r="NA4" s="55" t="s">
+      <c r="NA4" s="84" t="s">
         <v>40</v>
       </c>
-      <c r="NB4" s="55"/>
-      <c r="NC4" s="55"/>
-      <c r="ND4" s="55"/>
-      <c r="NE4" s="55"/>
-      <c r="NF4" s="55"/>
-      <c r="NG4" s="80" t="s">
+      <c r="NB4" s="84"/>
+      <c r="NC4" s="84"/>
+      <c r="ND4" s="84"/>
+      <c r="NE4" s="84"/>
+      <c r="NF4" s="84"/>
+      <c r="NG4" s="56" t="s">
         <v>41</v>
       </c>
-      <c r="NH4" s="84"/>
-      <c r="NI4" s="81"/>
+      <c r="NH4" s="57"/>
+      <c r="NI4" s="58"/>
       <c r="NJ4" s="27"/>
     </row>
     <row r="5" spans="1:374" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="75"/>
-      <c r="B5" s="75"/>
-      <c r="C5" s="76"/>
-      <c r="D5" s="76"/>
-      <c r="E5" s="76"/>
-      <c r="F5" s="76"/>
-      <c r="G5" s="76"/>
-      <c r="H5" s="76"/>
-      <c r="I5" s="77"/>
-      <c r="J5" s="77"/>
-      <c r="K5" s="77"/>
-      <c r="L5" s="77"/>
-      <c r="M5" s="77"/>
-      <c r="N5" s="68"/>
-      <c r="O5" s="68"/>
-      <c r="P5" s="68"/>
-      <c r="Q5" s="69"/>
-      <c r="R5" s="69"/>
-      <c r="S5" s="69"/>
-      <c r="T5" s="69"/>
-      <c r="U5" s="69"/>
-      <c r="V5" s="70"/>
-      <c r="W5" s="70"/>
-      <c r="X5" s="70"/>
-      <c r="Y5" s="70"/>
-      <c r="Z5" s="70"/>
-      <c r="AA5" s="70"/>
-      <c r="AB5" s="70"/>
-      <c r="AC5" s="71"/>
-      <c r="AD5" s="71"/>
-      <c r="AE5" s="71"/>
-      <c r="AF5" s="72"/>
-      <c r="AG5" s="72"/>
-      <c r="AH5" s="66"/>
-      <c r="AI5" s="66"/>
-      <c r="AJ5" s="66"/>
-      <c r="AK5" s="66"/>
-      <c r="AL5" s="66"/>
-      <c r="AM5" s="67"/>
-      <c r="AN5" s="67"/>
-      <c r="AO5" s="67"/>
-      <c r="AP5" s="67"/>
-      <c r="AQ5" s="67"/>
-      <c r="AR5" s="67"/>
-      <c r="AS5" s="67"/>
-      <c r="AT5" s="67"/>
-      <c r="AU5" s="67"/>
-      <c r="AV5" s="67"/>
-      <c r="AW5" s="67"/>
-      <c r="AX5" s="67"/>
-      <c r="AY5" s="67"/>
-      <c r="AZ5" s="67"/>
-      <c r="BA5" s="67"/>
-      <c r="BB5" s="67"/>
-      <c r="BC5" s="67"/>
-      <c r="BD5" s="67"/>
-      <c r="BE5" s="67"/>
-      <c r="BF5" s="67"/>
-      <c r="BG5" s="67"/>
-      <c r="BH5" s="67"/>
-      <c r="BI5" s="67"/>
-      <c r="BJ5" s="67"/>
-      <c r="BK5" s="67"/>
-      <c r="BL5" s="67"/>
-      <c r="BM5" s="67"/>
-      <c r="BN5" s="67"/>
+      <c r="A5" s="64"/>
+      <c r="B5" s="64"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="65"/>
+      <c r="E5" s="65"/>
+      <c r="F5" s="65"/>
+      <c r="G5" s="65"/>
+      <c r="H5" s="65"/>
+      <c r="I5" s="66"/>
+      <c r="J5" s="66"/>
+      <c r="K5" s="66"/>
+      <c r="L5" s="66"/>
+      <c r="M5" s="66"/>
+      <c r="N5" s="67"/>
+      <c r="O5" s="67"/>
+      <c r="P5" s="67"/>
+      <c r="Q5" s="68"/>
+      <c r="R5" s="68"/>
+      <c r="S5" s="68"/>
+      <c r="T5" s="68"/>
+      <c r="U5" s="68"/>
+      <c r="V5" s="69"/>
+      <c r="W5" s="69"/>
+      <c r="X5" s="69"/>
+      <c r="Y5" s="69"/>
+      <c r="Z5" s="69"/>
+      <c r="AA5" s="69"/>
+      <c r="AB5" s="69"/>
+      <c r="AC5" s="70"/>
+      <c r="AD5" s="70"/>
+      <c r="AE5" s="70"/>
+      <c r="AF5" s="71"/>
+      <c r="AG5" s="71"/>
+      <c r="AH5" s="72"/>
+      <c r="AI5" s="72"/>
+      <c r="AJ5" s="72"/>
+      <c r="AK5" s="72"/>
+      <c r="AL5" s="72"/>
+      <c r="AM5" s="73"/>
+      <c r="AN5" s="73"/>
+      <c r="AO5" s="73"/>
+      <c r="AP5" s="73"/>
+      <c r="AQ5" s="73"/>
+      <c r="AR5" s="73"/>
+      <c r="AS5" s="73"/>
+      <c r="AT5" s="73"/>
+      <c r="AU5" s="73"/>
+      <c r="AV5" s="73"/>
+      <c r="AW5" s="73"/>
+      <c r="AX5" s="73"/>
+      <c r="AY5" s="73"/>
+      <c r="AZ5" s="73"/>
+      <c r="BA5" s="73"/>
+      <c r="BB5" s="73"/>
+      <c r="BC5" s="73"/>
+      <c r="BD5" s="73"/>
+      <c r="BE5" s="73"/>
+      <c r="BF5" s="73"/>
+      <c r="BG5" s="73"/>
+      <c r="BH5" s="73"/>
+      <c r="BI5" s="73"/>
+      <c r="BJ5" s="73"/>
+      <c r="BK5" s="73"/>
+      <c r="BL5" s="73"/>
+      <c r="BM5" s="73"/>
+      <c r="BN5" s="73"/>
       <c r="BO5" s="28" t="s">
         <v>42</v>
       </c>
@@ -4765,33 +4765,33 @@
       <c r="MH5" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="MI5" s="54"/>
-      <c r="MJ5" s="54"/>
-      <c r="MK5" s="54"/>
-      <c r="ML5" s="54"/>
-      <c r="MM5" s="54"/>
-      <c r="MN5" s="54"/>
-      <c r="MO5" s="54"/>
-      <c r="MP5" s="54"/>
-      <c r="MQ5" s="54"/>
-      <c r="MR5" s="54"/>
-      <c r="MS5" s="54"/>
-      <c r="MT5" s="54"/>
-      <c r="MU5" s="54"/>
-      <c r="MV5" s="54"/>
-      <c r="MW5" s="55"/>
-      <c r="MX5" s="55"/>
-      <c r="MY5" s="55"/>
+      <c r="MI5" s="83"/>
+      <c r="MJ5" s="83"/>
+      <c r="MK5" s="83"/>
+      <c r="ML5" s="83"/>
+      <c r="MM5" s="83"/>
+      <c r="MN5" s="83"/>
+      <c r="MO5" s="83"/>
+      <c r="MP5" s="83"/>
+      <c r="MQ5" s="83"/>
+      <c r="MR5" s="83"/>
+      <c r="MS5" s="83"/>
+      <c r="MT5" s="83"/>
+      <c r="MU5" s="83"/>
+      <c r="MV5" s="83"/>
+      <c r="MW5" s="84"/>
+      <c r="MX5" s="84"/>
+      <c r="MY5" s="84"/>
       <c r="MZ5" s="26"/>
-      <c r="NA5" s="55"/>
-      <c r="NB5" s="55"/>
-      <c r="NC5" s="55"/>
-      <c r="ND5" s="55"/>
-      <c r="NE5" s="55"/>
-      <c r="NF5" s="55"/>
-      <c r="NG5" s="82"/>
-      <c r="NH5" s="85"/>
-      <c r="NI5" s="83"/>
+      <c r="NA5" s="84"/>
+      <c r="NB5" s="84"/>
+      <c r="NC5" s="84"/>
+      <c r="ND5" s="84"/>
+      <c r="NE5" s="84"/>
+      <c r="NF5" s="84"/>
+      <c r="NG5" s="59"/>
+      <c r="NH5" s="60"/>
+      <c r="NI5" s="61"/>
       <c r="NJ5" s="30"/>
     </row>
     <row r="6" spans="1:374" ht="81.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5908,10 +5908,10 @@
       <c r="NG6" s="40" t="s">
         <v>418</v>
       </c>
-      <c r="NH6" s="78" t="s">
+      <c r="NH6" s="54" t="s">
         <v>419</v>
       </c>
-      <c r="NI6" s="79"/>
+      <c r="NI6" s="55"/>
       <c r="NJ6" s="40" t="s">
         <v>420</v>
       </c>
@@ -6068,43 +6068,43 @@
         <v>0</v>
       </c>
       <c r="BO7" s="52">
-        <f>BY7+CI7+CS7+DC7+DM7+DW7+EG7+EQ7+FA7+FK7+FU7+GE7+GO7+GY7</f>
+        <f t="shared" ref="BO7:BX7" si="0">BY7+CI7+CS7+DC7+DM7+DW7+EG7+EQ7+FA7+FK7+FU7+GE7+GO7+GY7</f>
         <v>0</v>
       </c>
       <c r="BP7" s="52">
-        <f>BZ7+CJ7+CT7+DD7+DN7+DX7+EH7+ER7+FB7+FL7+FV7+GF7+GP7+GZ7</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="BQ7" s="52">
-        <f>CA7+CK7+CU7+DE7+DO7+DY7+EI7+ES7+FC7+FM7+FW7+GG7+GQ7+HA7</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="BR7" s="52">
-        <f>CB7+CL7+CV7+DF7+DP7+DZ7+EJ7+ET7+FD7+FN7+FX7+GH7+GR7+HB7</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="BS7" s="52">
-        <f>CC7+CM7+CW7+DG7+DQ7+EA7+EK7+EU7+FE7+FO7+FY7+GI7+GS7+HC7</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="BT7" s="52">
-        <f>CD7+CN7+CX7+DH7+DR7+EB7+EL7+EV7+FF7+FP7+FZ7+GJ7+GT7+HD7</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="BU7" s="52">
-        <f>CE7+CO7+CY7+DI7+DS7+EC7+EM7+EW7+FG7+FQ7+GA7+GK7+GU7+HE7</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="BV7" s="52">
-        <f>CF7+CP7+CZ7+DJ7+DT7+ED7+EN7+EX7+FH7+FR7+GB7+GL7+GV7+HF7</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="BW7" s="52">
-        <f>CG7+CQ7+DA7+DK7+DU7+EE7+EO7+EY7+FI7+FS7+GC7+GM7+GW7+HG7</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="BX7" s="52">
-        <f>CH7+CR7+DB7+DL7+DV7+EF7+EP7+EZ7+FJ7+FT7+GD7+GN7+GX7+HH7</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="BY7" s="47"/>
@@ -6409,6 +6409,35 @@
   </sheetData>
   <autoFilter ref="A6:MZ6" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="45">
+    <mergeCell ref="KA4:KJ4"/>
+    <mergeCell ref="MI4:MV5"/>
+    <mergeCell ref="MW4:MY5"/>
+    <mergeCell ref="NA4:NF5"/>
+    <mergeCell ref="KK4:KT4"/>
+    <mergeCell ref="KU4:LD4"/>
+    <mergeCell ref="LE4:LN4"/>
+    <mergeCell ref="LO4:LX4"/>
+    <mergeCell ref="LY4:MH4"/>
+    <mergeCell ref="IC4:IL4"/>
+    <mergeCell ref="IM4:IV4"/>
+    <mergeCell ref="IW4:JF4"/>
+    <mergeCell ref="JG4:JP4"/>
+    <mergeCell ref="JQ4:JZ4"/>
+    <mergeCell ref="GE4:GN4"/>
+    <mergeCell ref="GO4:GX4"/>
+    <mergeCell ref="GY4:HH4"/>
+    <mergeCell ref="HI4:HR4"/>
+    <mergeCell ref="HS4:IB4"/>
+    <mergeCell ref="EG4:EP4"/>
+    <mergeCell ref="EQ4:EZ4"/>
+    <mergeCell ref="FA4:FJ4"/>
+    <mergeCell ref="FK4:FT4"/>
+    <mergeCell ref="FU4:GD4"/>
+    <mergeCell ref="CI4:CR4"/>
+    <mergeCell ref="CS4:DB4"/>
+    <mergeCell ref="DC4:DL4"/>
+    <mergeCell ref="DM4:DV4"/>
+    <mergeCell ref="DW4:EF4"/>
     <mergeCell ref="NH6:NI6"/>
     <mergeCell ref="NG4:NI5"/>
     <mergeCell ref="A1:B1"/>
@@ -6425,35 +6454,6 @@
     <mergeCell ref="AM4:BN5"/>
     <mergeCell ref="BO4:BX4"/>
     <mergeCell ref="BY4:CH4"/>
-    <mergeCell ref="CI4:CR4"/>
-    <mergeCell ref="CS4:DB4"/>
-    <mergeCell ref="DC4:DL4"/>
-    <mergeCell ref="DM4:DV4"/>
-    <mergeCell ref="DW4:EF4"/>
-    <mergeCell ref="EG4:EP4"/>
-    <mergeCell ref="EQ4:EZ4"/>
-    <mergeCell ref="FA4:FJ4"/>
-    <mergeCell ref="FK4:FT4"/>
-    <mergeCell ref="FU4:GD4"/>
-    <mergeCell ref="GE4:GN4"/>
-    <mergeCell ref="GO4:GX4"/>
-    <mergeCell ref="GY4:HH4"/>
-    <mergeCell ref="HI4:HR4"/>
-    <mergeCell ref="HS4:IB4"/>
-    <mergeCell ref="IC4:IL4"/>
-    <mergeCell ref="IM4:IV4"/>
-    <mergeCell ref="IW4:JF4"/>
-    <mergeCell ref="JG4:JP4"/>
-    <mergeCell ref="JQ4:JZ4"/>
-    <mergeCell ref="KA4:KJ4"/>
-    <mergeCell ref="MI4:MV5"/>
-    <mergeCell ref="MW4:MY5"/>
-    <mergeCell ref="NA4:NF5"/>
-    <mergeCell ref="KK4:KT4"/>
-    <mergeCell ref="KU4:LD4"/>
-    <mergeCell ref="LE4:LN4"/>
-    <mergeCell ref="LO4:LX4"/>
-    <mergeCell ref="LY4:MH4"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:A6">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
